--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -10790,6 +10790,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E353">
+        <v>14.94</v>
+      </c>
+      <c r="F353">
+        <v>-8.960000000000001</v>
+      </c>
       <c r="G353" s="2">
         <v>45748</v>
       </c>
@@ -10815,6 +10821,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E354">
+        <v>14.04</v>
+      </c>
+      <c r="F354">
+        <v>0.57</v>
+      </c>
       <c r="G354" s="2">
         <v>45748</v>
       </c>
@@ -10840,6 +10852,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E355">
+        <v>4.96</v>
+      </c>
+      <c r="F355">
+        <v>38.55</v>
+      </c>
       <c r="G355" s="2">
         <v>45748</v>
       </c>
@@ -10865,6 +10883,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E356">
+        <v>27.51</v>
+      </c>
+      <c r="F356">
+        <v>26.13</v>
+      </c>
       <c r="G356" s="2">
         <v>45748</v>
       </c>
@@ -10890,6 +10914,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E357">
+        <v>20.35</v>
+      </c>
+      <c r="F357">
+        <v>1.45</v>
+      </c>
       <c r="G357" s="2">
         <v>45748</v>
       </c>
@@ -10915,6 +10945,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E358">
+        <v>334.85</v>
+      </c>
+      <c r="F358">
+        <v>3.7</v>
+      </c>
       <c r="G358" s="2">
         <v>45748</v>
       </c>
@@ -10940,6 +10976,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E359">
+        <v>5.71</v>
+      </c>
+      <c r="F359">
+        <v>1.42</v>
+      </c>
       <c r="G359" s="2">
         <v>45748</v>
       </c>
@@ -10965,6 +11007,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E360">
+        <v>29.63</v>
+      </c>
+      <c r="F360">
+        <v>2.56</v>
+      </c>
       <c r="G360" s="2">
         <v>45748</v>
       </c>
@@ -10990,6 +11038,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E361">
+        <v>36.41</v>
+      </c>
+      <c r="F361">
+        <v>4.96</v>
+      </c>
       <c r="G361" s="2">
         <v>45748</v>
       </c>
@@ -11015,6 +11069,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E362">
+        <v>24.22</v>
+      </c>
+      <c r="F362">
+        <v>1.51</v>
+      </c>
       <c r="G362" s="2">
         <v>45748</v>
       </c>
@@ -11040,6 +11100,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E363">
+        <v>94.2</v>
+      </c>
+      <c r="F363">
+        <v>3.29</v>
+      </c>
       <c r="G363" s="2">
         <v>45748</v>
       </c>
@@ -11065,6 +11131,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E364">
+        <v>67.37</v>
+      </c>
+      <c r="F364">
+        <v>-11.78</v>
+      </c>
       <c r="G364" s="2">
         <v>45748</v>
       </c>
@@ -11089,6 +11161,12 @@
         <is>
           <t>Óleo de Soja</t>
         </is>
+      </c>
+      <c r="E365">
+        <v>6.47</v>
+      </c>
+      <c r="F365">
+        <v>-0.46</v>
       </c>
       <c r="G365" s="2">
         <v>45748</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G573"/>
+  <dimension ref="A1:G677"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -11175,17 +11175,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -11194,23 +11194,23 @@
         </is>
       </c>
       <c r="G366" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -11219,23 +11219,23 @@
         </is>
       </c>
       <c r="G367" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -11244,23 +11244,23 @@
         </is>
       </c>
       <c r="G368" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -11269,23 +11269,23 @@
         </is>
       </c>
       <c r="G369" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -11294,23 +11294,23 @@
         </is>
       </c>
       <c r="G370" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -11319,23 +11319,23 @@
         </is>
       </c>
       <c r="G371" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -11344,23 +11344,23 @@
         </is>
       </c>
       <c r="G372" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -11369,23 +11369,23 @@
         </is>
       </c>
       <c r="G373" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -11394,23 +11394,23 @@
         </is>
       </c>
       <c r="G374" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -11419,23 +11419,23 @@
         </is>
       </c>
       <c r="G375" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -11444,23 +11444,23 @@
         </is>
       </c>
       <c r="G376" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -11469,23 +11469,23 @@
         </is>
       </c>
       <c r="G377" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -11494,23 +11494,23 @@
         </is>
       </c>
       <c r="G378" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -11518,27 +11518,24 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E379">
-        <v>18.31</v>
-      </c>
       <c r="G379" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -11546,27 +11543,24 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E380">
-        <v>13.46</v>
-      </c>
       <c r="G380" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -11574,27 +11568,24 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E381">
-        <v>5.63</v>
-      </c>
       <c r="G381" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -11602,27 +11593,24 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E382">
-        <v>56.91</v>
-      </c>
       <c r="G382" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -11630,27 +11618,24 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E383">
-        <v>8.75</v>
-      </c>
       <c r="G383" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -11658,27 +11643,24 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E384">
-        <v>234.48</v>
-      </c>
       <c r="G384" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -11686,27 +11668,24 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E385">
-        <v>5.73</v>
-      </c>
       <c r="G385" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -11714,27 +11693,24 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E386">
-        <v>39.21</v>
-      </c>
       <c r="G386" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -11742,27 +11718,24 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E387">
-        <v>29.62</v>
-      </c>
       <c r="G387" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -11770,27 +11743,24 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E388">
-        <v>18.75</v>
-      </c>
       <c r="G388" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -11798,27 +11768,24 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E389">
-        <v>83.66</v>
-      </c>
       <c r="G389" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -11826,27 +11793,24 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E390">
-        <v>94.41</v>
-      </c>
       <c r="G390" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -11854,27 +11818,24 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E391">
-        <v>5.42</v>
-      </c>
       <c r="G391" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11882,30 +11843,24 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E392">
-        <v>19.41</v>
-      </c>
-      <c r="F392">
-        <v>6.01</v>
-      </c>
       <c r="G392" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11913,30 +11868,24 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E393">
-        <v>14.67</v>
-      </c>
-      <c r="F393">
-        <v>8.99</v>
-      </c>
       <c r="G393" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11944,30 +11893,24 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E394">
-        <v>6.95</v>
-      </c>
-      <c r="F394">
-        <v>23.45</v>
-      </c>
       <c r="G394" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11975,30 +11918,24 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E395">
-        <v>47.64</v>
-      </c>
-      <c r="F395">
-        <v>-16.29</v>
-      </c>
       <c r="G395" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -12006,30 +11943,24 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E396">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="F396">
-        <v>4.11</v>
-      </c>
       <c r="G396" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -12037,30 +11968,24 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E397">
-        <v>275.65</v>
-      </c>
-      <c r="F397">
-        <v>17.56</v>
-      </c>
       <c r="G397" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -12068,30 +11993,24 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E398">
-        <v>6.43</v>
-      </c>
-      <c r="F398">
-        <v>12.22</v>
-      </c>
       <c r="G398" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -12099,30 +12018,24 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E399">
-        <v>45.58</v>
-      </c>
-      <c r="F399">
-        <v>16.25</v>
-      </c>
       <c r="G399" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -12130,30 +12043,24 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E400">
-        <v>30.86</v>
-      </c>
-      <c r="F400">
-        <v>4.19</v>
-      </c>
       <c r="G400" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12161,30 +12068,24 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E401">
-        <v>20.05</v>
-      </c>
-      <c r="F401">
-        <v>6.93</v>
-      </c>
       <c r="G401" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -12192,30 +12093,24 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E402">
-        <v>68.67</v>
-      </c>
-      <c r="F402">
-        <v>-17.92</v>
-      </c>
       <c r="G402" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -12223,30 +12118,24 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E403">
-        <v>85.41</v>
-      </c>
-      <c r="F403">
-        <v>-9.529999999999999</v>
-      </c>
       <c r="G403" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -12254,30 +12143,24 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E404">
-        <v>5.55</v>
-      </c>
-      <c r="F404">
-        <v>2.4</v>
-      </c>
       <c r="G404" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -12285,30 +12168,24 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E405">
-        <v>18.86</v>
-      </c>
-      <c r="F405">
-        <v>-2.83</v>
-      </c>
       <c r="G405" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -12316,30 +12193,24 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E406">
-        <v>13.88</v>
-      </c>
-      <c r="F406">
-        <v>-5.39</v>
-      </c>
       <c r="G406" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -12347,30 +12218,24 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E407">
-        <v>6.11</v>
-      </c>
-      <c r="F407">
-        <v>-12.09</v>
-      </c>
       <c r="G407" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -12378,30 +12243,24 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E408">
-        <v>37.94</v>
-      </c>
-      <c r="F408">
-        <v>-20.36</v>
-      </c>
       <c r="G408" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -12409,30 +12268,24 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E409">
-        <v>9.18</v>
-      </c>
-      <c r="F409">
-        <v>0.77</v>
-      </c>
       <c r="G409" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -12440,30 +12293,24 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E410">
-        <v>254.3</v>
-      </c>
-      <c r="F410">
-        <v>-7.75</v>
-      </c>
       <c r="G410" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -12471,30 +12318,24 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E411">
-        <v>5.84</v>
-      </c>
-      <c r="F411">
-        <v>-9.18</v>
-      </c>
       <c r="G411" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -12502,30 +12343,24 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E412">
-        <v>40.17</v>
-      </c>
-      <c r="F412">
-        <v>-11.87</v>
-      </c>
       <c r="G412" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -12533,30 +12368,24 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E413">
-        <v>30.55</v>
-      </c>
-      <c r="F413">
-        <v>-1</v>
-      </c>
       <c r="G413" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -12564,30 +12393,24 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E414">
-        <v>20.32</v>
-      </c>
-      <c r="F414">
-        <v>1.35</v>
-      </c>
       <c r="G414" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -12595,30 +12418,24 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E415">
-        <v>81.58</v>
-      </c>
-      <c r="F415">
-        <v>18.8</v>
-      </c>
       <c r="G415" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -12626,30 +12443,24 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E416">
-        <v>95.61</v>
-      </c>
-      <c r="F416">
-        <v>11.94</v>
-      </c>
       <c r="G416" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -12657,14 +12468,8 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E417">
-        <v>5.37</v>
-      </c>
-      <c r="F417">
-        <v>-3.24</v>
-      </c>
       <c r="G417" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="418">
@@ -12675,7 +12480,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -12688,14 +12493,8 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E418">
-        <v>17.57</v>
-      </c>
-      <c r="F418">
-        <v>-6.84</v>
-      </c>
       <c r="G418" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="419">
@@ -12706,7 +12505,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -12719,14 +12518,8 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E419">
-        <v>13.71</v>
-      </c>
-      <c r="F419">
-        <v>-1.22</v>
-      </c>
       <c r="G419" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="420">
@@ -12737,7 +12530,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -12750,14 +12543,8 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E420">
-        <v>6.11</v>
-      </c>
-      <c r="F420">
-        <v>0</v>
-      </c>
       <c r="G420" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="421">
@@ -12768,7 +12555,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -12781,14 +12568,8 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E421">
-        <v>43.94</v>
-      </c>
-      <c r="F421">
-        <v>15.81</v>
-      </c>
       <c r="G421" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="422">
@@ -12799,7 +12580,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -12812,14 +12593,8 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E422">
-        <v>9.65</v>
-      </c>
-      <c r="F422">
-        <v>5.12</v>
-      </c>
       <c r="G422" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="423">
@@ -12830,7 +12605,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -12843,14 +12618,8 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E423">
-        <v>252.8</v>
-      </c>
-      <c r="F423">
-        <v>-0.59</v>
-      </c>
       <c r="G423" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="424">
@@ -12861,7 +12630,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -12874,14 +12643,8 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E424">
-        <v>5.66</v>
-      </c>
-      <c r="F424">
-        <v>-3.08</v>
-      </c>
       <c r="G424" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="425">
@@ -12892,7 +12655,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -12905,14 +12668,8 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E425">
-        <v>35.28</v>
-      </c>
-      <c r="F425">
-        <v>-12.17</v>
-      </c>
       <c r="G425" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="426">
@@ -12923,7 +12680,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12936,14 +12693,8 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E426">
-        <v>32.27</v>
-      </c>
-      <c r="F426">
-        <v>5.63</v>
-      </c>
       <c r="G426" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="427">
@@ -12954,7 +12705,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12967,14 +12718,8 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E427">
-        <v>20.09</v>
-      </c>
-      <c r="F427">
-        <v>-1.13</v>
-      </c>
       <c r="G427" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="428">
@@ -12985,7 +12730,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12998,14 +12743,8 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E428">
-        <v>81.58</v>
-      </c>
-      <c r="F428">
-        <v>0</v>
-      </c>
       <c r="G428" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="429">
@@ -13016,7 +12755,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -13029,14 +12768,8 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E429">
-        <v>86.28</v>
-      </c>
-      <c r="F429">
-        <v>-9.76</v>
-      </c>
       <c r="G429" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="430">
@@ -13047,7 +12780,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -13060,14 +12793,8 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E430">
-        <v>5.08</v>
-      </c>
-      <c r="F430">
-        <v>-5.4</v>
-      </c>
       <c r="G430" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="431">
@@ -13078,7 +12805,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -13092,13 +12819,10 @@
         </is>
       </c>
       <c r="E431">
-        <v>19.58</v>
-      </c>
-      <c r="F431">
-        <v>11.44</v>
+        <v>18.31</v>
       </c>
       <c r="G431" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="432">
@@ -13109,7 +12833,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -13123,13 +12847,10 @@
         </is>
       </c>
       <c r="E432">
-        <v>13.62</v>
-      </c>
-      <c r="F432">
-        <v>-0.66</v>
+        <v>13.46</v>
       </c>
       <c r="G432" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="433">
@@ -13140,7 +12861,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -13154,13 +12875,10 @@
         </is>
       </c>
       <c r="E433">
-        <v>5.21</v>
-      </c>
-      <c r="F433">
-        <v>-14.73</v>
+        <v>5.63</v>
       </c>
       <c r="G433" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="434">
@@ -13171,7 +12889,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -13185,13 +12903,10 @@
         </is>
       </c>
       <c r="E434">
-        <v>55.14</v>
-      </c>
-      <c r="F434">
-        <v>25.49</v>
+        <v>56.91</v>
       </c>
       <c r="G434" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="435">
@@ -13202,7 +12917,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -13216,13 +12931,10 @@
         </is>
       </c>
       <c r="E435">
-        <v>9.56</v>
-      </c>
-      <c r="F435">
-        <v>-0.93</v>
+        <v>8.75</v>
       </c>
       <c r="G435" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="436">
@@ -13233,7 +12945,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -13247,13 +12959,10 @@
         </is>
       </c>
       <c r="E436">
-        <v>237.34</v>
-      </c>
-      <c r="F436">
-        <v>-6.12</v>
+        <v>234.48</v>
       </c>
       <c r="G436" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="437">
@@ -13264,7 +12973,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -13278,13 +12987,10 @@
         </is>
       </c>
       <c r="E437">
-        <v>6.14</v>
-      </c>
-      <c r="F437">
-        <v>8.48</v>
+        <v>5.73</v>
       </c>
       <c r="G437" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="438">
@@ -13295,7 +13001,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -13309,13 +13015,10 @@
         </is>
       </c>
       <c r="E438">
-        <v>32.87</v>
-      </c>
-      <c r="F438">
-        <v>-6.83</v>
+        <v>39.21</v>
       </c>
       <c r="G438" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="439">
@@ -13326,7 +13029,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -13340,13 +13043,10 @@
         </is>
       </c>
       <c r="E439">
-        <v>37.54</v>
-      </c>
-      <c r="F439">
-        <v>16.33</v>
+        <v>29.62</v>
       </c>
       <c r="G439" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="440">
@@ -13357,7 +13057,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -13371,13 +13071,10 @@
         </is>
       </c>
       <c r="E440">
-        <v>20.26</v>
-      </c>
-      <c r="F440">
-        <v>0.85</v>
+        <v>18.75</v>
       </c>
       <c r="G440" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="441">
@@ -13388,7 +13085,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -13402,13 +13099,10 @@
         </is>
       </c>
       <c r="E441">
-        <v>83.67</v>
-      </c>
-      <c r="F441">
-        <v>2.56</v>
+        <v>83.66</v>
       </c>
       <c r="G441" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="442">
@@ -13419,7 +13113,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -13433,13 +13127,10 @@
         </is>
       </c>
       <c r="E442">
-        <v>103.41</v>
-      </c>
-      <c r="F442">
-        <v>19.85</v>
+        <v>94.41</v>
       </c>
       <c r="G442" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="443">
@@ -13450,7 +13141,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -13464,13 +13155,10 @@
         </is>
       </c>
       <c r="E443">
-        <v>5.44</v>
-      </c>
-      <c r="F443">
-        <v>7.09</v>
+        <v>5.42</v>
       </c>
       <c r="G443" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="444">
@@ -13481,7 +13169,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -13498,10 +13186,10 @@
         <v>19.41</v>
       </c>
       <c r="F444">
-        <v>-0.87</v>
+        <v>6.01</v>
       </c>
       <c r="G444" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="445">
@@ -13512,7 +13200,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -13526,13 +13214,13 @@
         </is>
       </c>
       <c r="E445">
-        <v>13.54</v>
+        <v>14.67</v>
       </c>
       <c r="F445">
-        <v>-0.59</v>
+        <v>8.99</v>
       </c>
       <c r="G445" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="446">
@@ -13543,7 +13231,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -13557,13 +13245,13 @@
         </is>
       </c>
       <c r="E446">
-        <v>5.59</v>
+        <v>6.95</v>
       </c>
       <c r="F446">
-        <v>7.29</v>
+        <v>23.45</v>
       </c>
       <c r="G446" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="447">
@@ -13574,7 +13262,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -13588,13 +13276,13 @@
         </is>
       </c>
       <c r="E447">
-        <v>59.34</v>
+        <v>47.64</v>
       </c>
       <c r="F447">
-        <v>7.62</v>
+        <v>-16.29</v>
       </c>
       <c r="G447" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="448">
@@ -13605,7 +13293,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -13619,13 +13307,13 @@
         </is>
       </c>
       <c r="E448">
-        <v>10.44</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F448">
-        <v>9.210000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="G448" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="449">
@@ -13636,7 +13324,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -13650,13 +13338,13 @@
         </is>
       </c>
       <c r="E449">
-        <v>242.59</v>
+        <v>275.65</v>
       </c>
       <c r="F449">
-        <v>2.21</v>
+        <v>17.56</v>
       </c>
       <c r="G449" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="450">
@@ -13667,7 +13355,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -13681,13 +13369,13 @@
         </is>
       </c>
       <c r="E450">
-        <v>6.33</v>
+        <v>6.43</v>
       </c>
       <c r="F450">
-        <v>3.09</v>
+        <v>12.22</v>
       </c>
       <c r="G450" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="451">
@@ -13698,7 +13386,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -13712,13 +13400,13 @@
         </is>
       </c>
       <c r="E451">
-        <v>33.7</v>
+        <v>45.58</v>
       </c>
       <c r="F451">
-        <v>2.53</v>
+        <v>16.25</v>
       </c>
       <c r="G451" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="452">
@@ -13729,7 +13417,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -13743,13 +13431,13 @@
         </is>
       </c>
       <c r="E452">
-        <v>35.25</v>
+        <v>30.86</v>
       </c>
       <c r="F452">
-        <v>-6.1</v>
+        <v>4.19</v>
       </c>
       <c r="G452" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="453">
@@ -13760,7 +13448,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13774,13 +13462,13 @@
         </is>
       </c>
       <c r="E453">
-        <v>20.17</v>
+        <v>20.05</v>
       </c>
       <c r="F453">
-        <v>-0.44</v>
+        <v>6.93</v>
       </c>
       <c r="G453" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="454">
@@ -13791,7 +13479,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13805,13 +13493,13 @@
         </is>
       </c>
       <c r="E454">
-        <v>71.58</v>
+        <v>68.67</v>
       </c>
       <c r="F454">
-        <v>-14.45</v>
+        <v>-17.92</v>
       </c>
       <c r="G454" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="455">
@@ -13822,7 +13510,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -13836,13 +13524,13 @@
         </is>
       </c>
       <c r="E455">
-        <v>58.41</v>
+        <v>85.41</v>
       </c>
       <c r="F455">
-        <v>-43.52</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="G455" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="456">
@@ -13853,7 +13541,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13867,13 +13555,13 @@
         </is>
       </c>
       <c r="E456">
-        <v>5.32</v>
+        <v>5.55</v>
       </c>
       <c r="F456">
-        <v>-2.21</v>
+        <v>2.4</v>
       </c>
       <c r="G456" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="457">
@@ -13884,7 +13572,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -13898,13 +13586,13 @@
         </is>
       </c>
       <c r="E457">
-        <v>19.57</v>
+        <v>18.86</v>
       </c>
       <c r="F457">
-        <v>0.82</v>
+        <v>-2.83</v>
       </c>
       <c r="G457" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="458">
@@ -13915,7 +13603,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -13929,13 +13617,13 @@
         </is>
       </c>
       <c r="E458">
-        <v>13.78</v>
+        <v>13.88</v>
       </c>
       <c r="F458">
-        <v>1.77</v>
+        <v>-5.39</v>
       </c>
       <c r="G458" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="459">
@@ -13946,7 +13634,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -13963,10 +13651,10 @@
         <v>6.11</v>
       </c>
       <c r="F459">
-        <v>9.300000000000001</v>
+        <v>-12.09</v>
       </c>
       <c r="G459" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="460">
@@ -13977,7 +13665,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13991,13 +13679,13 @@
         </is>
       </c>
       <c r="E460">
-        <v>48.54</v>
+        <v>37.94</v>
       </c>
       <c r="F460">
-        <v>-18.2</v>
+        <v>-20.36</v>
       </c>
       <c r="G460" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="461">
@@ -14008,7 +13696,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -14022,13 +13710,13 @@
         </is>
       </c>
       <c r="E461">
-        <v>10.44</v>
+        <v>9.18</v>
       </c>
       <c r="F461">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="G461" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="462">
@@ -14039,7 +13727,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -14053,13 +13741,13 @@
         </is>
       </c>
       <c r="E462">
-        <v>241.01</v>
+        <v>254.3</v>
       </c>
       <c r="F462">
-        <v>-0.65</v>
+        <v>-7.75</v>
       </c>
       <c r="G462" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="463">
@@ -14070,7 +13758,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -14084,13 +13772,13 @@
         </is>
       </c>
       <c r="E463">
-        <v>6.68</v>
+        <v>5.84</v>
       </c>
       <c r="F463">
-        <v>5.53</v>
+        <v>-9.18</v>
       </c>
       <c r="G463" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="464">
@@ -14101,7 +13789,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -14115,13 +13803,13 @@
         </is>
       </c>
       <c r="E464">
-        <v>33.64</v>
+        <v>40.17</v>
       </c>
       <c r="F464">
-        <v>-0.18</v>
+        <v>-11.87</v>
       </c>
       <c r="G464" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="465">
@@ -14132,7 +13820,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -14146,13 +13834,13 @@
         </is>
       </c>
       <c r="E465">
-        <v>33.48</v>
+        <v>30.55</v>
       </c>
       <c r="F465">
-        <v>-5.02</v>
+        <v>-1</v>
       </c>
       <c r="G465" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="466">
@@ -14163,7 +13851,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -14177,13 +13865,13 @@
         </is>
       </c>
       <c r="E466">
-        <v>20.5</v>
+        <v>20.32</v>
       </c>
       <c r="F466">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="G466" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="467">
@@ -14194,7 +13882,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -14208,13 +13896,13 @@
         </is>
       </c>
       <c r="E467">
-        <v>85.58</v>
+        <v>81.58</v>
       </c>
       <c r="F467">
-        <v>19.56</v>
+        <v>18.8</v>
       </c>
       <c r="G467" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="468">
@@ -14225,7 +13913,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -14239,13 +13927,13 @@
         </is>
       </c>
       <c r="E468">
-        <v>56.31</v>
+        <v>95.61</v>
       </c>
       <c r="F468">
-        <v>-3.6</v>
+        <v>11.94</v>
       </c>
       <c r="G468" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="469">
@@ -14256,7 +13944,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -14270,13 +13958,13 @@
         </is>
       </c>
       <c r="E469">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="F469">
-        <v>0.5600000000000001</v>
+        <v>-3.24</v>
       </c>
       <c r="G469" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="470">
@@ -14287,7 +13975,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -14301,13 +13989,13 @@
         </is>
       </c>
       <c r="E470">
-        <v>20.28</v>
+        <v>17.57</v>
       </c>
       <c r="F470">
-        <v>3.63</v>
+        <v>-6.84</v>
       </c>
       <c r="G470" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="471">
@@ -14318,7 +14006,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -14335,10 +14023,10 @@
         <v>13.71</v>
       </c>
       <c r="F471">
-        <v>-0.51</v>
+        <v>-1.22</v>
       </c>
       <c r="G471" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="472">
@@ -14349,7 +14037,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -14363,13 +14051,13 @@
         </is>
       </c>
       <c r="E472">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="F472">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="G472" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="473">
@@ -14380,7 +14068,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -14394,13 +14082,13 @@
         </is>
       </c>
       <c r="E473">
-        <v>41.73</v>
+        <v>43.94</v>
       </c>
       <c r="F473">
-        <v>-14.03</v>
+        <v>15.81</v>
       </c>
       <c r="G473" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="474">
@@ -14411,7 +14099,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -14425,13 +14113,13 @@
         </is>
       </c>
       <c r="E474">
-        <v>11.04</v>
+        <v>9.65</v>
       </c>
       <c r="F474">
-        <v>5.75</v>
+        <v>5.12</v>
       </c>
       <c r="G474" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="475">
@@ -14442,7 +14130,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -14456,13 +14144,13 @@
         </is>
       </c>
       <c r="E475">
-        <v>237.85</v>
+        <v>252.8</v>
       </c>
       <c r="F475">
-        <v>-1.31</v>
+        <v>-0.59</v>
       </c>
       <c r="G475" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="476">
@@ -14473,7 +14161,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -14487,13 +14175,13 @@
         </is>
       </c>
       <c r="E476">
-        <v>6.41</v>
+        <v>5.66</v>
       </c>
       <c r="F476">
-        <v>-4.04</v>
+        <v>-3.08</v>
       </c>
       <c r="G476" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="477">
@@ -14504,7 +14192,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -14518,13 +14206,13 @@
         </is>
       </c>
       <c r="E477">
-        <v>37.09</v>
+        <v>35.28</v>
       </c>
       <c r="F477">
-        <v>10.26</v>
+        <v>-12.17</v>
       </c>
       <c r="G477" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="478">
@@ -14535,7 +14223,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -14549,13 +14237,13 @@
         </is>
       </c>
       <c r="E478">
-        <v>34.69</v>
+        <v>32.27</v>
       </c>
       <c r="F478">
-        <v>3.61</v>
+        <v>5.63</v>
       </c>
       <c r="G478" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="479">
@@ -14566,7 +14254,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -14580,13 +14268,13 @@
         </is>
       </c>
       <c r="E479">
-        <v>17.59</v>
+        <v>20.09</v>
       </c>
       <c r="F479">
-        <v>-14.2</v>
+        <v>-1.13</v>
       </c>
       <c r="G479" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="480">
@@ -14597,7 +14285,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -14611,13 +14299,13 @@
         </is>
       </c>
       <c r="E480">
-        <v>88.06</v>
+        <v>81.58</v>
       </c>
       <c r="F480">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="G480" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="481">
@@ -14628,7 +14316,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -14642,13 +14330,13 @@
         </is>
       </c>
       <c r="E481">
-        <v>47.79</v>
+        <v>86.28</v>
       </c>
       <c r="F481">
-        <v>-15.13</v>
+        <v>-9.76</v>
       </c>
       <c r="G481" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="482">
@@ -14659,7 +14347,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -14673,13 +14361,13 @@
         </is>
       </c>
       <c r="E482">
-        <v>5.63</v>
+        <v>5.08</v>
       </c>
       <c r="F482">
-        <v>5.23</v>
+        <v>-5.4</v>
       </c>
       <c r="G482" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="483">
@@ -14690,7 +14378,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -14704,13 +14392,13 @@
         </is>
       </c>
       <c r="E483">
-        <v>19.38</v>
+        <v>19.58</v>
       </c>
       <c r="F483">
-        <v>-4.44</v>
+        <v>11.44</v>
       </c>
       <c r="G483" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="484">
@@ -14721,7 +14409,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -14735,13 +14423,13 @@
         </is>
       </c>
       <c r="E484">
-        <v>13.08</v>
+        <v>13.62</v>
       </c>
       <c r="F484">
-        <v>-4.6</v>
+        <v>-0.66</v>
       </c>
       <c r="G484" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="485">
@@ -14752,7 +14440,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -14766,13 +14454,13 @@
         </is>
       </c>
       <c r="E485">
-        <v>6.59</v>
+        <v>5.21</v>
       </c>
       <c r="F485">
-        <v>2.65</v>
+        <v>-14.73</v>
       </c>
       <c r="G485" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="486">
@@ -14783,7 +14471,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -14797,13 +14485,13 @@
         </is>
       </c>
       <c r="E486">
-        <v>34.74</v>
+        <v>55.14</v>
       </c>
       <c r="F486">
-        <v>-16.75</v>
+        <v>25.49</v>
       </c>
       <c r="G486" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="487">
@@ -14814,7 +14502,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -14828,13 +14516,13 @@
         </is>
       </c>
       <c r="E487">
-        <v>11.83</v>
+        <v>9.56</v>
       </c>
       <c r="F487">
-        <v>7.16</v>
+        <v>-0.93</v>
       </c>
       <c r="G487" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="488">
@@ -14845,7 +14533,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -14859,13 +14547,13 @@
         </is>
       </c>
       <c r="E488">
-        <v>238.33</v>
+        <v>237.34</v>
       </c>
       <c r="F488">
-        <v>0.2</v>
+        <v>-6.12</v>
       </c>
       <c r="G488" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="489">
@@ -14876,7 +14564,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -14890,13 +14578,13 @@
         </is>
       </c>
       <c r="E489">
-        <v>5.98</v>
+        <v>6.14</v>
       </c>
       <c r="F489">
-        <v>-6.71</v>
+        <v>8.48</v>
       </c>
       <c r="G489" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="490">
@@ -14907,7 +14595,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -14921,13 +14609,13 @@
         </is>
       </c>
       <c r="E490">
-        <v>32.98</v>
+        <v>32.87</v>
       </c>
       <c r="F490">
-        <v>-11.08</v>
+        <v>-6.83</v>
       </c>
       <c r="G490" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="491">
@@ -14938,7 +14626,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -14952,13 +14640,13 @@
         </is>
       </c>
       <c r="E491">
-        <v>35.17</v>
+        <v>37.54</v>
       </c>
       <c r="F491">
-        <v>1.38</v>
+        <v>16.33</v>
       </c>
       <c r="G491" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="492">
@@ -14969,7 +14657,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -14983,13 +14671,13 @@
         </is>
       </c>
       <c r="E492">
-        <v>20.02</v>
+        <v>20.26</v>
       </c>
       <c r="F492">
-        <v>13.81</v>
+        <v>0.85</v>
       </c>
       <c r="G492" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="493">
@@ -15000,7 +14688,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -15014,13 +14702,13 @@
         </is>
       </c>
       <c r="E493">
-        <v>77.37</v>
+        <v>83.67</v>
       </c>
       <c r="F493">
-        <v>-12.14</v>
+        <v>2.56</v>
       </c>
       <c r="G493" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="494">
@@ -15031,7 +14719,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -15045,13 +14733,13 @@
         </is>
       </c>
       <c r="E494">
-        <v>53.46</v>
+        <v>103.41</v>
       </c>
       <c r="F494">
-        <v>11.86</v>
+        <v>19.85</v>
       </c>
       <c r="G494" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="495">
@@ -15062,7 +14750,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -15076,13 +14764,13 @@
         </is>
       </c>
       <c r="E495">
-        <v>5.73</v>
+        <v>5.44</v>
       </c>
       <c r="F495">
-        <v>1.78</v>
+        <v>7.09</v>
       </c>
       <c r="G495" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="496">
@@ -15093,7 +14781,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -15107,13 +14795,13 @@
         </is>
       </c>
       <c r="E496">
-        <v>19.12</v>
+        <v>19.41</v>
       </c>
       <c r="F496">
-        <v>-1.34</v>
+        <v>-0.87</v>
       </c>
       <c r="G496" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="497">
@@ -15124,7 +14812,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -15138,13 +14826,13 @@
         </is>
       </c>
       <c r="E497">
-        <v>12.87</v>
+        <v>13.54</v>
       </c>
       <c r="F497">
-        <v>-1.61</v>
+        <v>-0.59</v>
       </c>
       <c r="G497" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="498">
@@ -15155,7 +14843,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -15169,13 +14857,13 @@
         </is>
       </c>
       <c r="E498">
-        <v>6.59</v>
+        <v>5.59</v>
       </c>
       <c r="F498">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="G498" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="499">
@@ -15186,7 +14874,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -15200,13 +14888,13 @@
         </is>
       </c>
       <c r="E499">
-        <v>38.94</v>
+        <v>59.34</v>
       </c>
       <c r="F499">
-        <v>12.09</v>
+        <v>7.62</v>
       </c>
       <c r="G499" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="500">
@@ -15217,7 +14905,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -15231,13 +14919,13 @@
         </is>
       </c>
       <c r="E500">
-        <v>12.1</v>
+        <v>10.44</v>
       </c>
       <c r="F500">
-        <v>2.28</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G500" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="501">
@@ -15248,7 +14936,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -15262,13 +14950,13 @@
         </is>
       </c>
       <c r="E501">
-        <v>282.41</v>
+        <v>242.59</v>
       </c>
       <c r="F501">
-        <v>18.5</v>
+        <v>2.21</v>
       </c>
       <c r="G501" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="502">
@@ -15279,7 +14967,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -15293,13 +14981,13 @@
         </is>
       </c>
       <c r="E502">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="F502">
-        <v>4.52</v>
+        <v>3.09</v>
       </c>
       <c r="G502" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="503">
@@ -15310,7 +14998,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -15324,13 +15012,13 @@
         </is>
       </c>
       <c r="E503">
-        <v>35.39</v>
+        <v>33.7</v>
       </c>
       <c r="F503">
-        <v>7.31</v>
+        <v>2.53</v>
       </c>
       <c r="G503" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="504">
@@ -15341,7 +15029,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -15355,13 +15043,13 @@
         </is>
       </c>
       <c r="E504">
-        <v>33.86</v>
+        <v>35.25</v>
       </c>
       <c r="F504">
-        <v>-3.72</v>
+        <v>-6.1</v>
       </c>
       <c r="G504" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="505">
@@ -15372,7 +15060,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -15386,13 +15074,13 @@
         </is>
       </c>
       <c r="E505">
-        <v>20.89</v>
+        <v>20.17</v>
       </c>
       <c r="F505">
-        <v>4.35</v>
+        <v>-0.44</v>
       </c>
       <c r="G505" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="506">
@@ -15403,7 +15091,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -15417,13 +15105,13 @@
         </is>
       </c>
       <c r="E506">
-        <v>71.91</v>
+        <v>71.58</v>
       </c>
       <c r="F506">
-        <v>-7.06</v>
+        <v>-14.45</v>
       </c>
       <c r="G506" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="507">
@@ -15434,7 +15122,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -15448,13 +15136,13 @@
         </is>
       </c>
       <c r="E507">
-        <v>44.91</v>
+        <v>58.41</v>
       </c>
       <c r="F507">
-        <v>-15.99</v>
+        <v>-43.52</v>
       </c>
       <c r="G507" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="508">
@@ -15465,7 +15153,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -15479,13 +15167,13 @@
         </is>
       </c>
       <c r="E508">
-        <v>6.36</v>
+        <v>5.32</v>
       </c>
       <c r="F508">
-        <v>10.99</v>
+        <v>-2.21</v>
       </c>
       <c r="G508" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="509">
@@ -15496,7 +15184,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -15510,13 +15198,13 @@
         </is>
       </c>
       <c r="E509">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="F509">
-        <v>-2.88</v>
+        <v>0.82</v>
       </c>
       <c r="G509" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="510">
@@ -15527,7 +15215,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -15541,13 +15229,13 @@
         </is>
       </c>
       <c r="E510">
-        <v>13.17</v>
+        <v>13.78</v>
       </c>
       <c r="F510">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="G510" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="511">
@@ -15558,7 +15246,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -15572,13 +15260,13 @@
         </is>
       </c>
       <c r="E511">
-        <v>5.99</v>
+        <v>6.11</v>
       </c>
       <c r="F511">
-        <v>-9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G511" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="512">
@@ -15589,7 +15277,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -15603,13 +15291,13 @@
         </is>
       </c>
       <c r="E512">
-        <v>23.61</v>
+        <v>48.54</v>
       </c>
       <c r="F512">
-        <v>-39.37</v>
+        <v>-18.2</v>
       </c>
       <c r="G512" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="513">
@@ -15620,7 +15308,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -15634,13 +15322,13 @@
         </is>
       </c>
       <c r="E513">
-        <v>12.26</v>
+        <v>10.44</v>
       </c>
       <c r="F513">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="G513" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="514">
@@ -15651,7 +15339,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -15665,13 +15353,13 @@
         </is>
       </c>
       <c r="E514">
-        <v>274.33</v>
+        <v>241.01</v>
       </c>
       <c r="F514">
-        <v>-2.86</v>
+        <v>-0.65</v>
       </c>
       <c r="G514" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="515">
@@ -15682,7 +15370,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -15696,13 +15384,13 @@
         </is>
       </c>
       <c r="E515">
-        <v>6.17</v>
+        <v>6.68</v>
       </c>
       <c r="F515">
-        <v>-1.28</v>
+        <v>5.53</v>
       </c>
       <c r="G515" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="516">
@@ -15713,7 +15401,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -15727,13 +15415,13 @@
         </is>
       </c>
       <c r="E516">
-        <v>33.66</v>
+        <v>33.64</v>
       </c>
       <c r="F516">
-        <v>-4.89</v>
+        <v>-0.18</v>
       </c>
       <c r="G516" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="517">
@@ -15744,7 +15432,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -15758,13 +15446,13 @@
         </is>
       </c>
       <c r="E517">
-        <v>35.18</v>
+        <v>33.48</v>
       </c>
       <c r="F517">
-        <v>3.9</v>
+        <v>-5.02</v>
       </c>
       <c r="G517" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="518">
@@ -15775,7 +15463,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -15789,13 +15477,13 @@
         </is>
       </c>
       <c r="E518">
-        <v>21.11</v>
+        <v>20.5</v>
       </c>
       <c r="F518">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="G518" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="519">
@@ -15806,7 +15494,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -15820,13 +15508,13 @@
         </is>
       </c>
       <c r="E519">
-        <v>80.37</v>
+        <v>85.58</v>
       </c>
       <c r="F519">
-        <v>11.76</v>
+        <v>19.56</v>
       </c>
       <c r="G519" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="520">
@@ -15837,7 +15525,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -15851,13 +15539,13 @@
         </is>
       </c>
       <c r="E520">
-        <v>34.11</v>
+        <v>56.31</v>
       </c>
       <c r="F520">
-        <v>-24.05</v>
+        <v>-3.6</v>
       </c>
       <c r="G520" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="521">
@@ -15868,7 +15556,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -15882,24 +15570,24 @@
         </is>
       </c>
       <c r="E521">
-        <v>6.83</v>
+        <v>5.35</v>
       </c>
       <c r="F521">
-        <v>7.39</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G521" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -15913,24 +15601,24 @@
         </is>
       </c>
       <c r="E522">
-        <v>17.9</v>
+        <v>20.28</v>
       </c>
       <c r="F522">
-        <v>-3.61</v>
+        <v>3.63</v>
       </c>
       <c r="G522" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -15944,24 +15632,24 @@
         </is>
       </c>
       <c r="E523">
-        <v>14.58</v>
+        <v>13.71</v>
       </c>
       <c r="F523">
-        <v>10.71</v>
+        <v>-0.51</v>
       </c>
       <c r="G523" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -15975,24 +15663,24 @@
         </is>
       </c>
       <c r="E524">
-        <v>6.39</v>
+        <v>6.42</v>
       </c>
       <c r="F524">
-        <v>6.68</v>
+        <v>5.07</v>
       </c>
       <c r="G524" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -16006,24 +15694,24 @@
         </is>
       </c>
       <c r="E525">
-        <v>22.94</v>
+        <v>41.73</v>
       </c>
       <c r="F525">
-        <v>-2.84</v>
+        <v>-14.03</v>
       </c>
       <c r="G525" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -16037,24 +15725,24 @@
         </is>
       </c>
       <c r="E526">
-        <v>13.82</v>
+        <v>11.04</v>
       </c>
       <c r="F526">
-        <v>12.72</v>
+        <v>5.75</v>
       </c>
       <c r="G526" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -16068,24 +15756,24 @@
         </is>
       </c>
       <c r="E527">
-        <v>295.28</v>
+        <v>237.85</v>
       </c>
       <c r="F527">
-        <v>7.64</v>
+        <v>-1.31</v>
       </c>
       <c r="G527" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -16099,24 +15787,24 @@
         </is>
       </c>
       <c r="E528">
-        <v>5.46</v>
+        <v>6.41</v>
       </c>
       <c r="F528">
-        <v>-11.51</v>
+        <v>-4.04</v>
       </c>
       <c r="G528" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -16130,24 +15818,24 @@
         </is>
       </c>
       <c r="E529">
-        <v>30.81</v>
+        <v>37.09</v>
       </c>
       <c r="F529">
-        <v>-8.470000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="G529" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -16161,24 +15849,24 @@
         </is>
       </c>
       <c r="E530">
-        <v>33.42</v>
+        <v>34.69</v>
       </c>
       <c r="F530">
-        <v>-5</v>
+        <v>3.61</v>
       </c>
       <c r="G530" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -16192,24 +15880,24 @@
         </is>
       </c>
       <c r="E531">
-        <v>21.88</v>
+        <v>17.59</v>
       </c>
       <c r="F531">
-        <v>3.65</v>
+        <v>-14.2</v>
       </c>
       <c r="G531" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -16223,24 +15911,24 @@
         </is>
       </c>
       <c r="E532">
-        <v>81.76000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="F532">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="G532" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -16254,24 +15942,24 @@
         </is>
       </c>
       <c r="E533">
-        <v>33.81</v>
+        <v>47.79</v>
       </c>
       <c r="F533">
-        <v>-0.88</v>
+        <v>-15.13</v>
       </c>
       <c r="G533" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -16285,24 +15973,24 @@
         </is>
       </c>
       <c r="E534">
-        <v>7.19</v>
+        <v>5.63</v>
       </c>
       <c r="F534">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="G534" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -16316,24 +16004,24 @@
         </is>
       </c>
       <c r="E535">
-        <v>18.09</v>
+        <v>19.38</v>
       </c>
       <c r="F535">
-        <v>1.06</v>
+        <v>-4.44</v>
       </c>
       <c r="G535" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -16347,24 +16035,24 @@
         </is>
       </c>
       <c r="E536">
-        <v>14.43</v>
+        <v>13.08</v>
       </c>
       <c r="F536">
-        <v>-1.03</v>
+        <v>-4.6</v>
       </c>
       <c r="G536" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -16378,24 +16066,24 @@
         </is>
       </c>
       <c r="E537">
-        <v>6.35</v>
+        <v>6.59</v>
       </c>
       <c r="F537">
-        <v>-0.63</v>
+        <v>2.65</v>
       </c>
       <c r="G537" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -16409,24 +16097,24 @@
         </is>
       </c>
       <c r="E538">
-        <v>22.94</v>
+        <v>34.74</v>
       </c>
       <c r="F538">
-        <v>0</v>
+        <v>-16.75</v>
       </c>
       <c r="G538" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -16440,24 +16128,24 @@
         </is>
       </c>
       <c r="E539">
-        <v>16.25</v>
+        <v>11.83</v>
       </c>
       <c r="F539">
-        <v>17.58</v>
+        <v>7.16</v>
       </c>
       <c r="G539" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -16471,24 +16159,24 @@
         </is>
       </c>
       <c r="E540">
-        <v>302.48</v>
+        <v>238.33</v>
       </c>
       <c r="F540">
-        <v>2.44</v>
+        <v>0.2</v>
       </c>
       <c r="G540" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -16502,24 +16190,24 @@
         </is>
       </c>
       <c r="E541">
-        <v>5.76</v>
+        <v>5.98</v>
       </c>
       <c r="F541">
-        <v>5.49</v>
+        <v>-6.71</v>
       </c>
       <c r="G541" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -16533,24 +16221,24 @@
         </is>
       </c>
       <c r="E542">
-        <v>32.38</v>
+        <v>32.98</v>
       </c>
       <c r="F542">
-        <v>5.1</v>
+        <v>-11.08</v>
       </c>
       <c r="G542" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -16564,24 +16252,24 @@
         </is>
       </c>
       <c r="E543">
-        <v>33.42</v>
+        <v>35.17</v>
       </c>
       <c r="F543">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="G543" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -16595,24 +16283,24 @@
         </is>
       </c>
       <c r="E544">
-        <v>22.14</v>
+        <v>20.02</v>
       </c>
       <c r="F544">
-        <v>1.19</v>
+        <v>13.81</v>
       </c>
       <c r="G544" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16626,24 +16314,24 @@
         </is>
       </c>
       <c r="E545">
-        <v>81.14</v>
+        <v>77.37</v>
       </c>
       <c r="F545">
-        <v>-0.76</v>
+        <v>-12.14</v>
       </c>
       <c r="G545" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -16657,24 +16345,24 @@
         </is>
       </c>
       <c r="E546">
-        <v>47.91</v>
+        <v>53.46</v>
       </c>
       <c r="F546">
-        <v>41.7</v>
+        <v>11.86</v>
       </c>
       <c r="G546" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -16688,24 +16376,24 @@
         </is>
       </c>
       <c r="E547">
-        <v>7.03</v>
+        <v>5.73</v>
       </c>
       <c r="F547">
-        <v>-2.23</v>
+        <v>1.78</v>
       </c>
       <c r="G547" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -16719,24 +16407,24 @@
         </is>
       </c>
       <c r="E548">
-        <v>16.67</v>
+        <v>19.12</v>
       </c>
       <c r="F548">
-        <v>-7.85</v>
+        <v>-1.34</v>
       </c>
       <c r="G548" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -16750,24 +16438,24 @@
         </is>
       </c>
       <c r="E549">
-        <v>13.87</v>
+        <v>12.87</v>
       </c>
       <c r="F549">
-        <v>-3.88</v>
+        <v>-1.61</v>
       </c>
       <c r="G549" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -16781,24 +16469,24 @@
         </is>
       </c>
       <c r="E550">
-        <v>4.47</v>
+        <v>6.59</v>
       </c>
       <c r="F550">
-        <v>-29.61</v>
+        <v>0</v>
       </c>
       <c r="G550" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -16812,24 +16500,24 @@
         </is>
       </c>
       <c r="E551">
-        <v>17.54</v>
+        <v>38.94</v>
       </c>
       <c r="F551">
-        <v>-23.54</v>
+        <v>12.09</v>
       </c>
       <c r="G551" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -16843,24 +16531,24 @@
         </is>
       </c>
       <c r="E552">
-        <v>16.73</v>
+        <v>12.1</v>
       </c>
       <c r="F552">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="G552" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -16874,24 +16562,24 @@
         </is>
       </c>
       <c r="E553">
-        <v>306.06</v>
+        <v>282.41</v>
       </c>
       <c r="F553">
-        <v>1.18</v>
+        <v>18.5</v>
       </c>
       <c r="G553" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -16905,24 +16593,24 @@
         </is>
       </c>
       <c r="E554">
-        <v>6.16</v>
+        <v>6.25</v>
       </c>
       <c r="F554">
-        <v>6.94</v>
+        <v>4.52</v>
       </c>
       <c r="G554" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -16936,24 +16624,24 @@
         </is>
       </c>
       <c r="E555">
-        <v>26.22</v>
+        <v>35.39</v>
       </c>
       <c r="F555">
-        <v>-19.02</v>
+        <v>7.31</v>
       </c>
       <c r="G555" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -16967,24 +16655,24 @@
         </is>
       </c>
       <c r="E556">
-        <v>35.12</v>
+        <v>33.86</v>
       </c>
       <c r="F556">
-        <v>5.09</v>
+        <v>-3.72</v>
       </c>
       <c r="G556" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -16998,24 +16686,24 @@
         </is>
       </c>
       <c r="E557">
-        <v>22.5</v>
+        <v>20.89</v>
       </c>
       <c r="F557">
-        <v>1.63</v>
+        <v>4.35</v>
       </c>
       <c r="G557" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -17029,24 +16717,24 @@
         </is>
       </c>
       <c r="E558">
-        <v>87.14</v>
+        <v>71.91</v>
       </c>
       <c r="F558">
-        <v>7.39</v>
+        <v>-7.06</v>
       </c>
       <c r="G558" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -17060,24 +16748,24 @@
         </is>
       </c>
       <c r="E559">
-        <v>56.91</v>
+        <v>44.91</v>
       </c>
       <c r="F559">
-        <v>18.79</v>
+        <v>-15.99</v>
       </c>
       <c r="G559" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -17091,24 +16779,24 @@
         </is>
       </c>
       <c r="E560">
-        <v>6.58</v>
+        <v>6.36</v>
       </c>
       <c r="F560">
-        <v>-6.4</v>
+        <v>10.99</v>
       </c>
       <c r="G560" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -17121,19 +16809,25 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E561">
+        <v>18.57</v>
+      </c>
+      <c r="F561">
+        <v>-2.88</v>
+      </c>
       <c r="G561" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -17146,19 +16840,25 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E562">
+        <v>13.17</v>
+      </c>
+      <c r="F562">
+        <v>2.33</v>
+      </c>
       <c r="G562" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -17171,19 +16871,25 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E563">
+        <v>5.99</v>
+      </c>
+      <c r="F563">
+        <v>-9.1</v>
+      </c>
       <c r="G563" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -17196,19 +16902,25 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E564">
+        <v>23.61</v>
+      </c>
+      <c r="F564">
+        <v>-39.37</v>
+      </c>
       <c r="G564" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -17221,19 +16933,25 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E565">
+        <v>12.26</v>
+      </c>
+      <c r="F565">
+        <v>1.32</v>
+      </c>
       <c r="G565" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -17246,19 +16964,25 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E566">
+        <v>274.33</v>
+      </c>
+      <c r="F566">
+        <v>-2.86</v>
+      </c>
       <c r="G566" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -17271,19 +16995,25 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E567">
+        <v>6.17</v>
+      </c>
+      <c r="F567">
+        <v>-1.28</v>
+      </c>
       <c r="G567" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -17296,19 +17026,25 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E568">
+        <v>33.66</v>
+      </c>
+      <c r="F568">
+        <v>-4.89</v>
+      </c>
       <c r="G568" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -17321,19 +17057,25 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E569">
+        <v>35.18</v>
+      </c>
+      <c r="F569">
+        <v>3.9</v>
+      </c>
       <c r="G569" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -17346,19 +17088,25 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E570">
+        <v>21.11</v>
+      </c>
+      <c r="F570">
+        <v>1.05</v>
+      </c>
       <c r="G570" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -17371,19 +17119,25 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E571">
+        <v>80.37</v>
+      </c>
+      <c r="F571">
+        <v>11.76</v>
+      </c>
       <c r="G571" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -17396,33 +17150,2879 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E572">
+        <v>34.11</v>
+      </c>
+      <c r="F572">
+        <v>-24.05</v>
+      </c>
       <c r="G572" s="2">
-        <v>45748</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E573">
+        <v>6.83</v>
+      </c>
+      <c r="F573">
+        <v>7.39</v>
+      </c>
+      <c r="G573" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E574">
+        <v>17.9</v>
+      </c>
+      <c r="F574">
+        <v>-3.61</v>
+      </c>
+      <c r="G574" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E575">
+        <v>14.58</v>
+      </c>
+      <c r="F575">
+        <v>10.71</v>
+      </c>
+      <c r="G575" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E576">
+        <v>6.39</v>
+      </c>
+      <c r="F576">
+        <v>6.68</v>
+      </c>
+      <c r="G576" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E577">
+        <v>22.94</v>
+      </c>
+      <c r="F577">
+        <v>-2.84</v>
+      </c>
+      <c r="G577" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E578">
+        <v>13.82</v>
+      </c>
+      <c r="F578">
+        <v>12.72</v>
+      </c>
+      <c r="G578" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E579">
+        <v>295.28</v>
+      </c>
+      <c r="F579">
+        <v>7.64</v>
+      </c>
+      <c r="G579" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E580">
+        <v>5.46</v>
+      </c>
+      <c r="F580">
+        <v>-11.51</v>
+      </c>
+      <c r="G580" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E581">
+        <v>30.81</v>
+      </c>
+      <c r="F581">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="G581" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E582">
+        <v>33.42</v>
+      </c>
+      <c r="F582">
+        <v>-5</v>
+      </c>
+      <c r="G582" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E583">
+        <v>21.88</v>
+      </c>
+      <c r="F583">
+        <v>3.65</v>
+      </c>
+      <c r="G583" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E584">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="F584">
+        <v>1.73</v>
+      </c>
+      <c r="G584" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E585">
+        <v>33.81</v>
+      </c>
+      <c r="F585">
+        <v>-0.88</v>
+      </c>
+      <c r="G585" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E586">
+        <v>7.19</v>
+      </c>
+      <c r="F586">
+        <v>5.27</v>
+      </c>
+      <c r="G586" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E587">
+        <v>18.09</v>
+      </c>
+      <c r="F587">
+        <v>1.06</v>
+      </c>
+      <c r="G587" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E588">
+        <v>14.43</v>
+      </c>
+      <c r="F588">
+        <v>-1.03</v>
+      </c>
+      <c r="G588" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E589">
+        <v>6.35</v>
+      </c>
+      <c r="F589">
+        <v>-0.63</v>
+      </c>
+      <c r="G589" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E590">
+        <v>22.94</v>
+      </c>
+      <c r="F590">
+        <v>0</v>
+      </c>
+      <c r="G590" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E591">
+        <v>16.25</v>
+      </c>
+      <c r="F591">
+        <v>17.58</v>
+      </c>
+      <c r="G591" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E592">
+        <v>302.48</v>
+      </c>
+      <c r="F592">
+        <v>2.44</v>
+      </c>
+      <c r="G592" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E593">
+        <v>5.76</v>
+      </c>
+      <c r="F593">
+        <v>5.49</v>
+      </c>
+      <c r="G593" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E594">
+        <v>32.38</v>
+      </c>
+      <c r="F594">
+        <v>5.1</v>
+      </c>
+      <c r="G594" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E595">
+        <v>33.42</v>
+      </c>
+      <c r="F595">
+        <v>0</v>
+      </c>
+      <c r="G595" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E596">
+        <v>22.14</v>
+      </c>
+      <c r="F596">
+        <v>1.19</v>
+      </c>
+      <c r="G596" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E597">
+        <v>81.14</v>
+      </c>
+      <c r="F597">
+        <v>-0.76</v>
+      </c>
+      <c r="G597" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E598">
+        <v>47.91</v>
+      </c>
+      <c r="F598">
+        <v>41.7</v>
+      </c>
+      <c r="G598" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E599">
+        <v>7.03</v>
+      </c>
+      <c r="F599">
+        <v>-2.23</v>
+      </c>
+      <c r="G599" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E600">
+        <v>16.67</v>
+      </c>
+      <c r="F600">
+        <v>-7.85</v>
+      </c>
+      <c r="G600" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E601">
+        <v>13.87</v>
+      </c>
+      <c r="F601">
+        <v>-3.88</v>
+      </c>
+      <c r="G601" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E602">
+        <v>4.47</v>
+      </c>
+      <c r="F602">
+        <v>-29.61</v>
+      </c>
+      <c r="G602" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E603">
+        <v>17.54</v>
+      </c>
+      <c r="F603">
+        <v>-23.54</v>
+      </c>
+      <c r="G603" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E604">
+        <v>16.73</v>
+      </c>
+      <c r="F604">
+        <v>2.95</v>
+      </c>
+      <c r="G604" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E605">
+        <v>306.06</v>
+      </c>
+      <c r="F605">
+        <v>1.18</v>
+      </c>
+      <c r="G605" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E606">
+        <v>6.16</v>
+      </c>
+      <c r="F606">
+        <v>6.94</v>
+      </c>
+      <c r="G606" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E607">
+        <v>26.22</v>
+      </c>
+      <c r="F607">
+        <v>-19.02</v>
+      </c>
+      <c r="G607" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E608">
+        <v>35.12</v>
+      </c>
+      <c r="F608">
+        <v>5.09</v>
+      </c>
+      <c r="G608" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E609">
+        <v>22.5</v>
+      </c>
+      <c r="F609">
+        <v>1.63</v>
+      </c>
+      <c r="G609" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E610">
+        <v>87.14</v>
+      </c>
+      <c r="F610">
+        <v>7.39</v>
+      </c>
+      <c r="G610" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E611">
+        <v>56.91</v>
+      </c>
+      <c r="F611">
+        <v>18.79</v>
+      </c>
+      <c r="G611" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E612">
+        <v>6.58</v>
+      </c>
+      <c r="F612">
+        <v>-6.4</v>
+      </c>
+      <c r="G612" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>Gaspar</t>
-        </is>
-      </c>
-      <c r="D573" t="inlineStr">
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G613" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G614" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G615" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G616" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G617" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G618" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G619" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G620" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G621" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G622" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G623" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G624" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="G573" s="2">
+      <c r="G625" s="2">
         <v>45748</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G626" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G627" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G628" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G629" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G630" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G631" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G632" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G633" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G634" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G635" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G636" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G637" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G638" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G639" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G640" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G641" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G642" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G643" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G644" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G645" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G646" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G647" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G648" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G649" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G650" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G651" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G652" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G653" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G654" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G655" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G656" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G657" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G658" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G659" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G660" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G661" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G662" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G663" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G664" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G665" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G666" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G667" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G668" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G669" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G670" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G671" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G672" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G673" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G674" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G675" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G676" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G677" s="2">
+        <v>45870</v>
       </c>
     </row>
   </sheetData>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -1836,12 +1836,6 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E54">
-        <v>13.26</v>
-      </c>
-      <c r="F54">
-        <v>-2.57</v>
-      </c>
       <c r="G54" s="2">
         <v>45047</v>
       </c>
@@ -1867,12 +1861,6 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E55">
-        <v>11.91</v>
-      </c>
-      <c r="F55">
-        <v>-4.64</v>
-      </c>
       <c r="G55" s="2">
         <v>45047</v>
       </c>
@@ -1948,12 +1936,6 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E58">
-        <v>8.69</v>
-      </c>
-      <c r="F58">
-        <v>-2.25</v>
-      </c>
       <c r="G58" s="2">
         <v>45047</v>
       </c>
@@ -2004,12 +1986,6 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E60">
-        <v>5.58</v>
-      </c>
-      <c r="F60">
-        <v>-15.07</v>
-      </c>
       <c r="G60" s="2">
         <v>45047</v>
       </c>
@@ -2188,9 +2164,6 @@
       <c r="E67">
         <v>13.85</v>
       </c>
-      <c r="F67">
-        <v>4.45</v>
-      </c>
       <c r="G67" s="2">
         <v>45078</v>
       </c>
@@ -2219,9 +2192,6 @@
       <c r="E68">
         <v>12.59</v>
       </c>
-      <c r="F68">
-        <v>5.71</v>
-      </c>
       <c r="G68" s="2">
         <v>45078</v>
       </c>
@@ -2306,9 +2276,6 @@
       <c r="E71">
         <v>8.84</v>
       </c>
-      <c r="F71">
-        <v>1.73</v>
-      </c>
       <c r="G71" s="2">
         <v>45078</v>
       </c>
@@ -2365,9 +2332,6 @@
       <c r="E73">
         <v>7.11</v>
       </c>
-      <c r="F73">
-        <v>27.42</v>
-      </c>
       <c r="G73" s="2">
         <v>45078</v>
       </c>
@@ -5382,6 +5346,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E171">
+        <v>14.55</v>
+      </c>
+      <c r="F171">
+        <v>-11.66</v>
+      </c>
       <c r="G171" s="2">
         <v>45323</v>
       </c>
@@ -5407,6 +5377,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E172">
+        <v>10.89</v>
+      </c>
+      <c r="F172">
+        <v>-30.99</v>
+      </c>
       <c r="G172" s="2">
         <v>45323</v>
       </c>
@@ -5432,6 +5408,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E173">
+        <v>5.23</v>
+      </c>
+      <c r="F173">
+        <v>26.33</v>
+      </c>
       <c r="G173" s="2">
         <v>45323</v>
       </c>
@@ -5457,6 +5439,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E174">
+        <v>33.9</v>
+      </c>
+      <c r="F174">
+        <v>7.82</v>
+      </c>
       <c r="G174" s="2">
         <v>45323</v>
       </c>
@@ -5482,6 +5470,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E175">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="F175">
+        <v>-4.17</v>
+      </c>
       <c r="G175" s="2">
         <v>45323</v>
       </c>
@@ -5507,6 +5501,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E176">
+        <v>224.73</v>
+      </c>
+      <c r="F176">
+        <v>4.8</v>
+      </c>
       <c r="G176" s="2">
         <v>45323</v>
       </c>
@@ -5532,6 +5532,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E177">
+        <v>6.23</v>
+      </c>
+      <c r="F177">
+        <v>-19.51</v>
+      </c>
       <c r="G177" s="2">
         <v>45323</v>
       </c>
@@ -5557,6 +5563,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E178">
+        <v>32.58</v>
+      </c>
+      <c r="F178">
+        <v>12.62</v>
+      </c>
       <c r="G178" s="2">
         <v>45323</v>
       </c>
@@ -5582,6 +5594,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E179">
+        <v>38.77</v>
+      </c>
+      <c r="F179">
+        <v>26.7</v>
+      </c>
       <c r="G179" s="2">
         <v>45323</v>
       </c>
@@ -5607,6 +5625,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E180">
+        <v>21.47</v>
+      </c>
+      <c r="F180">
+        <v>0.8</v>
+      </c>
       <c r="G180" s="2">
         <v>45323</v>
       </c>
@@ -5632,6 +5656,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E181">
+        <v>79.5</v>
+      </c>
+      <c r="F181">
+        <v>7.81</v>
+      </c>
       <c r="G181" s="2">
         <v>45323</v>
       </c>
@@ -5657,6 +5687,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E182">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="F182">
+        <v>8.25</v>
+      </c>
       <c r="G182" s="2">
         <v>45323</v>
       </c>
@@ -5682,6 +5718,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E183">
+        <v>6.91</v>
+      </c>
+      <c r="F183">
+        <v>10.56</v>
+      </c>
       <c r="G183" s="2">
         <v>45323</v>
       </c>
@@ -5710,6 +5752,9 @@
       <c r="E184">
         <v>13.89</v>
       </c>
+      <c r="F184">
+        <v>-4.54</v>
+      </c>
       <c r="G184" s="2">
         <v>45352</v>
       </c>
@@ -5738,6 +5783,9 @@
       <c r="E185">
         <v>12.42</v>
       </c>
+      <c r="F185">
+        <v>14.05</v>
+      </c>
       <c r="G185" s="2">
         <v>45352</v>
       </c>
@@ -5766,6 +5814,9 @@
       <c r="E186">
         <v>4.38</v>
       </c>
+      <c r="F186">
+        <v>-16.25</v>
+      </c>
       <c r="G186" s="2">
         <v>45352</v>
       </c>
@@ -5794,6 +5845,9 @@
       <c r="E187">
         <v>28.14</v>
       </c>
+      <c r="F187">
+        <v>-16.99</v>
+      </c>
       <c r="G187" s="2">
         <v>45352</v>
       </c>
@@ -5822,6 +5876,9 @@
       <c r="E188">
         <v>7.58</v>
       </c>
+      <c r="F188">
+        <v>-5.72</v>
+      </c>
       <c r="G188" s="2">
         <v>45352</v>
       </c>
@@ -5850,6 +5907,9 @@
       <c r="E189">
         <v>217.01</v>
       </c>
+      <c r="F189">
+        <v>-3.44</v>
+      </c>
       <c r="G189" s="2">
         <v>45352</v>
       </c>
@@ -5878,6 +5938,9 @@
       <c r="E190">
         <v>6.4</v>
       </c>
+      <c r="F190">
+        <v>2.73</v>
+      </c>
       <c r="G190" s="2">
         <v>45352</v>
       </c>
@@ -5906,6 +5969,9 @@
       <c r="E191">
         <v>27.9</v>
       </c>
+      <c r="F191">
+        <v>-14.36</v>
+      </c>
       <c r="G191" s="2">
         <v>45352</v>
       </c>
@@ -5934,6 +6000,9 @@
       <c r="E192">
         <v>34.05</v>
       </c>
+      <c r="F192">
+        <v>-12.17</v>
+      </c>
       <c r="G192" s="2">
         <v>45352</v>
       </c>
@@ -5962,6 +6031,9 @@
       <c r="E193">
         <v>20</v>
       </c>
+      <c r="F193">
+        <v>-6.85</v>
+      </c>
       <c r="G193" s="2">
         <v>45352</v>
       </c>
@@ -5990,6 +6062,9 @@
       <c r="E194">
         <v>75.3</v>
       </c>
+      <c r="F194">
+        <v>-5.28</v>
+      </c>
       <c r="G194" s="2">
         <v>45352</v>
       </c>
@@ -6018,6 +6093,9 @@
       <c r="E195">
         <v>62.01</v>
       </c>
+      <c r="F195">
+        <v>-6.26</v>
+      </c>
       <c r="G195" s="2">
         <v>45352</v>
       </c>
@@ -6046,6 +6124,9 @@
       <c r="E196">
         <v>4.95</v>
       </c>
+      <c r="F196">
+        <v>-28.36</v>
+      </c>
       <c r="G196" s="2">
         <v>45352</v>
       </c>
@@ -11193,6 +11274,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E366">
+        <v>15.44</v>
+      </c>
+      <c r="F366">
+        <v>3.35</v>
+      </c>
       <c r="G366" s="2">
         <v>45778</v>
       </c>
@@ -11218,6 +11305,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E367">
+        <v>13.21</v>
+      </c>
+      <c r="F367">
+        <v>-5.91</v>
+      </c>
       <c r="G367" s="2">
         <v>45778</v>
       </c>
@@ -11243,6 +11336,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E368">
+        <v>5.18</v>
+      </c>
+      <c r="F368">
+        <v>4.44</v>
+      </c>
       <c r="G368" s="2">
         <v>45778</v>
       </c>
@@ -11268,6 +11367,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E369">
+        <v>30.59</v>
+      </c>
+      <c r="F369">
+        <v>11.2</v>
+      </c>
       <c r="G369" s="2">
         <v>45778</v>
       </c>
@@ -11293,6 +11398,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E370">
+        <v>20.4</v>
+      </c>
+      <c r="F370">
+        <v>0.25</v>
+      </c>
       <c r="G370" s="2">
         <v>45778</v>
       </c>
@@ -11318,6 +11429,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E371">
+        <v>299.02</v>
+      </c>
+      <c r="F371">
+        <v>-10.7</v>
+      </c>
       <c r="G371" s="2">
         <v>45778</v>
       </c>
@@ -11343,6 +11460,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E372">
+        <v>5.91</v>
+      </c>
+      <c r="F372">
+        <v>3.5</v>
+      </c>
       <c r="G372" s="2">
         <v>45778</v>
       </c>
@@ -11368,6 +11491,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E373">
+        <v>31.72</v>
+      </c>
+      <c r="F373">
+        <v>7.05</v>
+      </c>
       <c r="G373" s="2">
         <v>45778</v>
       </c>
@@ -11393,6 +11522,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E374">
+        <v>37.96</v>
+      </c>
+      <c r="F374">
+        <v>4.26</v>
+      </c>
       <c r="G374" s="2">
         <v>45778</v>
       </c>
@@ -11418,6 +11553,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E375">
+        <v>24.56</v>
+      </c>
+      <c r="F375">
+        <v>1.4</v>
+      </c>
       <c r="G375" s="2">
         <v>45778</v>
       </c>
@@ -11443,6 +11584,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E376">
+        <v>93.22</v>
+      </c>
+      <c r="F376">
+        <v>-1.04</v>
+      </c>
       <c r="G376" s="2">
         <v>45778</v>
       </c>
@@ -11468,6 +11615,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E377">
+        <v>68.27</v>
+      </c>
+      <c r="F377">
+        <v>1.34</v>
+      </c>
       <c r="G377" s="2">
         <v>45778</v>
       </c>
@@ -11493,6 +11646,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E378">
+        <v>6.66</v>
+      </c>
+      <c r="F378">
+        <v>2.94</v>
+      </c>
       <c r="G378" s="2">
         <v>45778</v>
       </c>
@@ -11518,6 +11677,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E379">
+        <v>14.63</v>
+      </c>
+      <c r="F379">
+        <v>-5.25</v>
+      </c>
       <c r="G379" s="2">
         <v>45809</v>
       </c>
@@ -11543,6 +11708,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E380">
+        <v>13.21</v>
+      </c>
+      <c r="F380">
+        <v>0</v>
+      </c>
       <c r="G380" s="2">
         <v>45809</v>
       </c>
@@ -11568,6 +11739,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E381">
+        <v>5.54</v>
+      </c>
+      <c r="F381">
+        <v>6.95</v>
+      </c>
       <c r="G381" s="2">
         <v>45809</v>
       </c>
@@ -11593,6 +11770,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E382">
+        <v>36.87</v>
+      </c>
+      <c r="F382">
+        <v>20.53</v>
+      </c>
       <c r="G382" s="2">
         <v>45809</v>
       </c>
@@ -11618,6 +11801,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E383">
+        <v>17.61</v>
+      </c>
+      <c r="F383">
+        <v>-13.68</v>
+      </c>
       <c r="G383" s="2">
         <v>45809</v>
       </c>
@@ -11643,6 +11832,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E384">
+        <v>301.12</v>
+      </c>
+      <c r="F384">
+        <v>0.7</v>
+      </c>
       <c r="G384" s="2">
         <v>45809</v>
       </c>
@@ -11668,6 +11863,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E385">
+        <v>5.65</v>
+      </c>
+      <c r="F385">
+        <v>-4.4</v>
+      </c>
       <c r="G385" s="2">
         <v>45809</v>
       </c>
@@ -11693,6 +11894,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E386">
+        <v>27.59</v>
+      </c>
+      <c r="F386">
+        <v>-13.02</v>
+      </c>
       <c r="G386" s="2">
         <v>45809</v>
       </c>
@@ -11718,6 +11925,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E387">
+        <v>37.05</v>
+      </c>
+      <c r="F387">
+        <v>-2.4</v>
+      </c>
       <c r="G387" s="2">
         <v>45809</v>
       </c>
@@ -11743,6 +11956,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E388">
+        <v>24.1</v>
+      </c>
+      <c r="F388">
+        <v>-1.87</v>
+      </c>
       <c r="G388" s="2">
         <v>45809</v>
       </c>
@@ -11768,6 +11987,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E389">
+        <v>90.61</v>
+      </c>
+      <c r="F389">
+        <v>-2.8</v>
+      </c>
       <c r="G389" s="2">
         <v>45809</v>
       </c>
@@ -11793,6 +12018,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E390">
+        <v>83.98</v>
+      </c>
+      <c r="F390">
+        <v>23.01</v>
+      </c>
       <c r="G390" s="2">
         <v>45809</v>
       </c>
@@ -11818,6 +12049,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E391">
+        <v>6.58</v>
+      </c>
+      <c r="F391">
+        <v>-1.2</v>
+      </c>
       <c r="G391" s="2">
         <v>45809</v>
       </c>
@@ -11843,6 +12080,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E392">
+        <v>11.45</v>
+      </c>
+      <c r="F392">
+        <v>-21.74</v>
+      </c>
       <c r="G392" s="2">
         <v>45839</v>
       </c>
@@ -11868,6 +12111,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E393">
+        <v>13.38</v>
+      </c>
+      <c r="F393">
+        <v>1.29</v>
+      </c>
       <c r="G393" s="2">
         <v>45839</v>
       </c>
@@ -11893,6 +12142,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E394">
+        <v>4.45</v>
+      </c>
+      <c r="F394">
+        <v>-19.68</v>
+      </c>
       <c r="G394" s="2">
         <v>45839</v>
       </c>
@@ -11918,6 +12173,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E395">
+        <v>39.41</v>
+      </c>
+      <c r="F395">
+        <v>6.89</v>
+      </c>
       <c r="G395" s="2">
         <v>45839</v>
       </c>
@@ -11943,6 +12204,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E396">
+        <v>18.06</v>
+      </c>
+      <c r="F396">
+        <v>2.56</v>
+      </c>
       <c r="G396" s="2">
         <v>45839</v>
       </c>
@@ -11968,6 +12235,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E397">
+        <v>316.5</v>
+      </c>
+      <c r="F397">
+        <v>5.11</v>
+      </c>
       <c r="G397" s="2">
         <v>45839</v>
       </c>
@@ -11993,6 +12266,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E398">
+        <v>5.89</v>
+      </c>
+      <c r="F398">
+        <v>4.25</v>
+      </c>
       <c r="G398" s="2">
         <v>45839</v>
       </c>
@@ -12018,6 +12297,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E399">
+        <v>24.53</v>
+      </c>
+      <c r="F399">
+        <v>-11.09</v>
+      </c>
       <c r="G399" s="2">
         <v>45839</v>
       </c>
@@ -12043,6 +12328,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E400">
+        <v>34.65</v>
+      </c>
+      <c r="F400">
+        <v>-6.48</v>
+      </c>
       <c r="G400" s="2">
         <v>45839</v>
       </c>
@@ -12068,6 +12359,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E401">
+        <v>22.77</v>
+      </c>
+      <c r="F401">
+        <v>-5.52</v>
+      </c>
       <c r="G401" s="2">
         <v>45839</v>
       </c>
@@ -12093,6 +12390,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E402">
+        <v>94.12</v>
+      </c>
+      <c r="F402">
+        <v>3.87</v>
+      </c>
       <c r="G402" s="2">
         <v>45839</v>
       </c>
@@ -12118,6 +12421,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E403">
+        <v>90.7</v>
+      </c>
+      <c r="F403">
+        <v>8</v>
+      </c>
       <c r="G403" s="2">
         <v>45839</v>
       </c>
@@ -12143,6 +12452,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E404">
+        <v>6.27</v>
+      </c>
+      <c r="F404">
+        <v>-4.71</v>
+      </c>
       <c r="G404" s="2">
         <v>45839</v>
       </c>
@@ -12168,6 +12483,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E405">
+        <v>11.22</v>
+      </c>
+      <c r="F405">
+        <v>-2.01</v>
+      </c>
       <c r="G405" s="2">
         <v>45870</v>
       </c>
@@ -12193,6 +12514,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E406">
+        <v>13.41</v>
+      </c>
+      <c r="F406">
+        <v>0.22</v>
+      </c>
       <c r="G406" s="2">
         <v>45870</v>
       </c>
@@ -12218,6 +12545,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E407">
+        <v>4.76</v>
+      </c>
+      <c r="F407">
+        <v>6.97</v>
+      </c>
       <c r="G407" s="2">
         <v>45870</v>
       </c>
@@ -12243,6 +12576,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E408">
+        <v>46.5</v>
+      </c>
+      <c r="F408">
+        <v>17.99</v>
+      </c>
       <c r="G408" s="2">
         <v>45870</v>
       </c>
@@ -12268,6 +12607,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E409">
+        <v>16.78</v>
+      </c>
+      <c r="F409">
+        <v>-7.09</v>
+      </c>
       <c r="G409" s="2">
         <v>45870</v>
       </c>
@@ -12293,6 +12638,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E410">
+        <v>300.7</v>
+      </c>
+      <c r="F410">
+        <v>-4.99</v>
+      </c>
       <c r="G410" s="2">
         <v>45870</v>
       </c>
@@ -12318,6 +12669,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E411">
+        <v>5.96</v>
+      </c>
+      <c r="F411">
+        <v>1.19</v>
+      </c>
       <c r="G411" s="2">
         <v>45870</v>
       </c>
@@ -12343,6 +12700,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E412">
+        <v>23.76</v>
+      </c>
+      <c r="F412">
+        <v>-3.14</v>
+      </c>
       <c r="G412" s="2">
         <v>45870</v>
       </c>
@@ -12368,6 +12731,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E413">
+        <v>33.52</v>
+      </c>
+      <c r="F413">
+        <v>-3.26</v>
+      </c>
       <c r="G413" s="2">
         <v>45870</v>
       </c>
@@ -12393,6 +12762,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E414">
+        <v>21.82</v>
+      </c>
+      <c r="F414">
+        <v>-4.17</v>
+      </c>
       <c r="G414" s="2">
         <v>45870</v>
       </c>
@@ -12418,6 +12793,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E415">
+        <v>95.58</v>
+      </c>
+      <c r="F415">
+        <v>1.55</v>
+      </c>
       <c r="G415" s="2">
         <v>45870</v>
       </c>
@@ -12443,6 +12824,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E416">
+        <v>89.73</v>
+      </c>
+      <c r="F416">
+        <v>-1.07</v>
+      </c>
       <c r="G416" s="2">
         <v>45870</v>
       </c>
@@ -12467,6 +12854,12 @@
         <is>
           <t>Óleo de Soja</t>
         </is>
+      </c>
+      <c r="E417">
+        <v>6.2</v>
+      </c>
+      <c r="F417">
+        <v>-1.12</v>
       </c>
       <c r="G417" s="2">
         <v>45870</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="E41">
-        <v>13.61</v>
+        <v>13.63</v>
       </c>
       <c r="F41">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
       <c r="G41" s="2">
         <v>45017</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="E42">
-        <v>12.49</v>
+        <v>12.73</v>
       </c>
       <c r="F42">
-        <v>-0.72</v>
+        <v>1.19</v>
       </c>
       <c r="G42" s="2">
         <v>45017</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="E43">
-        <v>4.93</v>
+        <v>4.58</v>
       </c>
       <c r="F43">
-        <v>-16.72</v>
+        <v>-22.64</v>
       </c>
       <c r="G43" s="2">
         <v>45017</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="E44">
-        <v>25.11</v>
+        <v>25.52</v>
       </c>
       <c r="F44">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="G44" s="2">
         <v>45017</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="E45">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F45">
-        <v>-10.47</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="G45" s="2">
         <v>45017</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="E46">
-        <v>242.55</v>
+        <v>245.76</v>
       </c>
       <c r="F46">
-        <v>5.33</v>
+        <v>6.73</v>
       </c>
       <c r="G46" s="2">
         <v>45017</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="E47">
-        <v>6.57</v>
+        <v>6.89</v>
       </c>
       <c r="F47">
-        <v>-4.92</v>
+        <v>-0.29</v>
       </c>
       <c r="G47" s="2">
         <v>45017</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="E48">
-        <v>34.64</v>
+        <v>35.1</v>
       </c>
       <c r="F48">
-        <v>2.79</v>
+        <v>4.15</v>
       </c>
       <c r="G48" s="2">
         <v>45017</v>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="E49">
-        <v>34.99</v>
+        <v>34.92</v>
       </c>
       <c r="F49">
-        <v>-1.88</v>
+        <v>-2.08</v>
       </c>
       <c r="G49" s="2">
         <v>45017</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="E50">
-        <v>17.66</v>
+        <v>18.05</v>
       </c>
       <c r="F50">
-        <v>-8.449999999999999</v>
+        <v>-6.43</v>
       </c>
       <c r="G50" s="2">
         <v>45017</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="E51">
-        <v>68.2</v>
+        <v>67.14</v>
       </c>
       <c r="F51">
-        <v>-8.66</v>
+        <v>-10.08</v>
       </c>
       <c r="G51" s="2">
         <v>45017</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="E52">
-        <v>58.82</v>
+        <v>57.48</v>
       </c>
       <c r="F52">
-        <v>-2.24</v>
+        <v>-4.47</v>
       </c>
       <c r="G52" s="2">
         <v>45017</v>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="E53">
-        <v>6.71</v>
+        <v>6.74</v>
       </c>
       <c r="F53">
-        <v>-4.28</v>
+        <v>-3.85</v>
       </c>
       <c r="G53" s="2">
         <v>45017</v>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="E80">
-        <v>13.76</v>
+        <v>14.05</v>
       </c>
       <c r="F80">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G80" s="2">
         <v>45108</v>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E81">
-        <v>12.62</v>
+        <v>12.69</v>
       </c>
       <c r="F81">
-        <v>0.24</v>
+        <v>0.79</v>
       </c>
       <c r="G81" s="2">
         <v>45108</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="E82">
-        <v>4.78</v>
+        <v>4.18</v>
       </c>
       <c r="F82">
-        <v>-1.04</v>
+        <v>-13.46</v>
       </c>
       <c r="G82" s="2">
         <v>45108</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="E83">
-        <v>34.7</v>
+        <v>34.11</v>
       </c>
       <c r="F83">
-        <v>11.15</v>
+        <v>9.26</v>
       </c>
       <c r="G83" s="2">
         <v>45108</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="E84">
-        <v>8.380000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="F84">
-        <v>-5.2</v>
+        <v>-9.73</v>
       </c>
       <c r="G84" s="2">
         <v>45108</v>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="E85">
-        <v>231.75</v>
+        <v>223.61</v>
       </c>
       <c r="F85">
-        <v>-4.13</v>
+        <v>-7.5</v>
       </c>
       <c r="G85" s="2">
         <v>45108</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="E86">
-        <v>6.3</v>
+        <v>6.54</v>
       </c>
       <c r="F86">
-        <v>-11.39</v>
+        <v>-8.02</v>
       </c>
       <c r="G86" s="2">
         <v>45108</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="E87">
-        <v>30.9</v>
+        <v>29.95</v>
       </c>
       <c r="F87">
-        <v>-13.01</v>
+        <v>-15.68</v>
       </c>
       <c r="G87" s="2">
         <v>45108</v>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="E88">
-        <v>33.27</v>
+        <v>33.45</v>
       </c>
       <c r="F88">
-        <v>-6.1</v>
+        <v>-5.59</v>
       </c>
       <c r="G88" s="2">
         <v>45108</v>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="E89">
-        <v>20.82</v>
+        <v>21.37</v>
       </c>
       <c r="F89">
-        <v>32.19</v>
+        <v>35.68</v>
       </c>
       <c r="G89" s="2">
         <v>45108</v>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="E90">
-        <v>75.54000000000001</v>
+        <v>74.61</v>
       </c>
       <c r="F90">
-        <v>-0.89</v>
+        <v>-2.11</v>
       </c>
       <c r="G90" s="2">
         <v>45108</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="E91">
-        <v>70.31999999999999</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="F91">
-        <v>-1.22</v>
+        <v>-8.6</v>
       </c>
       <c r="G91" s="2">
         <v>45108</v>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="E92">
-        <v>4.79</v>
+        <v>4.64</v>
       </c>
       <c r="F92">
-        <v>-20.3</v>
+        <v>-22.8</v>
       </c>
       <c r="G92" s="2">
         <v>45108</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="E93">
-        <v>13.55</v>
+        <v>13.74</v>
       </c>
       <c r="F93">
-        <v>-1.53</v>
+        <v>-2.21</v>
       </c>
       <c r="G93" s="2">
         <v>45139</v>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="E94">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="F94">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="G94" s="2">
         <v>45139</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="E95">
-        <v>5.02</v>
+        <v>4.54</v>
       </c>
       <c r="F95">
-        <v>5.02</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G95" s="2">
         <v>45139</v>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="E96">
-        <v>26.9</v>
+        <v>25.41</v>
       </c>
       <c r="F96">
-        <v>-22.48</v>
+        <v>-25.51</v>
       </c>
       <c r="G96" s="2">
         <v>45139</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="E97">
-        <v>8.369999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F97">
-        <v>-0.12</v>
+        <v>6.02</v>
       </c>
       <c r="G97" s="2">
         <v>45139</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="E98">
-        <v>225.04</v>
+        <v>233.38</v>
       </c>
       <c r="F98">
-        <v>-2.9</v>
+        <v>4.37</v>
       </c>
       <c r="G98" s="2">
         <v>45139</v>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="E99">
-        <v>5.74</v>
+        <v>5.77</v>
       </c>
       <c r="F99">
-        <v>-8.890000000000001</v>
+        <v>-11.77</v>
       </c>
       <c r="G99" s="2">
         <v>45139</v>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="E100">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="F100">
-        <v>-0.19</v>
+        <v>0.67</v>
       </c>
       <c r="G100" s="2">
         <v>45139</v>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="E101">
-        <v>31.18</v>
+        <v>31.69</v>
       </c>
       <c r="F101">
-        <v>-6.28</v>
+        <v>-5.26</v>
       </c>
       <c r="G101" s="2">
         <v>45139</v>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="E102">
-        <v>20.17</v>
+        <v>20.42</v>
       </c>
       <c r="F102">
-        <v>-3.12</v>
+        <v>-4.45</v>
       </c>
       <c r="G102" s="2">
         <v>45139</v>
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="E103">
-        <v>76.94</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="F103">
-        <v>1.85</v>
+        <v>2.81</v>
       </c>
       <c r="G103" s="2">
         <v>45139</v>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="E104">
-        <v>67.2</v>
+        <v>55.89</v>
       </c>
       <c r="F104">
-        <v>-4.44</v>
+        <v>-14.11</v>
       </c>
       <c r="G104" s="2">
         <v>45139</v>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="E105">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="F105">
-        <v>-1.88</v>
+        <v>0.86</v>
       </c>
       <c r="G105" s="2">
         <v>45139</v>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="E106">
-        <v>14.73</v>
+        <v>13.89</v>
       </c>
       <c r="F106">
-        <v>8.710000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="G106" s="2">
         <v>45170</v>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="E107">
-        <v>12.99</v>
+        <v>12.42</v>
       </c>
       <c r="F107">
-        <v>0.7</v>
+        <v>-4.17</v>
       </c>
       <c r="G107" s="2">
         <v>45170</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="E108">
-        <v>5.18</v>
+        <v>4.38</v>
       </c>
       <c r="F108">
-        <v>3.19</v>
+        <v>-3.52</v>
       </c>
       <c r="G108" s="2">
         <v>45170</v>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="E109">
-        <v>28.11</v>
+        <v>28.14</v>
       </c>
       <c r="F109">
-        <v>4.5</v>
+        <v>10.74</v>
       </c>
       <c r="G109" s="2">
         <v>45170</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="E110">
-        <v>7.88</v>
+        <v>7.58</v>
       </c>
       <c r="F110">
-        <v>-5.85</v>
+        <v>-10.4</v>
       </c>
       <c r="G110" s="2">
         <v>45170</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="E111">
-        <v>213.77</v>
+        <v>219.19</v>
       </c>
       <c r="F111">
-        <v>-5.01</v>
+        <v>-6.08</v>
       </c>
       <c r="G111" s="2">
         <v>45170</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="E112">
-        <v>5.87</v>
+        <v>6.4</v>
       </c>
       <c r="F112">
-        <v>2.26</v>
+        <v>10.92</v>
       </c>
       <c r="G112" s="2">
         <v>45170</v>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="E113">
-        <v>30.2</v>
+        <v>27.9</v>
       </c>
       <c r="F113">
-        <v>-2.08</v>
+        <v>-7.46</v>
       </c>
       <c r="G113" s="2">
         <v>45170</v>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="E114">
-        <v>31.65</v>
+        <v>33.9</v>
       </c>
       <c r="F114">
-        <v>1.51</v>
+        <v>6.97</v>
       </c>
       <c r="G114" s="2">
         <v>45170</v>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="E115">
-        <v>20.08</v>
+        <v>20</v>
       </c>
       <c r="F115">
-        <v>-0.45</v>
+        <v>-2.06</v>
       </c>
       <c r="G115" s="2">
         <v>45170</v>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="E116">
-        <v>76.34999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="F116">
-        <v>-0.77</v>
+        <v>-1.84</v>
       </c>
       <c r="G116" s="2">
         <v>45170</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E117">
-        <v>62.42</v>
+        <v>62.01</v>
       </c>
       <c r="F117">
-        <v>-7.11</v>
+        <v>10.95</v>
       </c>
       <c r="G117" s="2">
         <v>45170</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="E118">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="F118">
-        <v>3.4</v>
+        <v>5.77</v>
       </c>
       <c r="G118" s="2">
         <v>45170</v>
@@ -3734,12 +3734,6 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E119">
-        <v>15.06</v>
-      </c>
-      <c r="F119">
-        <v>2.24</v>
-      </c>
       <c r="G119" s="2">
         <v>45200</v>
       </c>
@@ -3765,12 +3759,6 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E120">
-        <v>12.58</v>
-      </c>
-      <c r="F120">
-        <v>-3.16</v>
-      </c>
       <c r="G120" s="2">
         <v>45200</v>
       </c>
@@ -3796,12 +3784,6 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E121">
-        <v>5.18</v>
-      </c>
-      <c r="F121">
-        <v>0</v>
-      </c>
       <c r="G121" s="2">
         <v>45200</v>
       </c>
@@ -3827,12 +3809,6 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E122">
-        <v>28.9</v>
-      </c>
-      <c r="F122">
-        <v>2.81</v>
-      </c>
       <c r="G122" s="2">
         <v>45200</v>
       </c>
@@ -3858,12 +3834,6 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E123">
-        <v>8.09</v>
-      </c>
-      <c r="F123">
-        <v>2.66</v>
-      </c>
       <c r="G123" s="2">
         <v>45200</v>
       </c>
@@ -3889,12 +3859,6 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E124">
-        <v>230.38</v>
-      </c>
-      <c r="F124">
-        <v>7.77</v>
-      </c>
       <c r="G124" s="2">
         <v>45200</v>
       </c>
@@ -3920,12 +3884,6 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E125">
-        <v>5.49</v>
-      </c>
-      <c r="F125">
-        <v>-6.47</v>
-      </c>
       <c r="G125" s="2">
         <v>45200</v>
       </c>
@@ -3951,12 +3909,6 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E126">
-        <v>33.13</v>
-      </c>
-      <c r="F126">
-        <v>9.699999999999999</v>
-      </c>
       <c r="G126" s="2">
         <v>45200</v>
       </c>
@@ -3982,12 +3934,6 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E127">
-        <v>29.7</v>
-      </c>
-      <c r="F127">
-        <v>-6.16</v>
-      </c>
       <c r="G127" s="2">
         <v>45200</v>
       </c>
@@ -4013,12 +3959,6 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E128">
-        <v>17.95</v>
-      </c>
-      <c r="F128">
-        <v>-10.61</v>
-      </c>
       <c r="G128" s="2">
         <v>45200</v>
       </c>
@@ -4044,12 +3984,6 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E129">
-        <v>76.98</v>
-      </c>
-      <c r="F129">
-        <v>0.83</v>
-      </c>
       <c r="G129" s="2">
         <v>45200</v>
       </c>
@@ -4075,12 +4009,6 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E130">
-        <v>68.84999999999999</v>
-      </c>
-      <c r="F130">
-        <v>10.3</v>
-      </c>
       <c r="G130" s="2">
         <v>45200</v>
       </c>
@@ -4106,12 +4034,6 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E131">
-        <v>5.28</v>
-      </c>
-      <c r="F131">
-        <v>8.640000000000001</v>
-      </c>
       <c r="G131" s="2">
         <v>45200</v>
       </c>
@@ -4140,9 +4062,6 @@
       <c r="E132">
         <v>14.97</v>
       </c>
-      <c r="F132">
-        <v>-0.6</v>
-      </c>
       <c r="G132" s="2">
         <v>45231</v>
       </c>
@@ -4171,9 +4090,6 @@
       <c r="E133">
         <v>12.13</v>
       </c>
-      <c r="F133">
-        <v>-3.58</v>
-      </c>
       <c r="G133" s="2">
         <v>45231</v>
       </c>
@@ -4202,9 +4118,6 @@
       <c r="E134">
         <v>4.94</v>
       </c>
-      <c r="F134">
-        <v>-4.63</v>
-      </c>
       <c r="G134" s="2">
         <v>45231</v>
       </c>
@@ -4233,9 +4146,6 @@
       <c r="E135">
         <v>27.99</v>
       </c>
-      <c r="F135">
-        <v>-3.15</v>
-      </c>
       <c r="G135" s="2">
         <v>45231</v>
       </c>
@@ -4264,9 +4174,6 @@
       <c r="E136">
         <v>8.390000000000001</v>
       </c>
-      <c r="F136">
-        <v>3.71</v>
-      </c>
       <c r="G136" s="2">
         <v>45231</v>
       </c>
@@ -4295,9 +4202,6 @@
       <c r="E137">
         <v>242.62</v>
       </c>
-      <c r="F137">
-        <v>5.31</v>
-      </c>
       <c r="G137" s="2">
         <v>45231</v>
       </c>
@@ -4326,9 +4230,6 @@
       <c r="E138">
         <v>6</v>
       </c>
-      <c r="F138">
-        <v>9.289999999999999</v>
-      </c>
       <c r="G138" s="2">
         <v>45231</v>
       </c>
@@ -4357,9 +4258,6 @@
       <c r="E139">
         <v>34</v>
       </c>
-      <c r="F139">
-        <v>2.63</v>
-      </c>
       <c r="G139" s="2">
         <v>45231</v>
       </c>
@@ -4388,9 +4286,6 @@
       <c r="E140">
         <v>30.75</v>
       </c>
-      <c r="F140">
-        <v>3.54</v>
-      </c>
       <c r="G140" s="2">
         <v>45231</v>
       </c>
@@ -4419,9 +4314,6 @@
       <c r="E141">
         <v>20.18</v>
       </c>
-      <c r="F141">
-        <v>12.42</v>
-      </c>
       <c r="G141" s="2">
         <v>45231</v>
       </c>
@@ -4450,9 +4342,6 @@
       <c r="E142">
         <v>66.48</v>
       </c>
-      <c r="F142">
-        <v>-13.64</v>
-      </c>
       <c r="G142" s="2">
         <v>45231</v>
       </c>
@@ -4481,9 +4370,6 @@
       <c r="E143">
         <v>73.98</v>
       </c>
-      <c r="F143">
-        <v>7.45</v>
-      </c>
       <c r="G143" s="2">
         <v>45231</v>
       </c>
@@ -4512,9 +4398,6 @@
       <c r="E144">
         <v>5.14</v>
       </c>
-      <c r="F144">
-        <v>-2.65</v>
-      </c>
       <c r="G144" s="2">
         <v>45231</v>
       </c>
@@ -4541,10 +4424,10 @@
         </is>
       </c>
       <c r="E145">
-        <v>14.8</v>
+        <v>14.04</v>
       </c>
       <c r="F145">
-        <v>-1.14</v>
+        <v>-6.21</v>
       </c>
       <c r="G145" s="2">
         <v>45261</v>
@@ -4572,10 +4455,10 @@
         </is>
       </c>
       <c r="E146">
-        <v>13.99</v>
+        <v>13.92</v>
       </c>
       <c r="F146">
-        <v>15.33</v>
+        <v>14.76</v>
       </c>
       <c r="G146" s="2">
         <v>45261</v>
@@ -4603,10 +4486,10 @@
         </is>
       </c>
       <c r="E147">
-        <v>5.18</v>
+        <v>3.9</v>
       </c>
       <c r="F147">
-        <v>4.86</v>
+        <v>-21.05</v>
       </c>
       <c r="G147" s="2">
         <v>45261</v>
@@ -4634,10 +4517,10 @@
         </is>
       </c>
       <c r="E148">
-        <v>31.32</v>
+        <v>26.76</v>
       </c>
       <c r="F148">
-        <v>11.9</v>
+        <v>-4.39</v>
       </c>
       <c r="G148" s="2">
         <v>45261</v>
@@ -4665,10 +4548,10 @@
         </is>
       </c>
       <c r="E149">
-        <v>8.27</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F149">
-        <v>-1.43</v>
+        <v>-2.98</v>
       </c>
       <c r="G149" s="2">
         <v>45261</v>
@@ -4696,10 +4579,10 @@
         </is>
       </c>
       <c r="E150">
-        <v>226.71</v>
+        <v>220.37</v>
       </c>
       <c r="F150">
-        <v>-6.56</v>
+        <v>-9.17</v>
       </c>
       <c r="G150" s="2">
         <v>45261</v>
@@ -4727,10 +4610,10 @@
         </is>
       </c>
       <c r="E151">
-        <v>5.97</v>
+        <v>6.66</v>
       </c>
       <c r="F151">
-        <v>-0.5</v>
+        <v>11</v>
       </c>
       <c r="G151" s="2">
         <v>45261</v>
@@ -4758,10 +4641,10 @@
         </is>
       </c>
       <c r="E152">
-        <v>29.86</v>
+        <v>26.78</v>
       </c>
       <c r="F152">
-        <v>-12.18</v>
+        <v>-21.24</v>
       </c>
       <c r="G152" s="2">
         <v>45261</v>
@@ -4789,10 +4672,10 @@
         </is>
       </c>
       <c r="E153">
-        <v>29.32</v>
+        <v>31.95</v>
       </c>
       <c r="F153">
-        <v>-4.65</v>
+        <v>3.9</v>
       </c>
       <c r="G153" s="2">
         <v>45261</v>
@@ -4820,10 +4703,10 @@
         </is>
       </c>
       <c r="E154">
-        <v>19.73</v>
+        <v>20.49</v>
       </c>
       <c r="F154">
-        <v>-2.23</v>
+        <v>1.54</v>
       </c>
       <c r="G154" s="2">
         <v>45261</v>
@@ -4851,10 +4734,10 @@
         </is>
       </c>
       <c r="E155">
-        <v>76.89</v>
+        <v>76.38</v>
       </c>
       <c r="F155">
-        <v>15.66</v>
+        <v>14.89</v>
       </c>
       <c r="G155" s="2">
         <v>45261</v>
@@ -4882,10 +4765,10 @@
         </is>
       </c>
       <c r="E156">
-        <v>75.28</v>
+        <v>60.75</v>
       </c>
       <c r="F156">
-        <v>1.76</v>
+        <v>-17.88</v>
       </c>
       <c r="G156" s="2">
         <v>45261</v>
@@ -4913,10 +4796,10 @@
         </is>
       </c>
       <c r="E157">
-        <v>5.22</v>
+        <v>5.65</v>
       </c>
       <c r="F157">
-        <v>1.56</v>
+        <v>9.92</v>
       </c>
       <c r="G157" s="2">
         <v>45261</v>
@@ -4947,7 +4830,7 @@
         <v>16.47</v>
       </c>
       <c r="F158">
-        <v>11.28</v>
+        <v>17.31</v>
       </c>
       <c r="G158" s="2">
         <v>45292</v>
@@ -4978,7 +4861,7 @@
         <v>15.78</v>
       </c>
       <c r="F159">
-        <v>12.79</v>
+        <v>13.36</v>
       </c>
       <c r="G159" s="2">
         <v>45292</v>
@@ -5009,7 +4892,7 @@
         <v>4.14</v>
       </c>
       <c r="F160">
-        <v>-20.08</v>
+        <v>6.15</v>
       </c>
       <c r="G160" s="2">
         <v>45292</v>
@@ -5040,7 +4923,7 @@
         <v>31.44</v>
       </c>
       <c r="F161">
-        <v>0.38</v>
+        <v>17.49</v>
       </c>
       <c r="G161" s="2">
         <v>45292</v>
@@ -5071,7 +4954,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="F162">
-        <v>1.45</v>
+        <v>3.07</v>
       </c>
       <c r="G162" s="2">
         <v>45292</v>
@@ -5102,7 +4985,7 @@
         <v>214.43</v>
       </c>
       <c r="F163">
-        <v>-5.42</v>
+        <v>-2.7</v>
       </c>
       <c r="G163" s="2">
         <v>45292</v>
@@ -5133,7 +5016,7 @@
         <v>7.74</v>
       </c>
       <c r="F164">
-        <v>29.65</v>
+        <v>16.22</v>
       </c>
       <c r="G164" s="2">
         <v>45292</v>
@@ -5164,7 +5047,7 @@
         <v>28.93</v>
       </c>
       <c r="F165">
-        <v>-3.11</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G165" s="2">
         <v>45292</v>
@@ -5195,7 +5078,7 @@
         <v>30.6</v>
       </c>
       <c r="F166">
-        <v>4.37</v>
+        <v>-4.23</v>
       </c>
       <c r="G166" s="2">
         <v>45292</v>
@@ -5226,7 +5109,7 @@
         <v>21.3</v>
       </c>
       <c r="F167">
-        <v>7.96</v>
+        <v>3.95</v>
       </c>
       <c r="G167" s="2">
         <v>45292</v>
@@ -5257,7 +5140,7 @@
         <v>73.73999999999999</v>
       </c>
       <c r="F168">
-        <v>-4.1</v>
+        <v>-3.46</v>
       </c>
       <c r="G168" s="2">
         <v>45292</v>
@@ -5288,7 +5171,7 @@
         <v>61.11</v>
       </c>
       <c r="F169">
-        <v>-18.82</v>
+        <v>0.59</v>
       </c>
       <c r="G169" s="2">
         <v>45292</v>
@@ -5319,7 +5202,7 @@
         <v>6.25</v>
       </c>
       <c r="F170">
-        <v>19.73</v>
+        <v>10.62</v>
       </c>
       <c r="G170" s="2">
         <v>45292</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G677"/>
+  <dimension ref="A1:G703"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -12751,17 +12751,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -12769,24 +12769,30 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E418">
+        <v>10.32</v>
+      </c>
+      <c r="F418">
+        <v>-8.02</v>
+      </c>
       <c r="G418" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -12794,24 +12800,30 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E419">
+        <v>13.17</v>
+      </c>
+      <c r="F419">
+        <v>-1.79</v>
+      </c>
       <c r="G419" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -12819,24 +12831,30 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E420">
+        <v>5.99</v>
+      </c>
+      <c r="F420">
+        <v>25.84</v>
+      </c>
       <c r="G420" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -12844,24 +12862,30 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E421">
+        <v>11.94</v>
+      </c>
+      <c r="F421">
+        <v>-74.31999999999999</v>
+      </c>
       <c r="G421" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -12869,24 +12893,30 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E422">
+        <v>20.36</v>
+      </c>
+      <c r="F422">
+        <v>21.33</v>
+      </c>
       <c r="G422" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -12894,24 +12924,30 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E423">
+        <v>377.72</v>
+      </c>
+      <c r="F423">
+        <v>25.61</v>
+      </c>
       <c r="G423" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -12919,24 +12955,30 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E424">
+        <v>5.54</v>
+      </c>
+      <c r="F424">
+        <v>-7.05</v>
+      </c>
       <c r="G424" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -12944,24 +12986,30 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E425">
+        <v>22.14</v>
+      </c>
+      <c r="F425">
+        <v>-6.82</v>
+      </c>
       <c r="G425" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -12969,24 +13017,30 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E426">
+        <v>32.92</v>
+      </c>
+      <c r="F426">
+        <v>-1.79</v>
+      </c>
       <c r="G426" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -12994,24 +13048,30 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E427">
+        <v>25.97</v>
+      </c>
+      <c r="F427">
+        <v>19.02</v>
+      </c>
       <c r="G427" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -13019,24 +13079,30 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E428">
+        <v>99</v>
+      </c>
+      <c r="F428">
+        <v>3.58</v>
+      </c>
       <c r="G428" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -13044,24 +13110,30 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E429">
+        <v>80.91</v>
+      </c>
+      <c r="F429">
+        <v>-9.83</v>
+      </c>
       <c r="G429" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -13069,8 +13141,14 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E430">
+        <v>6.5</v>
+      </c>
+      <c r="F430">
+        <v>4.84</v>
+      </c>
       <c r="G430" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="431">
@@ -13081,7 +13159,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -13094,11 +13172,8 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E431">
-        <v>18.31</v>
-      </c>
       <c r="G431" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="432">
@@ -13109,7 +13184,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -13122,11 +13197,8 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E432">
-        <v>13.46</v>
-      </c>
       <c r="G432" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="433">
@@ -13137,7 +13209,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -13150,11 +13222,8 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E433">
-        <v>5.63</v>
-      </c>
       <c r="G433" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="434">
@@ -13165,7 +13234,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -13178,11 +13247,8 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E434">
-        <v>56.91</v>
-      </c>
       <c r="G434" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="435">
@@ -13193,7 +13259,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -13206,11 +13272,8 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E435">
-        <v>8.75</v>
-      </c>
       <c r="G435" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="436">
@@ -13221,7 +13284,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -13234,11 +13297,8 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E436">
-        <v>234.48</v>
-      </c>
       <c r="G436" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="437">
@@ -13249,7 +13309,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -13262,11 +13322,8 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E437">
-        <v>5.73</v>
-      </c>
       <c r="G437" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="438">
@@ -13277,7 +13334,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -13290,11 +13347,8 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E438">
-        <v>39.21</v>
-      </c>
       <c r="G438" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="439">
@@ -13305,7 +13359,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -13318,11 +13372,8 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E439">
-        <v>29.62</v>
-      </c>
       <c r="G439" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="440">
@@ -13333,7 +13384,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -13346,11 +13397,8 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E440">
-        <v>18.75</v>
-      </c>
       <c r="G440" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="441">
@@ -13361,7 +13409,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -13374,11 +13422,8 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E441">
-        <v>83.66</v>
-      </c>
       <c r="G441" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="442">
@@ -13389,7 +13434,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -13402,11 +13447,8 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E442">
-        <v>94.41</v>
-      </c>
       <c r="G442" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="443">
@@ -13417,7 +13459,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -13430,11 +13472,8 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E443">
-        <v>5.42</v>
-      </c>
       <c r="G443" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="444">
@@ -13445,7 +13484,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -13459,13 +13498,10 @@
         </is>
       </c>
       <c r="E444">
-        <v>19.41</v>
-      </c>
-      <c r="F444">
-        <v>6.01</v>
+        <v>18.31</v>
       </c>
       <c r="G444" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="445">
@@ -13476,7 +13512,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -13490,13 +13526,10 @@
         </is>
       </c>
       <c r="E445">
-        <v>14.67</v>
-      </c>
-      <c r="F445">
-        <v>8.99</v>
+        <v>13.46</v>
       </c>
       <c r="G445" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="446">
@@ -13507,7 +13540,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -13521,13 +13554,10 @@
         </is>
       </c>
       <c r="E446">
-        <v>6.95</v>
-      </c>
-      <c r="F446">
-        <v>23.45</v>
+        <v>5.63</v>
       </c>
       <c r="G446" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="447">
@@ -13538,7 +13568,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -13552,13 +13582,10 @@
         </is>
       </c>
       <c r="E447">
-        <v>47.64</v>
-      </c>
-      <c r="F447">
-        <v>-16.29</v>
+        <v>56.91</v>
       </c>
       <c r="G447" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="448">
@@ -13569,7 +13596,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -13583,13 +13610,10 @@
         </is>
       </c>
       <c r="E448">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="F448">
-        <v>4.11</v>
+        <v>8.75</v>
       </c>
       <c r="G448" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="449">
@@ -13600,7 +13624,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -13614,13 +13638,10 @@
         </is>
       </c>
       <c r="E449">
-        <v>275.65</v>
-      </c>
-      <c r="F449">
-        <v>17.56</v>
+        <v>234.48</v>
       </c>
       <c r="G449" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="450">
@@ -13631,7 +13652,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -13645,13 +13666,10 @@
         </is>
       </c>
       <c r="E450">
-        <v>6.43</v>
-      </c>
-      <c r="F450">
-        <v>12.22</v>
+        <v>5.73</v>
       </c>
       <c r="G450" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="451">
@@ -13662,7 +13680,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -13676,13 +13694,10 @@
         </is>
       </c>
       <c r="E451">
-        <v>45.58</v>
-      </c>
-      <c r="F451">
-        <v>16.25</v>
+        <v>39.21</v>
       </c>
       <c r="G451" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="452">
@@ -13693,7 +13708,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -13707,13 +13722,10 @@
         </is>
       </c>
       <c r="E452">
-        <v>30.86</v>
-      </c>
-      <c r="F452">
-        <v>4.19</v>
+        <v>29.62</v>
       </c>
       <c r="G452" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="453">
@@ -13724,7 +13736,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13738,13 +13750,10 @@
         </is>
       </c>
       <c r="E453">
-        <v>20.05</v>
-      </c>
-      <c r="F453">
-        <v>6.93</v>
+        <v>18.75</v>
       </c>
       <c r="G453" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="454">
@@ -13755,7 +13764,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13769,13 +13778,10 @@
         </is>
       </c>
       <c r="E454">
-        <v>68.67</v>
-      </c>
-      <c r="F454">
-        <v>-17.92</v>
+        <v>83.66</v>
       </c>
       <c r="G454" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="455">
@@ -13786,7 +13792,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -13800,13 +13806,10 @@
         </is>
       </c>
       <c r="E455">
-        <v>85.41</v>
-      </c>
-      <c r="F455">
-        <v>-9.529999999999999</v>
+        <v>94.41</v>
       </c>
       <c r="G455" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="456">
@@ -13817,7 +13820,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13831,13 +13834,10 @@
         </is>
       </c>
       <c r="E456">
-        <v>5.55</v>
-      </c>
-      <c r="F456">
-        <v>2.4</v>
+        <v>5.42</v>
       </c>
       <c r="G456" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="457">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -13862,13 +13862,13 @@
         </is>
       </c>
       <c r="E457">
-        <v>18.86</v>
+        <v>19.41</v>
       </c>
       <c r="F457">
-        <v>-2.83</v>
+        <v>6.01</v>
       </c>
       <c r="G457" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="458">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -13893,13 +13893,13 @@
         </is>
       </c>
       <c r="E458">
-        <v>13.88</v>
+        <v>14.67</v>
       </c>
       <c r="F458">
-        <v>-5.39</v>
+        <v>8.99</v>
       </c>
       <c r="G458" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="459">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -13924,13 +13924,13 @@
         </is>
       </c>
       <c r="E459">
-        <v>6.11</v>
+        <v>6.95</v>
       </c>
       <c r="F459">
-        <v>-12.09</v>
+        <v>23.45</v>
       </c>
       <c r="G459" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="460">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13955,13 +13955,13 @@
         </is>
       </c>
       <c r="E460">
-        <v>37.94</v>
+        <v>47.64</v>
       </c>
       <c r="F460">
-        <v>-20.36</v>
+        <v>-16.29</v>
       </c>
       <c r="G460" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="461">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -13986,13 +13986,13 @@
         </is>
       </c>
       <c r="E461">
-        <v>9.18</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F461">
-        <v>0.77</v>
+        <v>4.11</v>
       </c>
       <c r="G461" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="462">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -14017,13 +14017,13 @@
         </is>
       </c>
       <c r="E462">
-        <v>254.3</v>
+        <v>275.65</v>
       </c>
       <c r="F462">
-        <v>-7.75</v>
+        <v>17.56</v>
       </c>
       <c r="G462" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="463">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -14048,13 +14048,13 @@
         </is>
       </c>
       <c r="E463">
-        <v>5.84</v>
+        <v>6.43</v>
       </c>
       <c r="F463">
-        <v>-9.18</v>
+        <v>12.22</v>
       </c>
       <c r="G463" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="464">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -14079,13 +14079,13 @@
         </is>
       </c>
       <c r="E464">
-        <v>40.17</v>
+        <v>45.58</v>
       </c>
       <c r="F464">
-        <v>-11.87</v>
+        <v>16.25</v>
       </c>
       <c r="G464" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="465">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -14110,13 +14110,13 @@
         </is>
       </c>
       <c r="E465">
-        <v>30.55</v>
+        <v>30.86</v>
       </c>
       <c r="F465">
-        <v>-1</v>
+        <v>4.19</v>
       </c>
       <c r="G465" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="466">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -14141,13 +14141,13 @@
         </is>
       </c>
       <c r="E466">
-        <v>20.32</v>
+        <v>20.05</v>
       </c>
       <c r="F466">
-        <v>1.35</v>
+        <v>6.93</v>
       </c>
       <c r="G466" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="467">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="E467">
-        <v>81.58</v>
+        <v>68.67</v>
       </c>
       <c r="F467">
-        <v>18.8</v>
+        <v>-17.92</v>
       </c>
       <c r="G467" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="468">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -14203,13 +14203,13 @@
         </is>
       </c>
       <c r="E468">
-        <v>95.61</v>
+        <v>85.41</v>
       </c>
       <c r="F468">
-        <v>11.94</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="G468" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="469">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -14234,13 +14234,13 @@
         </is>
       </c>
       <c r="E469">
-        <v>5.37</v>
+        <v>5.55</v>
       </c>
       <c r="F469">
-        <v>-3.24</v>
+        <v>2.4</v>
       </c>
       <c r="G469" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="470">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -14265,13 +14265,13 @@
         </is>
       </c>
       <c r="E470">
-        <v>17.57</v>
+        <v>18.86</v>
       </c>
       <c r="F470">
-        <v>-6.84</v>
+        <v>-2.83</v>
       </c>
       <c r="G470" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="471">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -14296,13 +14296,13 @@
         </is>
       </c>
       <c r="E471">
-        <v>13.71</v>
+        <v>13.88</v>
       </c>
       <c r="F471">
-        <v>-1.22</v>
+        <v>-5.39</v>
       </c>
       <c r="G471" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="472">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -14330,10 +14330,10 @@
         <v>6.11</v>
       </c>
       <c r="F472">
-        <v>0</v>
+        <v>-12.09</v>
       </c>
       <c r="G472" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="473">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -14358,13 +14358,13 @@
         </is>
       </c>
       <c r="E473">
-        <v>43.94</v>
+        <v>37.94</v>
       </c>
       <c r="F473">
-        <v>15.81</v>
+        <v>-20.36</v>
       </c>
       <c r="G473" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="474">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="E474">
-        <v>9.65</v>
+        <v>9.18</v>
       </c>
       <c r="F474">
-        <v>5.12</v>
+        <v>0.77</v>
       </c>
       <c r="G474" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="475">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -14420,13 +14420,13 @@
         </is>
       </c>
       <c r="E475">
-        <v>252.8</v>
+        <v>254.3</v>
       </c>
       <c r="F475">
-        <v>-0.59</v>
+        <v>-7.75</v>
       </c>
       <c r="G475" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="476">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -14451,13 +14451,13 @@
         </is>
       </c>
       <c r="E476">
-        <v>5.66</v>
+        <v>5.84</v>
       </c>
       <c r="F476">
-        <v>-3.08</v>
+        <v>-9.18</v>
       </c>
       <c r="G476" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="477">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -14482,13 +14482,13 @@
         </is>
       </c>
       <c r="E477">
-        <v>35.28</v>
+        <v>40.17</v>
       </c>
       <c r="F477">
-        <v>-12.17</v>
+        <v>-11.87</v>
       </c>
       <c r="G477" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="478">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -14513,13 +14513,13 @@
         </is>
       </c>
       <c r="E478">
-        <v>32.27</v>
+        <v>30.55</v>
       </c>
       <c r="F478">
-        <v>5.63</v>
+        <v>-1</v>
       </c>
       <c r="G478" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="479">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -14544,13 +14544,13 @@
         </is>
       </c>
       <c r="E479">
-        <v>20.09</v>
+        <v>20.32</v>
       </c>
       <c r="F479">
-        <v>-1.13</v>
+        <v>1.35</v>
       </c>
       <c r="G479" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="480">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -14578,10 +14578,10 @@
         <v>81.58</v>
       </c>
       <c r="F480">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="G480" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="481">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -14606,13 +14606,13 @@
         </is>
       </c>
       <c r="E481">
-        <v>86.28</v>
+        <v>95.61</v>
       </c>
       <c r="F481">
-        <v>-9.76</v>
+        <v>11.94</v>
       </c>
       <c r="G481" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="482">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -14637,13 +14637,13 @@
         </is>
       </c>
       <c r="E482">
-        <v>5.08</v>
+        <v>5.37</v>
       </c>
       <c r="F482">
-        <v>-5.4</v>
+        <v>-3.24</v>
       </c>
       <c r="G482" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="483">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -14668,13 +14668,13 @@
         </is>
       </c>
       <c r="E483">
-        <v>19.58</v>
+        <v>17.57</v>
       </c>
       <c r="F483">
-        <v>11.44</v>
+        <v>-6.84</v>
       </c>
       <c r="G483" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="484">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -14699,13 +14699,13 @@
         </is>
       </c>
       <c r="E484">
-        <v>13.62</v>
+        <v>13.71</v>
       </c>
       <c r="F484">
-        <v>-0.66</v>
+        <v>-1.22</v>
       </c>
       <c r="G484" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="485">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="E485">
-        <v>5.21</v>
+        <v>6.11</v>
       </c>
       <c r="F485">
-        <v>-14.73</v>
+        <v>0</v>
       </c>
       <c r="G485" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="486">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -14761,13 +14761,13 @@
         </is>
       </c>
       <c r="E486">
-        <v>55.14</v>
+        <v>43.94</v>
       </c>
       <c r="F486">
-        <v>25.49</v>
+        <v>15.81</v>
       </c>
       <c r="G486" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="487">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -14792,13 +14792,13 @@
         </is>
       </c>
       <c r="E487">
-        <v>9.56</v>
+        <v>9.65</v>
       </c>
       <c r="F487">
-        <v>-0.93</v>
+        <v>5.12</v>
       </c>
       <c r="G487" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="488">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -14823,13 +14823,13 @@
         </is>
       </c>
       <c r="E488">
-        <v>237.34</v>
+        <v>252.8</v>
       </c>
       <c r="F488">
-        <v>-6.12</v>
+        <v>-0.59</v>
       </c>
       <c r="G488" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="489">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -14854,13 +14854,13 @@
         </is>
       </c>
       <c r="E489">
-        <v>6.14</v>
+        <v>5.66</v>
       </c>
       <c r="F489">
-        <v>8.48</v>
+        <v>-3.08</v>
       </c>
       <c r="G489" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="490">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -14885,13 +14885,13 @@
         </is>
       </c>
       <c r="E490">
-        <v>32.87</v>
+        <v>35.28</v>
       </c>
       <c r="F490">
-        <v>-6.83</v>
+        <v>-12.17</v>
       </c>
       <c r="G490" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="491">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -14916,13 +14916,13 @@
         </is>
       </c>
       <c r="E491">
-        <v>37.54</v>
+        <v>32.27</v>
       </c>
       <c r="F491">
-        <v>16.33</v>
+        <v>5.63</v>
       </c>
       <c r="G491" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="492">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -14947,13 +14947,13 @@
         </is>
       </c>
       <c r="E492">
-        <v>20.26</v>
+        <v>20.09</v>
       </c>
       <c r="F492">
-        <v>0.85</v>
+        <v>-1.13</v>
       </c>
       <c r="G492" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="493">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -14978,13 +14978,13 @@
         </is>
       </c>
       <c r="E493">
-        <v>83.67</v>
+        <v>81.58</v>
       </c>
       <c r="F493">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="G493" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="494">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="E494">
-        <v>103.41</v>
+        <v>86.28</v>
       </c>
       <c r="F494">
-        <v>19.85</v>
+        <v>-9.76</v>
       </c>
       <c r="G494" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="495">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -15040,13 +15040,13 @@
         </is>
       </c>
       <c r="E495">
-        <v>5.44</v>
+        <v>5.08</v>
       </c>
       <c r="F495">
-        <v>7.09</v>
+        <v>-5.4</v>
       </c>
       <c r="G495" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="496">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="E496">
-        <v>19.41</v>
+        <v>19.58</v>
       </c>
       <c r="F496">
-        <v>-0.87</v>
+        <v>11.44</v>
       </c>
       <c r="G496" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="497">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -15102,13 +15102,13 @@
         </is>
       </c>
       <c r="E497">
-        <v>13.54</v>
+        <v>13.62</v>
       </c>
       <c r="F497">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="G497" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="498">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="E498">
-        <v>5.59</v>
+        <v>5.21</v>
       </c>
       <c r="F498">
-        <v>7.29</v>
+        <v>-14.73</v>
       </c>
       <c r="G498" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="499">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -15164,13 +15164,13 @@
         </is>
       </c>
       <c r="E499">
-        <v>59.34</v>
+        <v>55.14</v>
       </c>
       <c r="F499">
-        <v>7.62</v>
+        <v>25.49</v>
       </c>
       <c r="G499" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="500">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -15195,13 +15195,13 @@
         </is>
       </c>
       <c r="E500">
-        <v>10.44</v>
+        <v>9.56</v>
       </c>
       <c r="F500">
-        <v>9.210000000000001</v>
+        <v>-0.93</v>
       </c>
       <c r="G500" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="501">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -15226,13 +15226,13 @@
         </is>
       </c>
       <c r="E501">
-        <v>242.59</v>
+        <v>237.34</v>
       </c>
       <c r="F501">
-        <v>2.21</v>
+        <v>-6.12</v>
       </c>
       <c r="G501" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="502">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -15257,13 +15257,13 @@
         </is>
       </c>
       <c r="E502">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="F502">
-        <v>3.09</v>
+        <v>8.48</v>
       </c>
       <c r="G502" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="503">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -15288,13 +15288,13 @@
         </is>
       </c>
       <c r="E503">
-        <v>33.7</v>
+        <v>32.87</v>
       </c>
       <c r="F503">
-        <v>2.53</v>
+        <v>-6.83</v>
       </c>
       <c r="G503" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="504">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -15319,13 +15319,13 @@
         </is>
       </c>
       <c r="E504">
-        <v>35.25</v>
+        <v>37.54</v>
       </c>
       <c r="F504">
-        <v>-6.1</v>
+        <v>16.33</v>
       </c>
       <c r="G504" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="505">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -15350,13 +15350,13 @@
         </is>
       </c>
       <c r="E505">
-        <v>20.17</v>
+        <v>20.26</v>
       </c>
       <c r="F505">
-        <v>-0.44</v>
+        <v>0.85</v>
       </c>
       <c r="G505" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="506">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="E506">
-        <v>71.58</v>
+        <v>83.67</v>
       </c>
       <c r="F506">
-        <v>-14.45</v>
+        <v>2.56</v>
       </c>
       <c r="G506" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="507">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -15412,13 +15412,13 @@
         </is>
       </c>
       <c r="E507">
-        <v>58.41</v>
+        <v>103.41</v>
       </c>
       <c r="F507">
-        <v>-43.52</v>
+        <v>19.85</v>
       </c>
       <c r="G507" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="508">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -15443,13 +15443,13 @@
         </is>
       </c>
       <c r="E508">
-        <v>5.32</v>
+        <v>5.44</v>
       </c>
       <c r="F508">
-        <v>-2.21</v>
+        <v>7.09</v>
       </c>
       <c r="G508" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="509">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -15474,13 +15474,13 @@
         </is>
       </c>
       <c r="E509">
-        <v>19.57</v>
+        <v>19.41</v>
       </c>
       <c r="F509">
-        <v>0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="G509" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="510">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -15505,13 +15505,13 @@
         </is>
       </c>
       <c r="E510">
-        <v>13.78</v>
+        <v>13.54</v>
       </c>
       <c r="F510">
-        <v>1.77</v>
+        <v>-0.59</v>
       </c>
       <c r="G510" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="511">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -15536,13 +15536,13 @@
         </is>
       </c>
       <c r="E511">
-        <v>6.11</v>
+        <v>5.59</v>
       </c>
       <c r="F511">
-        <v>9.300000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="G511" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="512">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -15567,13 +15567,13 @@
         </is>
       </c>
       <c r="E512">
-        <v>48.54</v>
+        <v>59.34</v>
       </c>
       <c r="F512">
-        <v>-18.2</v>
+        <v>7.62</v>
       </c>
       <c r="G512" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="513">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -15601,10 +15601,10 @@
         <v>10.44</v>
       </c>
       <c r="F513">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G513" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="514">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -15629,13 +15629,13 @@
         </is>
       </c>
       <c r="E514">
-        <v>241.01</v>
+        <v>242.59</v>
       </c>
       <c r="F514">
-        <v>-0.65</v>
+        <v>2.21</v>
       </c>
       <c r="G514" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="515">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -15660,13 +15660,13 @@
         </is>
       </c>
       <c r="E515">
-        <v>6.68</v>
+        <v>6.33</v>
       </c>
       <c r="F515">
-        <v>5.53</v>
+        <v>3.09</v>
       </c>
       <c r="G515" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="516">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="E516">
-        <v>33.64</v>
+        <v>33.7</v>
       </c>
       <c r="F516">
-        <v>-0.18</v>
+        <v>2.53</v>
       </c>
       <c r="G516" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="517">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="E517">
-        <v>33.48</v>
+        <v>35.25</v>
       </c>
       <c r="F517">
-        <v>-5.02</v>
+        <v>-6.1</v>
       </c>
       <c r="G517" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="518">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -15753,13 +15753,13 @@
         </is>
       </c>
       <c r="E518">
-        <v>20.5</v>
+        <v>20.17</v>
       </c>
       <c r="F518">
-        <v>1.64</v>
+        <v>-0.44</v>
       </c>
       <c r="G518" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="519">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -15784,13 +15784,13 @@
         </is>
       </c>
       <c r="E519">
-        <v>85.58</v>
+        <v>71.58</v>
       </c>
       <c r="F519">
-        <v>19.56</v>
+        <v>-14.45</v>
       </c>
       <c r="G519" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="520">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="E520">
-        <v>56.31</v>
+        <v>58.41</v>
       </c>
       <c r="F520">
-        <v>-3.6</v>
+        <v>-43.52</v>
       </c>
       <c r="G520" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="521">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -15846,13 +15846,13 @@
         </is>
       </c>
       <c r="E521">
-        <v>5.35</v>
+        <v>5.32</v>
       </c>
       <c r="F521">
-        <v>0.5600000000000001</v>
+        <v>-2.21</v>
       </c>
       <c r="G521" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="522">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -15877,13 +15877,13 @@
         </is>
       </c>
       <c r="E522">
-        <v>20.28</v>
+        <v>19.57</v>
       </c>
       <c r="F522">
-        <v>3.63</v>
+        <v>0.82</v>
       </c>
       <c r="G522" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="523">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -15908,13 +15908,13 @@
         </is>
       </c>
       <c r="E523">
-        <v>13.71</v>
+        <v>13.78</v>
       </c>
       <c r="F523">
-        <v>-0.51</v>
+        <v>1.77</v>
       </c>
       <c r="G523" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="524">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -15939,13 +15939,13 @@
         </is>
       </c>
       <c r="E524">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="F524">
-        <v>5.07</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G524" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="525">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="E525">
-        <v>41.73</v>
+        <v>48.54</v>
       </c>
       <c r="F525">
-        <v>-14.03</v>
+        <v>-18.2</v>
       </c>
       <c r="G525" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="526">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -16001,13 +16001,13 @@
         </is>
       </c>
       <c r="E526">
-        <v>11.04</v>
+        <v>10.44</v>
       </c>
       <c r="F526">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="G526" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="527">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -16032,13 +16032,13 @@
         </is>
       </c>
       <c r="E527">
-        <v>237.85</v>
+        <v>241.01</v>
       </c>
       <c r="F527">
-        <v>-1.31</v>
+        <v>-0.65</v>
       </c>
       <c r="G527" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="528">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="E528">
-        <v>6.41</v>
+        <v>6.68</v>
       </c>
       <c r="F528">
-        <v>-4.04</v>
+        <v>5.53</v>
       </c>
       <c r="G528" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="529">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -16094,13 +16094,13 @@
         </is>
       </c>
       <c r="E529">
-        <v>37.09</v>
+        <v>33.64</v>
       </c>
       <c r="F529">
-        <v>10.26</v>
+        <v>-0.18</v>
       </c>
       <c r="G529" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="530">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -16125,13 +16125,13 @@
         </is>
       </c>
       <c r="E530">
-        <v>34.69</v>
+        <v>33.48</v>
       </c>
       <c r="F530">
-        <v>3.61</v>
+        <v>-5.02</v>
       </c>
       <c r="G530" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="531">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -16156,13 +16156,13 @@
         </is>
       </c>
       <c r="E531">
-        <v>17.59</v>
+        <v>20.5</v>
       </c>
       <c r="F531">
-        <v>-14.2</v>
+        <v>1.64</v>
       </c>
       <c r="G531" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="532">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -16187,13 +16187,13 @@
         </is>
       </c>
       <c r="E532">
-        <v>88.06</v>
+        <v>85.58</v>
       </c>
       <c r="F532">
-        <v>2.9</v>
+        <v>19.56</v>
       </c>
       <c r="G532" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="533">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -16218,13 +16218,13 @@
         </is>
       </c>
       <c r="E533">
-        <v>47.79</v>
+        <v>56.31</v>
       </c>
       <c r="F533">
-        <v>-15.13</v>
+        <v>-3.6</v>
       </c>
       <c r="G533" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="534">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -16249,13 +16249,13 @@
         </is>
       </c>
       <c r="E534">
-        <v>5.63</v>
+        <v>5.35</v>
       </c>
       <c r="F534">
-        <v>5.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G534" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="535">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -16280,13 +16280,13 @@
         </is>
       </c>
       <c r="E535">
-        <v>19.38</v>
+        <v>20.28</v>
       </c>
       <c r="F535">
-        <v>-4.44</v>
+        <v>3.63</v>
       </c>
       <c r="G535" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="536">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -16311,13 +16311,13 @@
         </is>
       </c>
       <c r="E536">
-        <v>13.08</v>
+        <v>13.71</v>
       </c>
       <c r="F536">
-        <v>-4.6</v>
+        <v>-0.51</v>
       </c>
       <c r="G536" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="537">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -16342,13 +16342,13 @@
         </is>
       </c>
       <c r="E537">
-        <v>6.59</v>
+        <v>6.42</v>
       </c>
       <c r="F537">
-        <v>2.65</v>
+        <v>5.07</v>
       </c>
       <c r="G537" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="538">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -16373,13 +16373,13 @@
         </is>
       </c>
       <c r="E538">
-        <v>34.74</v>
+        <v>41.73</v>
       </c>
       <c r="F538">
-        <v>-16.75</v>
+        <v>-14.03</v>
       </c>
       <c r="G538" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="539">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -16404,13 +16404,13 @@
         </is>
       </c>
       <c r="E539">
-        <v>11.83</v>
+        <v>11.04</v>
       </c>
       <c r="F539">
-        <v>7.16</v>
+        <v>5.75</v>
       </c>
       <c r="G539" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="540">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -16435,13 +16435,13 @@
         </is>
       </c>
       <c r="E540">
-        <v>238.33</v>
+        <v>237.85</v>
       </c>
       <c r="F540">
-        <v>0.2</v>
+        <v>-1.31</v>
       </c>
       <c r="G540" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="541">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="E541">
-        <v>5.98</v>
+        <v>6.41</v>
       </c>
       <c r="F541">
-        <v>-6.71</v>
+        <v>-4.04</v>
       </c>
       <c r="G541" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="542">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -16497,13 +16497,13 @@
         </is>
       </c>
       <c r="E542">
-        <v>32.98</v>
+        <v>37.09</v>
       </c>
       <c r="F542">
-        <v>-11.08</v>
+        <v>10.26</v>
       </c>
       <c r="G542" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="543">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -16528,13 +16528,13 @@
         </is>
       </c>
       <c r="E543">
-        <v>35.17</v>
+        <v>34.69</v>
       </c>
       <c r="F543">
-        <v>1.38</v>
+        <v>3.61</v>
       </c>
       <c r="G543" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="544">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -16559,13 +16559,13 @@
         </is>
       </c>
       <c r="E544">
-        <v>20.02</v>
+        <v>17.59</v>
       </c>
       <c r="F544">
-        <v>13.81</v>
+        <v>-14.2</v>
       </c>
       <c r="G544" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="545">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16590,13 +16590,13 @@
         </is>
       </c>
       <c r="E545">
-        <v>77.37</v>
+        <v>88.06</v>
       </c>
       <c r="F545">
-        <v>-12.14</v>
+        <v>2.9</v>
       </c>
       <c r="G545" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="546">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -16621,13 +16621,13 @@
         </is>
       </c>
       <c r="E546">
-        <v>53.46</v>
+        <v>47.79</v>
       </c>
       <c r="F546">
-        <v>11.86</v>
+        <v>-15.13</v>
       </c>
       <c r="G546" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="547">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -16652,13 +16652,13 @@
         </is>
       </c>
       <c r="E547">
-        <v>5.73</v>
+        <v>5.63</v>
       </c>
       <c r="F547">
-        <v>1.78</v>
+        <v>5.23</v>
       </c>
       <c r="G547" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="548">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -16683,13 +16683,13 @@
         </is>
       </c>
       <c r="E548">
-        <v>19.12</v>
+        <v>19.38</v>
       </c>
       <c r="F548">
-        <v>-1.34</v>
+        <v>-4.44</v>
       </c>
       <c r="G548" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="549">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -16714,13 +16714,13 @@
         </is>
       </c>
       <c r="E549">
-        <v>12.87</v>
+        <v>13.08</v>
       </c>
       <c r="F549">
-        <v>-1.61</v>
+        <v>-4.6</v>
       </c>
       <c r="G549" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="550">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -16748,10 +16748,10 @@
         <v>6.59</v>
       </c>
       <c r="F550">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="G550" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="551">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -16776,13 +16776,13 @@
         </is>
       </c>
       <c r="E551">
-        <v>38.94</v>
+        <v>34.74</v>
       </c>
       <c r="F551">
-        <v>12.09</v>
+        <v>-16.75</v>
       </c>
       <c r="G551" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="552">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -16807,13 +16807,13 @@
         </is>
       </c>
       <c r="E552">
-        <v>12.1</v>
+        <v>11.83</v>
       </c>
       <c r="F552">
-        <v>2.28</v>
+        <v>7.16</v>
       </c>
       <c r="G552" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="553">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -16838,13 +16838,13 @@
         </is>
       </c>
       <c r="E553">
-        <v>282.41</v>
+        <v>238.33</v>
       </c>
       <c r="F553">
-        <v>18.5</v>
+        <v>0.2</v>
       </c>
       <c r="G553" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="554">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -16869,13 +16869,13 @@
         </is>
       </c>
       <c r="E554">
-        <v>6.25</v>
+        <v>5.98</v>
       </c>
       <c r="F554">
-        <v>4.52</v>
+        <v>-6.71</v>
       </c>
       <c r="G554" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="555">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -16900,13 +16900,13 @@
         </is>
       </c>
       <c r="E555">
-        <v>35.39</v>
+        <v>32.98</v>
       </c>
       <c r="F555">
-        <v>7.31</v>
+        <v>-11.08</v>
       </c>
       <c r="G555" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="556">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -16931,13 +16931,13 @@
         </is>
       </c>
       <c r="E556">
-        <v>33.86</v>
+        <v>35.17</v>
       </c>
       <c r="F556">
-        <v>-3.72</v>
+        <v>1.38</v>
       </c>
       <c r="G556" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="557">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="E557">
-        <v>20.89</v>
+        <v>20.02</v>
       </c>
       <c r="F557">
-        <v>4.35</v>
+        <v>13.81</v>
       </c>
       <c r="G557" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="558">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -16993,13 +16993,13 @@
         </is>
       </c>
       <c r="E558">
-        <v>71.91</v>
+        <v>77.37</v>
       </c>
       <c r="F558">
-        <v>-7.06</v>
+        <v>-12.14</v>
       </c>
       <c r="G558" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="559">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -17024,13 +17024,13 @@
         </is>
       </c>
       <c r="E559">
-        <v>44.91</v>
+        <v>53.46</v>
       </c>
       <c r="F559">
-        <v>-15.99</v>
+        <v>11.86</v>
       </c>
       <c r="G559" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="560">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -17055,13 +17055,13 @@
         </is>
       </c>
       <c r="E560">
-        <v>6.36</v>
+        <v>5.73</v>
       </c>
       <c r="F560">
-        <v>10.99</v>
+        <v>1.78</v>
       </c>
       <c r="G560" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="561">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -17086,13 +17086,13 @@
         </is>
       </c>
       <c r="E561">
-        <v>18.57</v>
+        <v>19.12</v>
       </c>
       <c r="F561">
-        <v>-2.88</v>
+        <v>-1.34</v>
       </c>
       <c r="G561" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="562">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -17117,13 +17117,13 @@
         </is>
       </c>
       <c r="E562">
-        <v>13.17</v>
+        <v>12.87</v>
       </c>
       <c r="F562">
-        <v>2.33</v>
+        <v>-1.61</v>
       </c>
       <c r="G562" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="563">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="E563">
-        <v>5.99</v>
+        <v>6.59</v>
       </c>
       <c r="F563">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
       <c r="G563" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="564">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -17179,13 +17179,13 @@
         </is>
       </c>
       <c r="E564">
-        <v>23.61</v>
+        <v>38.94</v>
       </c>
       <c r="F564">
-        <v>-39.37</v>
+        <v>12.09</v>
       </c>
       <c r="G564" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="565">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="E565">
-        <v>12.26</v>
+        <v>12.1</v>
       </c>
       <c r="F565">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="G565" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="566">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -17241,13 +17241,13 @@
         </is>
       </c>
       <c r="E566">
-        <v>274.33</v>
+        <v>282.41</v>
       </c>
       <c r="F566">
-        <v>-2.86</v>
+        <v>18.5</v>
       </c>
       <c r="G566" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="567">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -17272,13 +17272,13 @@
         </is>
       </c>
       <c r="E567">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="F567">
-        <v>-1.28</v>
+        <v>4.52</v>
       </c>
       <c r="G567" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="568">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -17303,13 +17303,13 @@
         </is>
       </c>
       <c r="E568">
-        <v>33.66</v>
+        <v>35.39</v>
       </c>
       <c r="F568">
-        <v>-4.89</v>
+        <v>7.31</v>
       </c>
       <c r="G568" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="569">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -17334,13 +17334,13 @@
         </is>
       </c>
       <c r="E569">
-        <v>35.18</v>
+        <v>33.86</v>
       </c>
       <c r="F569">
-        <v>3.9</v>
+        <v>-3.72</v>
       </c>
       <c r="G569" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="570">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -17365,13 +17365,13 @@
         </is>
       </c>
       <c r="E570">
-        <v>21.11</v>
+        <v>20.89</v>
       </c>
       <c r="F570">
-        <v>1.05</v>
+        <v>4.35</v>
       </c>
       <c r="G570" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="571">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -17396,13 +17396,13 @@
         </is>
       </c>
       <c r="E571">
-        <v>80.37</v>
+        <v>71.91</v>
       </c>
       <c r="F571">
-        <v>11.76</v>
+        <v>-7.06</v>
       </c>
       <c r="G571" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="572">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="E572">
-        <v>34.11</v>
+        <v>44.91</v>
       </c>
       <c r="F572">
-        <v>-24.05</v>
+        <v>-15.99</v>
       </c>
       <c r="G572" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="573">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -17458,24 +17458,24 @@
         </is>
       </c>
       <c r="E573">
-        <v>6.83</v>
+        <v>6.36</v>
       </c>
       <c r="F573">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
       <c r="G573" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -17489,24 +17489,24 @@
         </is>
       </c>
       <c r="E574">
-        <v>17.9</v>
+        <v>18.57</v>
       </c>
       <c r="F574">
-        <v>-3.61</v>
+        <v>-2.88</v>
       </c>
       <c r="G574" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -17520,24 +17520,24 @@
         </is>
       </c>
       <c r="E575">
-        <v>14.58</v>
+        <v>13.17</v>
       </c>
       <c r="F575">
-        <v>10.71</v>
+        <v>2.33</v>
       </c>
       <c r="G575" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -17551,24 +17551,24 @@
         </is>
       </c>
       <c r="E576">
-        <v>6.39</v>
+        <v>5.99</v>
       </c>
       <c r="F576">
-        <v>6.68</v>
+        <v>-9.1</v>
       </c>
       <c r="G576" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -17582,24 +17582,24 @@
         </is>
       </c>
       <c r="E577">
-        <v>22.94</v>
+        <v>23.61</v>
       </c>
       <c r="F577">
-        <v>-2.84</v>
+        <v>-39.37</v>
       </c>
       <c r="G577" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -17613,24 +17613,24 @@
         </is>
       </c>
       <c r="E578">
-        <v>13.82</v>
+        <v>12.26</v>
       </c>
       <c r="F578">
-        <v>12.72</v>
+        <v>1.32</v>
       </c>
       <c r="G578" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -17644,24 +17644,24 @@
         </is>
       </c>
       <c r="E579">
-        <v>295.28</v>
+        <v>274.33</v>
       </c>
       <c r="F579">
-        <v>7.64</v>
+        <v>-2.86</v>
       </c>
       <c r="G579" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -17675,24 +17675,24 @@
         </is>
       </c>
       <c r="E580">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="F580">
-        <v>-11.51</v>
+        <v>-1.28</v>
       </c>
       <c r="G580" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -17706,24 +17706,24 @@
         </is>
       </c>
       <c r="E581">
-        <v>30.81</v>
+        <v>33.66</v>
       </c>
       <c r="F581">
-        <v>-8.470000000000001</v>
+        <v>-4.89</v>
       </c>
       <c r="G581" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -17737,24 +17737,24 @@
         </is>
       </c>
       <c r="E582">
-        <v>33.42</v>
+        <v>35.18</v>
       </c>
       <c r="F582">
-        <v>-5</v>
+        <v>3.9</v>
       </c>
       <c r="G582" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -17768,24 +17768,24 @@
         </is>
       </c>
       <c r="E583">
-        <v>21.88</v>
+        <v>21.11</v>
       </c>
       <c r="F583">
-        <v>3.65</v>
+        <v>1.05</v>
       </c>
       <c r="G583" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -17799,24 +17799,24 @@
         </is>
       </c>
       <c r="E584">
-        <v>81.76000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F584">
-        <v>1.73</v>
+        <v>11.76</v>
       </c>
       <c r="G584" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -17830,24 +17830,24 @@
         </is>
       </c>
       <c r="E585">
-        <v>33.81</v>
+        <v>34.11</v>
       </c>
       <c r="F585">
-        <v>-0.88</v>
+        <v>-24.05</v>
       </c>
       <c r="G585" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -17861,13 +17861,13 @@
         </is>
       </c>
       <c r="E586">
-        <v>7.19</v>
+        <v>6.83</v>
       </c>
       <c r="F586">
-        <v>5.27</v>
+        <v>7.39</v>
       </c>
       <c r="G586" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="587">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -17892,13 +17892,13 @@
         </is>
       </c>
       <c r="E587">
-        <v>18.09</v>
+        <v>17.9</v>
       </c>
       <c r="F587">
-        <v>1.06</v>
+        <v>-3.61</v>
       </c>
       <c r="G587" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="588">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -17923,13 +17923,13 @@
         </is>
       </c>
       <c r="E588">
-        <v>14.43</v>
+        <v>14.58</v>
       </c>
       <c r="F588">
-        <v>-1.03</v>
+        <v>10.71</v>
       </c>
       <c r="G588" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="589">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -17954,13 +17954,13 @@
         </is>
       </c>
       <c r="E589">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="F589">
-        <v>-0.63</v>
+        <v>6.68</v>
       </c>
       <c r="G589" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="590">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -17988,10 +17988,10 @@
         <v>22.94</v>
       </c>
       <c r="F590">
-        <v>0</v>
+        <v>-2.84</v>
       </c>
       <c r="G590" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="591">
@@ -18002,7 +18002,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -18016,13 +18016,13 @@
         </is>
       </c>
       <c r="E591">
-        <v>16.25</v>
+        <v>13.82</v>
       </c>
       <c r="F591">
-        <v>17.58</v>
+        <v>12.72</v>
       </c>
       <c r="G591" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="592">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -18047,13 +18047,13 @@
         </is>
       </c>
       <c r="E592">
-        <v>302.48</v>
+        <v>295.28</v>
       </c>
       <c r="F592">
-        <v>2.44</v>
+        <v>7.64</v>
       </c>
       <c r="G592" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="593">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -18078,13 +18078,13 @@
         </is>
       </c>
       <c r="E593">
-        <v>5.76</v>
+        <v>5.46</v>
       </c>
       <c r="F593">
-        <v>5.49</v>
+        <v>-11.51</v>
       </c>
       <c r="G593" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="594">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -18109,13 +18109,13 @@
         </is>
       </c>
       <c r="E594">
-        <v>32.38</v>
+        <v>30.81</v>
       </c>
       <c r="F594">
-        <v>5.1</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="G594" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="595">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -18143,10 +18143,10 @@
         <v>33.42</v>
       </c>
       <c r="F595">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G595" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="596">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="E596">
-        <v>22.14</v>
+        <v>21.88</v>
       </c>
       <c r="F596">
-        <v>1.19</v>
+        <v>3.65</v>
       </c>
       <c r="G596" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="597">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -18202,13 +18202,13 @@
         </is>
       </c>
       <c r="E597">
-        <v>81.14</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="F597">
-        <v>-0.76</v>
+        <v>1.73</v>
       </c>
       <c r="G597" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="598">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -18233,13 +18233,13 @@
         </is>
       </c>
       <c r="E598">
-        <v>47.91</v>
+        <v>33.81</v>
       </c>
       <c r="F598">
-        <v>41.7</v>
+        <v>-0.88</v>
       </c>
       <c r="G598" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="599">
@@ -18250,7 +18250,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -18264,13 +18264,13 @@
         </is>
       </c>
       <c r="E599">
-        <v>7.03</v>
+        <v>7.19</v>
       </c>
       <c r="F599">
-        <v>-2.23</v>
+        <v>5.27</v>
       </c>
       <c r="G599" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="600">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -18295,13 +18295,13 @@
         </is>
       </c>
       <c r="E600">
-        <v>16.67</v>
+        <v>18.09</v>
       </c>
       <c r="F600">
-        <v>-7.85</v>
+        <v>1.06</v>
       </c>
       <c r="G600" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="601">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -18326,13 +18326,13 @@
         </is>
       </c>
       <c r="E601">
-        <v>13.87</v>
+        <v>14.43</v>
       </c>
       <c r="F601">
-        <v>-3.88</v>
+        <v>-1.03</v>
       </c>
       <c r="G601" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="602">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -18357,13 +18357,13 @@
         </is>
       </c>
       <c r="E602">
-        <v>4.47</v>
+        <v>6.35</v>
       </c>
       <c r="F602">
-        <v>-29.61</v>
+        <v>-0.63</v>
       </c>
       <c r="G602" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="603">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -18388,13 +18388,13 @@
         </is>
       </c>
       <c r="E603">
-        <v>17.54</v>
+        <v>22.94</v>
       </c>
       <c r="F603">
-        <v>-23.54</v>
+        <v>0</v>
       </c>
       <c r="G603" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="604">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -18419,13 +18419,13 @@
         </is>
       </c>
       <c r="E604">
-        <v>16.73</v>
+        <v>16.25</v>
       </c>
       <c r="F604">
-        <v>2.95</v>
+        <v>17.58</v>
       </c>
       <c r="G604" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="605">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -18450,13 +18450,13 @@
         </is>
       </c>
       <c r="E605">
-        <v>306.06</v>
+        <v>302.48</v>
       </c>
       <c r="F605">
-        <v>1.18</v>
+        <v>2.44</v>
       </c>
       <c r="G605" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="606">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -18481,13 +18481,13 @@
         </is>
       </c>
       <c r="E606">
-        <v>6.16</v>
+        <v>5.76</v>
       </c>
       <c r="F606">
-        <v>6.94</v>
+        <v>5.49</v>
       </c>
       <c r="G606" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="607">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -18512,13 +18512,13 @@
         </is>
       </c>
       <c r="E607">
-        <v>26.22</v>
+        <v>32.38</v>
       </c>
       <c r="F607">
-        <v>-19.02</v>
+        <v>5.1</v>
       </c>
       <c r="G607" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="608">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -18543,13 +18543,13 @@
         </is>
       </c>
       <c r="E608">
-        <v>35.12</v>
+        <v>33.42</v>
       </c>
       <c r="F608">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="G608" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="609">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -18574,13 +18574,13 @@
         </is>
       </c>
       <c r="E609">
-        <v>22.5</v>
+        <v>22.14</v>
       </c>
       <c r="F609">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="G609" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="610">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="E610">
-        <v>87.14</v>
+        <v>81.14</v>
       </c>
       <c r="F610">
-        <v>7.39</v>
+        <v>-0.76</v>
       </c>
       <c r="G610" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="611">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -18636,13 +18636,13 @@
         </is>
       </c>
       <c r="E611">
-        <v>56.91</v>
+        <v>47.91</v>
       </c>
       <c r="F611">
-        <v>18.79</v>
+        <v>41.7</v>
       </c>
       <c r="G611" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="612">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -18667,13 +18667,13 @@
         </is>
       </c>
       <c r="E612">
-        <v>6.58</v>
+        <v>7.03</v>
       </c>
       <c r="F612">
-        <v>-6.4</v>
+        <v>-2.23</v>
       </c>
       <c r="G612" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="613">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -18697,8 +18697,14 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E613">
+        <v>16.67</v>
+      </c>
+      <c r="F613">
+        <v>-7.85</v>
+      </c>
       <c r="G613" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="614">
@@ -18709,7 +18715,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -18722,8 +18728,14 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E614">
+        <v>13.87</v>
+      </c>
+      <c r="F614">
+        <v>-3.88</v>
+      </c>
       <c r="G614" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="615">
@@ -18734,7 +18746,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -18747,8 +18759,14 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E615">
+        <v>4.47</v>
+      </c>
+      <c r="F615">
+        <v>-29.61</v>
+      </c>
       <c r="G615" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="616">
@@ -18759,7 +18777,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -18772,8 +18790,14 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E616">
+        <v>17.54</v>
+      </c>
+      <c r="F616">
+        <v>-23.54</v>
+      </c>
       <c r="G616" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="617">
@@ -18784,7 +18808,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -18797,8 +18821,14 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E617">
+        <v>16.73</v>
+      </c>
+      <c r="F617">
+        <v>2.95</v>
+      </c>
       <c r="G617" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="618">
@@ -18809,7 +18839,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -18822,8 +18852,14 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E618">
+        <v>306.06</v>
+      </c>
+      <c r="F618">
+        <v>1.18</v>
+      </c>
       <c r="G618" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="619">
@@ -18834,7 +18870,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -18847,8 +18883,14 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E619">
+        <v>6.16</v>
+      </c>
+      <c r="F619">
+        <v>6.94</v>
+      </c>
       <c r="G619" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="620">
@@ -18859,7 +18901,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -18872,8 +18914,14 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E620">
+        <v>26.22</v>
+      </c>
+      <c r="F620">
+        <v>-19.02</v>
+      </c>
       <c r="G620" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="621">
@@ -18884,7 +18932,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -18897,8 +18945,14 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E621">
+        <v>35.12</v>
+      </c>
+      <c r="F621">
+        <v>5.09</v>
+      </c>
       <c r="G621" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="622">
@@ -18909,7 +18963,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -18922,8 +18976,14 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E622">
+        <v>22.5</v>
+      </c>
+      <c r="F622">
+        <v>1.63</v>
+      </c>
       <c r="G622" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="623">
@@ -18934,7 +18994,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -18947,8 +19007,14 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E623">
+        <v>87.14</v>
+      </c>
+      <c r="F623">
+        <v>7.39</v>
+      </c>
       <c r="G623" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="624">
@@ -18959,7 +19025,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -18972,8 +19038,14 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E624">
+        <v>56.91</v>
+      </c>
+      <c r="F624">
+        <v>18.79</v>
+      </c>
       <c r="G624" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="625">
@@ -18984,7 +19056,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -18997,8 +19069,14 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E625">
+        <v>6.58</v>
+      </c>
+      <c r="F625">
+        <v>-6.4</v>
+      </c>
       <c r="G625" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="626">
@@ -19009,7 +19087,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -19023,7 +19101,7 @@
         </is>
       </c>
       <c r="G626" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="627">
@@ -19034,7 +19112,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -19048,7 +19126,7 @@
         </is>
       </c>
       <c r="G627" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="628">
@@ -19059,7 +19137,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -19073,7 +19151,7 @@
         </is>
       </c>
       <c r="G628" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="629">
@@ -19084,7 +19162,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -19098,7 +19176,7 @@
         </is>
       </c>
       <c r="G629" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="630">
@@ -19109,7 +19187,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -19123,7 +19201,7 @@
         </is>
       </c>
       <c r="G630" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="631">
@@ -19134,7 +19212,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -19148,7 +19226,7 @@
         </is>
       </c>
       <c r="G631" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="632">
@@ -19159,7 +19237,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -19173,7 +19251,7 @@
         </is>
       </c>
       <c r="G632" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="633">
@@ -19184,7 +19262,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -19198,7 +19276,7 @@
         </is>
       </c>
       <c r="G633" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="634">
@@ -19209,7 +19287,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -19223,7 +19301,7 @@
         </is>
       </c>
       <c r="G634" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="635">
@@ -19234,7 +19312,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -19248,7 +19326,7 @@
         </is>
       </c>
       <c r="G635" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="636">
@@ -19259,7 +19337,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -19273,7 +19351,7 @@
         </is>
       </c>
       <c r="G636" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="637">
@@ -19284,7 +19362,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -19298,7 +19376,7 @@
         </is>
       </c>
       <c r="G637" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="638">
@@ -19309,7 +19387,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -19323,7 +19401,7 @@
         </is>
       </c>
       <c r="G638" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="639">
@@ -19334,7 +19412,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -19348,7 +19426,7 @@
         </is>
       </c>
       <c r="G639" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="640">
@@ -19359,7 +19437,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -19373,7 +19451,7 @@
         </is>
       </c>
       <c r="G640" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="641">
@@ -19384,7 +19462,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -19398,7 +19476,7 @@
         </is>
       </c>
       <c r="G641" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="642">
@@ -19409,7 +19487,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -19423,7 +19501,7 @@
         </is>
       </c>
       <c r="G642" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="643">
@@ -19434,7 +19512,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -19448,7 +19526,7 @@
         </is>
       </c>
       <c r="G643" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="644">
@@ -19459,7 +19537,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -19473,7 +19551,7 @@
         </is>
       </c>
       <c r="G644" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="645">
@@ -19484,7 +19562,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -19498,7 +19576,7 @@
         </is>
       </c>
       <c r="G645" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="646">
@@ -19509,7 +19587,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -19523,7 +19601,7 @@
         </is>
       </c>
       <c r="G646" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="647">
@@ -19534,7 +19612,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -19548,7 +19626,7 @@
         </is>
       </c>
       <c r="G647" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="648">
@@ -19559,7 +19637,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -19573,7 +19651,7 @@
         </is>
       </c>
       <c r="G648" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="649">
@@ -19584,7 +19662,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -19598,7 +19676,7 @@
         </is>
       </c>
       <c r="G649" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="650">
@@ -19609,7 +19687,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -19623,7 +19701,7 @@
         </is>
       </c>
       <c r="G650" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="651">
@@ -19634,7 +19712,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -19648,7 +19726,7 @@
         </is>
       </c>
       <c r="G651" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="652">
@@ -19659,7 +19737,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -19673,7 +19751,7 @@
         </is>
       </c>
       <c r="G652" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="653">
@@ -19684,7 +19762,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -19698,7 +19776,7 @@
         </is>
       </c>
       <c r="G653" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="654">
@@ -19709,7 +19787,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -19723,7 +19801,7 @@
         </is>
       </c>
       <c r="G654" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="655">
@@ -19734,7 +19812,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -19748,7 +19826,7 @@
         </is>
       </c>
       <c r="G655" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="656">
@@ -19759,7 +19837,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -19773,7 +19851,7 @@
         </is>
       </c>
       <c r="G656" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="657">
@@ -19784,7 +19862,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -19798,7 +19876,7 @@
         </is>
       </c>
       <c r="G657" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="658">
@@ -19809,7 +19887,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -19823,7 +19901,7 @@
         </is>
       </c>
       <c r="G658" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="659">
@@ -19834,7 +19912,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -19848,7 +19926,7 @@
         </is>
       </c>
       <c r="G659" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="660">
@@ -19859,7 +19937,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -19873,7 +19951,7 @@
         </is>
       </c>
       <c r="G660" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="661">
@@ -19884,7 +19962,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -19898,7 +19976,7 @@
         </is>
       </c>
       <c r="G661" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="662">
@@ -19909,7 +19987,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -19923,7 +20001,7 @@
         </is>
       </c>
       <c r="G662" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="663">
@@ -19934,7 +20012,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -19948,7 +20026,7 @@
         </is>
       </c>
       <c r="G663" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="664">
@@ -19959,7 +20037,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -19973,7 +20051,7 @@
         </is>
       </c>
       <c r="G664" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="665">
@@ -19984,7 +20062,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -19998,7 +20076,7 @@
         </is>
       </c>
       <c r="G665" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="666">
@@ -20009,7 +20087,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -20023,7 +20101,7 @@
         </is>
       </c>
       <c r="G666" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="667">
@@ -20034,7 +20112,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -20048,7 +20126,7 @@
         </is>
       </c>
       <c r="G667" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="668">
@@ -20059,7 +20137,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -20073,7 +20151,7 @@
         </is>
       </c>
       <c r="G668" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="669">
@@ -20084,7 +20162,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20098,7 +20176,7 @@
         </is>
       </c>
       <c r="G669" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="670">
@@ -20109,7 +20187,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20123,7 +20201,7 @@
         </is>
       </c>
       <c r="G670" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="671">
@@ -20134,7 +20212,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -20148,7 +20226,7 @@
         </is>
       </c>
       <c r="G671" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="672">
@@ -20159,7 +20237,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -20173,7 +20251,7 @@
         </is>
       </c>
       <c r="G672" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="673">
@@ -20184,7 +20262,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -20198,7 +20276,7 @@
         </is>
       </c>
       <c r="G673" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="674">
@@ -20209,7 +20287,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -20223,7 +20301,7 @@
         </is>
       </c>
       <c r="G674" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="675">
@@ -20234,7 +20312,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -20248,7 +20326,7 @@
         </is>
       </c>
       <c r="G675" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="676">
@@ -20259,7 +20337,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -20273,7 +20351,7 @@
         </is>
       </c>
       <c r="G676" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="677">
@@ -20284,21 +20362,671 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G677" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>Gaspar</t>
-        </is>
-      </c>
-      <c r="D677" t="inlineStr">
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G678" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G679" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G680" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G681" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G682" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G683" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G684" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G685" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G686" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G687" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G688" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G689" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="G677" s="2">
+      <c r="G690" s="2">
         <v>45870</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G691" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G692" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G693" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G694" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G695" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G696" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G697" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G698" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G699" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G700" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G701" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G702" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G703" s="2">
+        <v>45901</v>
       </c>
     </row>
   </sheetData>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G703"/>
+  <dimension ref="A1:G729"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -12770,10 +12770,10 @@
         </is>
       </c>
       <c r="E418">
-        <v>10.32</v>
+        <v>11.33</v>
       </c>
       <c r="F418">
-        <v>-8.02</v>
+        <v>0.98</v>
       </c>
       <c r="G418" s="2">
         <v>45901</v>
@@ -12801,10 +12801,10 @@
         </is>
       </c>
       <c r="E419">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="F419">
-        <v>-1.79</v>
+        <v>-1.94</v>
       </c>
       <c r="G419" s="2">
         <v>45901</v>
@@ -12832,10 +12832,10 @@
         </is>
       </c>
       <c r="E420">
-        <v>5.99</v>
+        <v>5.93</v>
       </c>
       <c r="F420">
-        <v>25.84</v>
+        <v>24.58</v>
       </c>
       <c r="G420" s="2">
         <v>45901</v>
@@ -12863,10 +12863,10 @@
         </is>
       </c>
       <c r="E421">
-        <v>11.94</v>
+        <v>19.08</v>
       </c>
       <c r="F421">
-        <v>-74.31999999999999</v>
+        <v>-58.97</v>
       </c>
       <c r="G421" s="2">
         <v>45901</v>
@@ -12894,10 +12894,10 @@
         </is>
       </c>
       <c r="E422">
-        <v>20.36</v>
+        <v>18.72</v>
       </c>
       <c r="F422">
-        <v>21.33</v>
+        <v>11.56</v>
       </c>
       <c r="G422" s="2">
         <v>45901</v>
@@ -12925,10 +12925,10 @@
         </is>
       </c>
       <c r="E423">
-        <v>377.72</v>
+        <v>350.23</v>
       </c>
       <c r="F423">
-        <v>25.61</v>
+        <v>16.47</v>
       </c>
       <c r="G423" s="2">
         <v>45901</v>
@@ -12956,10 +12956,10 @@
         </is>
       </c>
       <c r="E424">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="F424">
-        <v>-7.05</v>
+        <v>-7.21</v>
       </c>
       <c r="G424" s="2">
         <v>45901</v>
@@ -12987,10 +12987,10 @@
         </is>
       </c>
       <c r="E425">
-        <v>22.14</v>
+        <v>22.57</v>
       </c>
       <c r="F425">
-        <v>-6.82</v>
+        <v>-5.01</v>
       </c>
       <c r="G425" s="2">
         <v>45901</v>
@@ -13018,10 +13018,10 @@
         </is>
       </c>
       <c r="E426">
-        <v>32.92</v>
+        <v>33.15</v>
       </c>
       <c r="F426">
-        <v>-1.79</v>
+        <v>-1.1</v>
       </c>
       <c r="G426" s="2">
         <v>45901</v>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="E427">
-        <v>25.97</v>
+        <v>24.02</v>
       </c>
       <c r="F427">
-        <v>19.02</v>
+        <v>10.08</v>
       </c>
       <c r="G427" s="2">
         <v>45901</v>
@@ -13080,10 +13080,10 @@
         </is>
       </c>
       <c r="E428">
-        <v>99</v>
+        <v>94.2</v>
       </c>
       <c r="F428">
-        <v>3.58</v>
+        <v>-1.44</v>
       </c>
       <c r="G428" s="2">
         <v>45901</v>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="E429">
-        <v>80.91</v>
+        <v>65.12</v>
       </c>
       <c r="F429">
-        <v>-9.83</v>
+        <v>-27.43</v>
       </c>
       <c r="G429" s="2">
         <v>45901</v>
@@ -13142,10 +13142,10 @@
         </is>
       </c>
       <c r="E430">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="F430">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="G430" s="2">
         <v>45901</v>
@@ -13154,17 +13154,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -13172,24 +13172,30 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E431">
+        <v>13.27</v>
+      </c>
+      <c r="F431">
+        <v>17.12</v>
+      </c>
       <c r="G431" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -13197,24 +13203,30 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E432">
+        <v>15</v>
+      </c>
+      <c r="F432">
+        <v>14.07</v>
+      </c>
       <c r="G432" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -13222,24 +13234,30 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E433">
+        <v>5.99</v>
+      </c>
+      <c r="F433">
+        <v>1.01</v>
+      </c>
       <c r="G433" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -13247,24 +13265,30 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E434">
+        <v>29.04</v>
+      </c>
+      <c r="F434">
+        <v>52.2</v>
+      </c>
       <c r="G434" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -13272,24 +13296,30 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E435">
+        <v>19.7</v>
+      </c>
+      <c r="F435">
+        <v>5.24</v>
+      </c>
       <c r="G435" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -13297,24 +13327,30 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E436">
+        <v>253.97</v>
+      </c>
+      <c r="F436">
+        <v>-27.48</v>
+      </c>
       <c r="G436" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -13322,24 +13358,30 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E437">
+        <v>6.15</v>
+      </c>
+      <c r="F437">
+        <v>11.21</v>
+      </c>
       <c r="G437" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -13347,24 +13389,30 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E438">
+        <v>28.3</v>
+      </c>
+      <c r="F438">
+        <v>25.39</v>
+      </c>
       <c r="G438" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -13372,24 +13420,30 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E439">
+        <v>39.86</v>
+      </c>
+      <c r="F439">
+        <v>20.24</v>
+      </c>
       <c r="G439" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -13397,24 +13451,30 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E440">
+        <v>16.53</v>
+      </c>
+      <c r="F440">
+        <v>-31.18</v>
+      </c>
       <c r="G440" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -13422,24 +13482,30 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E441">
+        <v>98.67</v>
+      </c>
+      <c r="F441">
+        <v>4.75</v>
+      </c>
       <c r="G441" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -13447,24 +13513,30 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E442">
+        <v>76.41</v>
+      </c>
+      <c r="F442">
+        <v>17.34</v>
+      </c>
       <c r="G442" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -13472,8 +13544,14 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E443">
+        <v>7.87</v>
+      </c>
+      <c r="F443">
+        <v>20.89</v>
+      </c>
       <c r="G443" s="2">
-        <v>45292</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="444">
@@ -13484,7 +13562,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -13497,11 +13575,8 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
-      <c r="E444">
-        <v>18.31</v>
-      </c>
       <c r="G444" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="445">
@@ -13512,7 +13587,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -13525,11 +13600,8 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
-      <c r="E445">
-        <v>13.46</v>
-      </c>
       <c r="G445" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="446">
@@ -13540,7 +13612,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -13553,11 +13625,8 @@
           <t>Banana</t>
         </is>
       </c>
-      <c r="E446">
-        <v>5.63</v>
-      </c>
       <c r="G446" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="447">
@@ -13568,7 +13637,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -13581,11 +13650,8 @@
           <t>Batata</t>
         </is>
       </c>
-      <c r="E447">
-        <v>56.91</v>
-      </c>
       <c r="G447" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="448">
@@ -13596,7 +13662,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -13609,11 +13675,8 @@
           <t>Café em pó</t>
         </is>
       </c>
-      <c r="E448">
-        <v>8.75</v>
-      </c>
       <c r="G448" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="449">
@@ -13624,7 +13687,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -13637,11 +13700,8 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E449">
-        <v>234.48</v>
-      </c>
       <c r="G449" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="450">
@@ -13652,7 +13712,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -13665,11 +13725,8 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
-      <c r="E450">
-        <v>5.73</v>
-      </c>
       <c r="G450" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="451">
@@ -13680,7 +13737,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -13693,11 +13750,8 @@
           <t>Feijão Preto</t>
         </is>
       </c>
-      <c r="E451">
-        <v>39.21</v>
-      </c>
       <c r="G451" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="452">
@@ -13708,7 +13762,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -13721,11 +13775,8 @@
           <t>Leite</t>
         </is>
       </c>
-      <c r="E452">
-        <v>29.62</v>
-      </c>
       <c r="G452" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="453">
@@ -13736,7 +13787,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13749,11 +13800,8 @@
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="E453">
-        <v>18.75</v>
-      </c>
       <c r="G453" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="454">
@@ -13764,7 +13812,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13777,11 +13825,8 @@
           <t>Pão Francês</t>
         </is>
       </c>
-      <c r="E454">
-        <v>83.66</v>
-      </c>
       <c r="G454" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="455">
@@ -13792,7 +13837,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -13805,11 +13850,8 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="E455">
-        <v>94.41</v>
-      </c>
       <c r="G455" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="456">
@@ -13820,7 +13862,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13833,11 +13875,8 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E456">
-        <v>5.42</v>
-      </c>
       <c r="G456" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="457">
@@ -13848,7 +13887,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -13862,13 +13901,10 @@
         </is>
       </c>
       <c r="E457">
-        <v>19.41</v>
-      </c>
-      <c r="F457">
-        <v>6.01</v>
+        <v>18.31</v>
       </c>
       <c r="G457" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="458">
@@ -13879,7 +13915,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -13893,13 +13929,10 @@
         </is>
       </c>
       <c r="E458">
-        <v>14.67</v>
-      </c>
-      <c r="F458">
-        <v>8.99</v>
+        <v>13.46</v>
       </c>
       <c r="G458" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="459">
@@ -13910,7 +13943,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -13924,13 +13957,10 @@
         </is>
       </c>
       <c r="E459">
-        <v>6.95</v>
-      </c>
-      <c r="F459">
-        <v>23.45</v>
+        <v>5.63</v>
       </c>
       <c r="G459" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="460">
@@ -13941,7 +13971,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13955,13 +13985,10 @@
         </is>
       </c>
       <c r="E460">
-        <v>47.64</v>
-      </c>
-      <c r="F460">
-        <v>-16.29</v>
+        <v>56.91</v>
       </c>
       <c r="G460" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="461">
@@ -13972,7 +13999,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -13986,13 +14013,10 @@
         </is>
       </c>
       <c r="E461">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="F461">
-        <v>4.11</v>
+        <v>8.75</v>
       </c>
       <c r="G461" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="462">
@@ -14003,7 +14027,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -14017,13 +14041,10 @@
         </is>
       </c>
       <c r="E462">
-        <v>275.65</v>
-      </c>
-      <c r="F462">
-        <v>17.56</v>
+        <v>234.48</v>
       </c>
       <c r="G462" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="463">
@@ -14034,7 +14055,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -14048,13 +14069,10 @@
         </is>
       </c>
       <c r="E463">
-        <v>6.43</v>
-      </c>
-      <c r="F463">
-        <v>12.22</v>
+        <v>5.73</v>
       </c>
       <c r="G463" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="464">
@@ -14065,7 +14083,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -14079,13 +14097,10 @@
         </is>
       </c>
       <c r="E464">
-        <v>45.58</v>
-      </c>
-      <c r="F464">
-        <v>16.25</v>
+        <v>39.21</v>
       </c>
       <c r="G464" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="465">
@@ -14096,7 +14111,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -14110,13 +14125,10 @@
         </is>
       </c>
       <c r="E465">
-        <v>30.86</v>
-      </c>
-      <c r="F465">
-        <v>4.19</v>
+        <v>29.62</v>
       </c>
       <c r="G465" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="466">
@@ -14127,7 +14139,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -14141,13 +14153,10 @@
         </is>
       </c>
       <c r="E466">
-        <v>20.05</v>
-      </c>
-      <c r="F466">
-        <v>6.93</v>
+        <v>18.75</v>
       </c>
       <c r="G466" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="467">
@@ -14158,7 +14167,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -14172,13 +14181,10 @@
         </is>
       </c>
       <c r="E467">
-        <v>68.67</v>
-      </c>
-      <c r="F467">
-        <v>-17.92</v>
+        <v>83.66</v>
       </c>
       <c r="G467" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="468">
@@ -14189,7 +14195,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -14203,13 +14209,10 @@
         </is>
       </c>
       <c r="E468">
-        <v>85.41</v>
-      </c>
-      <c r="F468">
-        <v>-9.529999999999999</v>
+        <v>94.41</v>
       </c>
       <c r="G468" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="469">
@@ -14220,7 +14223,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -14234,13 +14237,10 @@
         </is>
       </c>
       <c r="E469">
-        <v>5.55</v>
-      </c>
-      <c r="F469">
-        <v>2.4</v>
+        <v>5.42</v>
       </c>
       <c r="G469" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="470">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -14265,13 +14265,13 @@
         </is>
       </c>
       <c r="E470">
-        <v>18.86</v>
+        <v>19.41</v>
       </c>
       <c r="F470">
-        <v>-2.83</v>
+        <v>6.01</v>
       </c>
       <c r="G470" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="471">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -14296,13 +14296,13 @@
         </is>
       </c>
       <c r="E471">
-        <v>13.88</v>
+        <v>14.67</v>
       </c>
       <c r="F471">
-        <v>-5.39</v>
+        <v>8.99</v>
       </c>
       <c r="G471" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="472">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="E472">
-        <v>6.11</v>
+        <v>6.95</v>
       </c>
       <c r="F472">
-        <v>-12.09</v>
+        <v>23.45</v>
       </c>
       <c r="G472" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="473">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -14358,13 +14358,13 @@
         </is>
       </c>
       <c r="E473">
-        <v>37.94</v>
+        <v>47.64</v>
       </c>
       <c r="F473">
-        <v>-20.36</v>
+        <v>-16.29</v>
       </c>
       <c r="G473" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="474">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="E474">
-        <v>9.18</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F474">
-        <v>0.77</v>
+        <v>4.11</v>
       </c>
       <c r="G474" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="475">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -14420,13 +14420,13 @@
         </is>
       </c>
       <c r="E475">
-        <v>254.3</v>
+        <v>275.65</v>
       </c>
       <c r="F475">
-        <v>-7.75</v>
+        <v>17.56</v>
       </c>
       <c r="G475" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="476">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -14451,13 +14451,13 @@
         </is>
       </c>
       <c r="E476">
-        <v>5.84</v>
+        <v>6.43</v>
       </c>
       <c r="F476">
-        <v>-9.18</v>
+        <v>12.22</v>
       </c>
       <c r="G476" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="477">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -14482,13 +14482,13 @@
         </is>
       </c>
       <c r="E477">
-        <v>40.17</v>
+        <v>45.58</v>
       </c>
       <c r="F477">
-        <v>-11.87</v>
+        <v>16.25</v>
       </c>
       <c r="G477" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="478">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -14513,13 +14513,13 @@
         </is>
       </c>
       <c r="E478">
-        <v>30.55</v>
+        <v>30.86</v>
       </c>
       <c r="F478">
-        <v>-1</v>
+        <v>4.19</v>
       </c>
       <c r="G478" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="479">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -14544,13 +14544,13 @@
         </is>
       </c>
       <c r="E479">
-        <v>20.32</v>
+        <v>20.05</v>
       </c>
       <c r="F479">
-        <v>1.35</v>
+        <v>6.93</v>
       </c>
       <c r="G479" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="480">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -14575,13 +14575,13 @@
         </is>
       </c>
       <c r="E480">
-        <v>81.58</v>
+        <v>68.67</v>
       </c>
       <c r="F480">
-        <v>18.8</v>
+        <v>-17.92</v>
       </c>
       <c r="G480" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="481">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -14606,13 +14606,13 @@
         </is>
       </c>
       <c r="E481">
-        <v>95.61</v>
+        <v>85.41</v>
       </c>
       <c r="F481">
-        <v>11.94</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="G481" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="482">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -14637,13 +14637,13 @@
         </is>
       </c>
       <c r="E482">
-        <v>5.37</v>
+        <v>5.55</v>
       </c>
       <c r="F482">
-        <v>-3.24</v>
+        <v>2.4</v>
       </c>
       <c r="G482" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="483">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -14668,13 +14668,13 @@
         </is>
       </c>
       <c r="E483">
-        <v>17.57</v>
+        <v>18.86</v>
       </c>
       <c r="F483">
-        <v>-6.84</v>
+        <v>-2.83</v>
       </c>
       <c r="G483" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="484">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -14699,13 +14699,13 @@
         </is>
       </c>
       <c r="E484">
-        <v>13.71</v>
+        <v>13.88</v>
       </c>
       <c r="F484">
-        <v>-1.22</v>
+        <v>-5.39</v>
       </c>
       <c r="G484" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="485">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -14733,10 +14733,10 @@
         <v>6.11</v>
       </c>
       <c r="F485">
-        <v>0</v>
+        <v>-12.09</v>
       </c>
       <c r="G485" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="486">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -14761,13 +14761,13 @@
         </is>
       </c>
       <c r="E486">
-        <v>43.94</v>
+        <v>37.94</v>
       </c>
       <c r="F486">
-        <v>15.81</v>
+        <v>-20.36</v>
       </c>
       <c r="G486" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="487">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -14792,13 +14792,13 @@
         </is>
       </c>
       <c r="E487">
-        <v>9.65</v>
+        <v>9.18</v>
       </c>
       <c r="F487">
-        <v>5.12</v>
+        <v>0.77</v>
       </c>
       <c r="G487" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="488">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -14823,13 +14823,13 @@
         </is>
       </c>
       <c r="E488">
-        <v>252.8</v>
+        <v>254.3</v>
       </c>
       <c r="F488">
-        <v>-0.59</v>
+        <v>-7.75</v>
       </c>
       <c r="G488" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="489">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -14854,13 +14854,13 @@
         </is>
       </c>
       <c r="E489">
-        <v>5.66</v>
+        <v>5.84</v>
       </c>
       <c r="F489">
-        <v>-3.08</v>
+        <v>-9.18</v>
       </c>
       <c r="G489" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="490">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -14885,13 +14885,13 @@
         </is>
       </c>
       <c r="E490">
-        <v>35.28</v>
+        <v>40.17</v>
       </c>
       <c r="F490">
-        <v>-12.17</v>
+        <v>-11.87</v>
       </c>
       <c r="G490" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="491">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -14916,13 +14916,13 @@
         </is>
       </c>
       <c r="E491">
-        <v>32.27</v>
+        <v>30.55</v>
       </c>
       <c r="F491">
-        <v>5.63</v>
+        <v>-1</v>
       </c>
       <c r="G491" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="492">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -14947,13 +14947,13 @@
         </is>
       </c>
       <c r="E492">
-        <v>20.09</v>
+        <v>20.32</v>
       </c>
       <c r="F492">
-        <v>-1.13</v>
+        <v>1.35</v>
       </c>
       <c r="G492" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="493">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -14981,10 +14981,10 @@
         <v>81.58</v>
       </c>
       <c r="F493">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="G493" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="494">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="E494">
-        <v>86.28</v>
+        <v>95.61</v>
       </c>
       <c r="F494">
-        <v>-9.76</v>
+        <v>11.94</v>
       </c>
       <c r="G494" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="495">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -15040,13 +15040,13 @@
         </is>
       </c>
       <c r="E495">
-        <v>5.08</v>
+        <v>5.37</v>
       </c>
       <c r="F495">
-        <v>-5.4</v>
+        <v>-3.24</v>
       </c>
       <c r="G495" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="496">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="E496">
-        <v>19.58</v>
+        <v>17.57</v>
       </c>
       <c r="F496">
-        <v>11.44</v>
+        <v>-6.84</v>
       </c>
       <c r="G496" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="497">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -15102,13 +15102,13 @@
         </is>
       </c>
       <c r="E497">
-        <v>13.62</v>
+        <v>13.71</v>
       </c>
       <c r="F497">
-        <v>-0.66</v>
+        <v>-1.22</v>
       </c>
       <c r="G497" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="498">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="E498">
-        <v>5.21</v>
+        <v>6.11</v>
       </c>
       <c r="F498">
-        <v>-14.73</v>
+        <v>0</v>
       </c>
       <c r="G498" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="499">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -15164,13 +15164,13 @@
         </is>
       </c>
       <c r="E499">
-        <v>55.14</v>
+        <v>43.94</v>
       </c>
       <c r="F499">
-        <v>25.49</v>
+        <v>15.81</v>
       </c>
       <c r="G499" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="500">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -15195,13 +15195,13 @@
         </is>
       </c>
       <c r="E500">
-        <v>9.56</v>
+        <v>9.65</v>
       </c>
       <c r="F500">
-        <v>-0.93</v>
+        <v>5.12</v>
       </c>
       <c r="G500" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="501">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -15226,13 +15226,13 @@
         </is>
       </c>
       <c r="E501">
-        <v>237.34</v>
+        <v>252.8</v>
       </c>
       <c r="F501">
-        <v>-6.12</v>
+        <v>-0.59</v>
       </c>
       <c r="G501" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="502">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -15257,13 +15257,13 @@
         </is>
       </c>
       <c r="E502">
-        <v>6.14</v>
+        <v>5.66</v>
       </c>
       <c r="F502">
-        <v>8.48</v>
+        <v>-3.08</v>
       </c>
       <c r="G502" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="503">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -15288,13 +15288,13 @@
         </is>
       </c>
       <c r="E503">
-        <v>32.87</v>
+        <v>35.28</v>
       </c>
       <c r="F503">
-        <v>-6.83</v>
+        <v>-12.17</v>
       </c>
       <c r="G503" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="504">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -15319,13 +15319,13 @@
         </is>
       </c>
       <c r="E504">
-        <v>37.54</v>
+        <v>32.27</v>
       </c>
       <c r="F504">
-        <v>16.33</v>
+        <v>5.63</v>
       </c>
       <c r="G504" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="505">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -15350,13 +15350,13 @@
         </is>
       </c>
       <c r="E505">
-        <v>20.26</v>
+        <v>20.09</v>
       </c>
       <c r="F505">
-        <v>0.85</v>
+        <v>-1.13</v>
       </c>
       <c r="G505" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="506">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="E506">
-        <v>83.67</v>
+        <v>81.58</v>
       </c>
       <c r="F506">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="G506" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="507">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -15412,13 +15412,13 @@
         </is>
       </c>
       <c r="E507">
-        <v>103.41</v>
+        <v>86.28</v>
       </c>
       <c r="F507">
-        <v>19.85</v>
+        <v>-9.76</v>
       </c>
       <c r="G507" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="508">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -15443,13 +15443,13 @@
         </is>
       </c>
       <c r="E508">
-        <v>5.44</v>
+        <v>5.08</v>
       </c>
       <c r="F508">
-        <v>7.09</v>
+        <v>-5.4</v>
       </c>
       <c r="G508" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="509">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -15474,13 +15474,13 @@
         </is>
       </c>
       <c r="E509">
-        <v>19.41</v>
+        <v>19.58</v>
       </c>
       <c r="F509">
-        <v>-0.87</v>
+        <v>11.44</v>
       </c>
       <c r="G509" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="510">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -15505,13 +15505,13 @@
         </is>
       </c>
       <c r="E510">
-        <v>13.54</v>
+        <v>13.62</v>
       </c>
       <c r="F510">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="G510" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="511">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -15536,13 +15536,13 @@
         </is>
       </c>
       <c r="E511">
-        <v>5.59</v>
+        <v>5.21</v>
       </c>
       <c r="F511">
-        <v>7.29</v>
+        <v>-14.73</v>
       </c>
       <c r="G511" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="512">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -15567,13 +15567,13 @@
         </is>
       </c>
       <c r="E512">
-        <v>59.34</v>
+        <v>55.14</v>
       </c>
       <c r="F512">
-        <v>7.62</v>
+        <v>25.49</v>
       </c>
       <c r="G512" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="513">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -15598,13 +15598,13 @@
         </is>
       </c>
       <c r="E513">
-        <v>10.44</v>
+        <v>9.56</v>
       </c>
       <c r="F513">
-        <v>9.210000000000001</v>
+        <v>-0.93</v>
       </c>
       <c r="G513" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="514">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -15629,13 +15629,13 @@
         </is>
       </c>
       <c r="E514">
-        <v>242.59</v>
+        <v>237.34</v>
       </c>
       <c r="F514">
-        <v>2.21</v>
+        <v>-6.12</v>
       </c>
       <c r="G514" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="515">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -15660,13 +15660,13 @@
         </is>
       </c>
       <c r="E515">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="F515">
-        <v>3.09</v>
+        <v>8.48</v>
       </c>
       <c r="G515" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="516">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="E516">
-        <v>33.7</v>
+        <v>32.87</v>
       </c>
       <c r="F516">
-        <v>2.53</v>
+        <v>-6.83</v>
       </c>
       <c r="G516" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="517">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="E517">
-        <v>35.25</v>
+        <v>37.54</v>
       </c>
       <c r="F517">
-        <v>-6.1</v>
+        <v>16.33</v>
       </c>
       <c r="G517" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="518">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -15753,13 +15753,13 @@
         </is>
       </c>
       <c r="E518">
-        <v>20.17</v>
+        <v>20.26</v>
       </c>
       <c r="F518">
-        <v>-0.44</v>
+        <v>0.85</v>
       </c>
       <c r="G518" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="519">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -15784,13 +15784,13 @@
         </is>
       </c>
       <c r="E519">
-        <v>71.58</v>
+        <v>83.67</v>
       </c>
       <c r="F519">
-        <v>-14.45</v>
+        <v>2.56</v>
       </c>
       <c r="G519" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="520">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="E520">
-        <v>58.41</v>
+        <v>103.41</v>
       </c>
       <c r="F520">
-        <v>-43.52</v>
+        <v>19.85</v>
       </c>
       <c r="G520" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="521">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -15846,13 +15846,13 @@
         </is>
       </c>
       <c r="E521">
-        <v>5.32</v>
+        <v>5.44</v>
       </c>
       <c r="F521">
-        <v>-2.21</v>
+        <v>7.09</v>
       </c>
       <c r="G521" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="522">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -15877,13 +15877,13 @@
         </is>
       </c>
       <c r="E522">
-        <v>19.57</v>
+        <v>19.41</v>
       </c>
       <c r="F522">
-        <v>0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="G522" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="523">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -15908,13 +15908,13 @@
         </is>
       </c>
       <c r="E523">
-        <v>13.78</v>
+        <v>13.54</v>
       </c>
       <c r="F523">
-        <v>1.77</v>
+        <v>-0.59</v>
       </c>
       <c r="G523" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="524">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -15939,13 +15939,13 @@
         </is>
       </c>
       <c r="E524">
-        <v>6.11</v>
+        <v>5.59</v>
       </c>
       <c r="F524">
-        <v>9.300000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="G524" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="525">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="E525">
-        <v>48.54</v>
+        <v>59.34</v>
       </c>
       <c r="F525">
-        <v>-18.2</v>
+        <v>7.62</v>
       </c>
       <c r="G525" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="526">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -16004,10 +16004,10 @@
         <v>10.44</v>
       </c>
       <c r="F526">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G526" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="527">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -16032,13 +16032,13 @@
         </is>
       </c>
       <c r="E527">
-        <v>241.01</v>
+        <v>242.59</v>
       </c>
       <c r="F527">
-        <v>-0.65</v>
+        <v>2.21</v>
       </c>
       <c r="G527" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="528">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="E528">
-        <v>6.68</v>
+        <v>6.33</v>
       </c>
       <c r="F528">
-        <v>5.53</v>
+        <v>3.09</v>
       </c>
       <c r="G528" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="529">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -16094,13 +16094,13 @@
         </is>
       </c>
       <c r="E529">
-        <v>33.64</v>
+        <v>33.7</v>
       </c>
       <c r="F529">
-        <v>-0.18</v>
+        <v>2.53</v>
       </c>
       <c r="G529" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="530">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -16125,13 +16125,13 @@
         </is>
       </c>
       <c r="E530">
-        <v>33.48</v>
+        <v>35.25</v>
       </c>
       <c r="F530">
-        <v>-5.02</v>
+        <v>-6.1</v>
       </c>
       <c r="G530" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="531">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -16156,13 +16156,13 @@
         </is>
       </c>
       <c r="E531">
-        <v>20.5</v>
+        <v>20.17</v>
       </c>
       <c r="F531">
-        <v>1.64</v>
+        <v>-0.44</v>
       </c>
       <c r="G531" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="532">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -16187,13 +16187,13 @@
         </is>
       </c>
       <c r="E532">
-        <v>85.58</v>
+        <v>71.58</v>
       </c>
       <c r="F532">
-        <v>19.56</v>
+        <v>-14.45</v>
       </c>
       <c r="G532" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="533">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -16218,13 +16218,13 @@
         </is>
       </c>
       <c r="E533">
-        <v>56.31</v>
+        <v>58.41</v>
       </c>
       <c r="F533">
-        <v>-3.6</v>
+        <v>-43.52</v>
       </c>
       <c r="G533" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="534">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -16249,13 +16249,13 @@
         </is>
       </c>
       <c r="E534">
-        <v>5.35</v>
+        <v>5.32</v>
       </c>
       <c r="F534">
-        <v>0.5600000000000001</v>
+        <v>-2.21</v>
       </c>
       <c r="G534" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="535">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -16280,13 +16280,13 @@
         </is>
       </c>
       <c r="E535">
-        <v>20.28</v>
+        <v>19.57</v>
       </c>
       <c r="F535">
-        <v>3.63</v>
+        <v>0.82</v>
       </c>
       <c r="G535" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="536">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -16311,13 +16311,13 @@
         </is>
       </c>
       <c r="E536">
-        <v>13.71</v>
+        <v>13.78</v>
       </c>
       <c r="F536">
-        <v>-0.51</v>
+        <v>1.77</v>
       </c>
       <c r="G536" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="537">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -16342,13 +16342,13 @@
         </is>
       </c>
       <c r="E537">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="F537">
-        <v>5.07</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G537" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="538">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -16373,13 +16373,13 @@
         </is>
       </c>
       <c r="E538">
-        <v>41.73</v>
+        <v>48.54</v>
       </c>
       <c r="F538">
-        <v>-14.03</v>
+        <v>-18.2</v>
       </c>
       <c r="G538" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="539">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -16404,13 +16404,13 @@
         </is>
       </c>
       <c r="E539">
-        <v>11.04</v>
+        <v>10.44</v>
       </c>
       <c r="F539">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="G539" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="540">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -16435,13 +16435,13 @@
         </is>
       </c>
       <c r="E540">
-        <v>237.85</v>
+        <v>241.01</v>
       </c>
       <c r="F540">
-        <v>-1.31</v>
+        <v>-0.65</v>
       </c>
       <c r="G540" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="541">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="E541">
-        <v>6.41</v>
+        <v>6.68</v>
       </c>
       <c r="F541">
-        <v>-4.04</v>
+        <v>5.53</v>
       </c>
       <c r="G541" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="542">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -16497,13 +16497,13 @@
         </is>
       </c>
       <c r="E542">
-        <v>37.09</v>
+        <v>33.64</v>
       </c>
       <c r="F542">
-        <v>10.26</v>
+        <v>-0.18</v>
       </c>
       <c r="G542" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="543">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -16528,13 +16528,13 @@
         </is>
       </c>
       <c r="E543">
-        <v>34.69</v>
+        <v>33.48</v>
       </c>
       <c r="F543">
-        <v>3.61</v>
+        <v>-5.02</v>
       </c>
       <c r="G543" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="544">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -16559,13 +16559,13 @@
         </is>
       </c>
       <c r="E544">
-        <v>17.59</v>
+        <v>20.5</v>
       </c>
       <c r="F544">
-        <v>-14.2</v>
+        <v>1.64</v>
       </c>
       <c r="G544" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="545">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16590,13 +16590,13 @@
         </is>
       </c>
       <c r="E545">
-        <v>88.06</v>
+        <v>85.58</v>
       </c>
       <c r="F545">
-        <v>2.9</v>
+        <v>19.56</v>
       </c>
       <c r="G545" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="546">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -16621,13 +16621,13 @@
         </is>
       </c>
       <c r="E546">
-        <v>47.79</v>
+        <v>56.31</v>
       </c>
       <c r="F546">
-        <v>-15.13</v>
+        <v>-3.6</v>
       </c>
       <c r="G546" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="547">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -16652,13 +16652,13 @@
         </is>
       </c>
       <c r="E547">
-        <v>5.63</v>
+        <v>5.35</v>
       </c>
       <c r="F547">
-        <v>5.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G547" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="548">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -16683,13 +16683,13 @@
         </is>
       </c>
       <c r="E548">
-        <v>19.38</v>
+        <v>20.28</v>
       </c>
       <c r="F548">
-        <v>-4.44</v>
+        <v>3.63</v>
       </c>
       <c r="G548" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="549">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -16714,13 +16714,13 @@
         </is>
       </c>
       <c r="E549">
-        <v>13.08</v>
+        <v>13.71</v>
       </c>
       <c r="F549">
-        <v>-4.6</v>
+        <v>-0.51</v>
       </c>
       <c r="G549" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="550">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -16745,13 +16745,13 @@
         </is>
       </c>
       <c r="E550">
-        <v>6.59</v>
+        <v>6.42</v>
       </c>
       <c r="F550">
-        <v>2.65</v>
+        <v>5.07</v>
       </c>
       <c r="G550" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="551">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -16776,13 +16776,13 @@
         </is>
       </c>
       <c r="E551">
-        <v>34.74</v>
+        <v>41.73</v>
       </c>
       <c r="F551">
-        <v>-16.75</v>
+        <v>-14.03</v>
       </c>
       <c r="G551" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="552">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -16807,13 +16807,13 @@
         </is>
       </c>
       <c r="E552">
-        <v>11.83</v>
+        <v>11.04</v>
       </c>
       <c r="F552">
-        <v>7.16</v>
+        <v>5.75</v>
       </c>
       <c r="G552" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="553">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -16838,13 +16838,13 @@
         </is>
       </c>
       <c r="E553">
-        <v>238.33</v>
+        <v>237.85</v>
       </c>
       <c r="F553">
-        <v>0.2</v>
+        <v>-1.31</v>
       </c>
       <c r="G553" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="554">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -16869,13 +16869,13 @@
         </is>
       </c>
       <c r="E554">
-        <v>5.98</v>
+        <v>6.41</v>
       </c>
       <c r="F554">
-        <v>-6.71</v>
+        <v>-4.04</v>
       </c>
       <c r="G554" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="555">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -16900,13 +16900,13 @@
         </is>
       </c>
       <c r="E555">
-        <v>32.98</v>
+        <v>37.09</v>
       </c>
       <c r="F555">
-        <v>-11.08</v>
+        <v>10.26</v>
       </c>
       <c r="G555" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="556">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -16931,13 +16931,13 @@
         </is>
       </c>
       <c r="E556">
-        <v>35.17</v>
+        <v>34.69</v>
       </c>
       <c r="F556">
-        <v>1.38</v>
+        <v>3.61</v>
       </c>
       <c r="G556" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="557">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="E557">
-        <v>20.02</v>
+        <v>17.59</v>
       </c>
       <c r="F557">
-        <v>13.81</v>
+        <v>-14.2</v>
       </c>
       <c r="G557" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="558">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -16993,13 +16993,13 @@
         </is>
       </c>
       <c r="E558">
-        <v>77.37</v>
+        <v>88.06</v>
       </c>
       <c r="F558">
-        <v>-12.14</v>
+        <v>2.9</v>
       </c>
       <c r="G558" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="559">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -17024,13 +17024,13 @@
         </is>
       </c>
       <c r="E559">
-        <v>53.46</v>
+        <v>47.79</v>
       </c>
       <c r="F559">
-        <v>11.86</v>
+        <v>-15.13</v>
       </c>
       <c r="G559" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="560">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -17055,13 +17055,13 @@
         </is>
       </c>
       <c r="E560">
-        <v>5.73</v>
+        <v>5.63</v>
       </c>
       <c r="F560">
-        <v>1.78</v>
+        <v>5.23</v>
       </c>
       <c r="G560" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="561">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -17086,13 +17086,13 @@
         </is>
       </c>
       <c r="E561">
-        <v>19.12</v>
+        <v>19.38</v>
       </c>
       <c r="F561">
-        <v>-1.34</v>
+        <v>-4.44</v>
       </c>
       <c r="G561" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="562">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -17117,13 +17117,13 @@
         </is>
       </c>
       <c r="E562">
-        <v>12.87</v>
+        <v>13.08</v>
       </c>
       <c r="F562">
-        <v>-1.61</v>
+        <v>-4.6</v>
       </c>
       <c r="G562" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="563">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -17151,10 +17151,10 @@
         <v>6.59</v>
       </c>
       <c r="F563">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="G563" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="564">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -17179,13 +17179,13 @@
         </is>
       </c>
       <c r="E564">
-        <v>38.94</v>
+        <v>34.74</v>
       </c>
       <c r="F564">
-        <v>12.09</v>
+        <v>-16.75</v>
       </c>
       <c r="G564" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="565">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="E565">
-        <v>12.1</v>
+        <v>11.83</v>
       </c>
       <c r="F565">
-        <v>2.28</v>
+        <v>7.16</v>
       </c>
       <c r="G565" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="566">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -17241,13 +17241,13 @@
         </is>
       </c>
       <c r="E566">
-        <v>282.41</v>
+        <v>238.33</v>
       </c>
       <c r="F566">
-        <v>18.5</v>
+        <v>0.2</v>
       </c>
       <c r="G566" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="567">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -17272,13 +17272,13 @@
         </is>
       </c>
       <c r="E567">
-        <v>6.25</v>
+        <v>5.98</v>
       </c>
       <c r="F567">
-        <v>4.52</v>
+        <v>-6.71</v>
       </c>
       <c r="G567" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="568">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -17303,13 +17303,13 @@
         </is>
       </c>
       <c r="E568">
-        <v>35.39</v>
+        <v>32.98</v>
       </c>
       <c r="F568">
-        <v>7.31</v>
+        <v>-11.08</v>
       </c>
       <c r="G568" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="569">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -17334,13 +17334,13 @@
         </is>
       </c>
       <c r="E569">
-        <v>33.86</v>
+        <v>35.17</v>
       </c>
       <c r="F569">
-        <v>-3.72</v>
+        <v>1.38</v>
       </c>
       <c r="G569" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="570">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -17365,13 +17365,13 @@
         </is>
       </c>
       <c r="E570">
-        <v>20.89</v>
+        <v>20.02</v>
       </c>
       <c r="F570">
-        <v>4.35</v>
+        <v>13.81</v>
       </c>
       <c r="G570" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="571">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -17396,13 +17396,13 @@
         </is>
       </c>
       <c r="E571">
-        <v>71.91</v>
+        <v>77.37</v>
       </c>
       <c r="F571">
-        <v>-7.06</v>
+        <v>-12.14</v>
       </c>
       <c r="G571" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="572">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="E572">
-        <v>44.91</v>
+        <v>53.46</v>
       </c>
       <c r="F572">
-        <v>-15.99</v>
+        <v>11.86</v>
       </c>
       <c r="G572" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="573">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -17458,13 +17458,13 @@
         </is>
       </c>
       <c r="E573">
-        <v>6.36</v>
+        <v>5.73</v>
       </c>
       <c r="F573">
-        <v>10.99</v>
+        <v>1.78</v>
       </c>
       <c r="G573" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="574">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -17489,13 +17489,13 @@
         </is>
       </c>
       <c r="E574">
-        <v>18.57</v>
+        <v>19.12</v>
       </c>
       <c r="F574">
-        <v>-2.88</v>
+        <v>-1.34</v>
       </c>
       <c r="G574" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="575">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -17520,13 +17520,13 @@
         </is>
       </c>
       <c r="E575">
-        <v>13.17</v>
+        <v>12.87</v>
       </c>
       <c r="F575">
-        <v>2.33</v>
+        <v>-1.61</v>
       </c>
       <c r="G575" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="576">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -17551,13 +17551,13 @@
         </is>
       </c>
       <c r="E576">
-        <v>5.99</v>
+        <v>6.59</v>
       </c>
       <c r="F576">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
       <c r="G576" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="577">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -17582,13 +17582,13 @@
         </is>
       </c>
       <c r="E577">
-        <v>23.61</v>
+        <v>38.94</v>
       </c>
       <c r="F577">
-        <v>-39.37</v>
+        <v>12.09</v>
       </c>
       <c r="G577" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="578">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -17613,13 +17613,13 @@
         </is>
       </c>
       <c r="E578">
-        <v>12.26</v>
+        <v>12.1</v>
       </c>
       <c r="F578">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="G578" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="579">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -17644,13 +17644,13 @@
         </is>
       </c>
       <c r="E579">
-        <v>274.33</v>
+        <v>282.41</v>
       </c>
       <c r="F579">
-        <v>-2.86</v>
+        <v>18.5</v>
       </c>
       <c r="G579" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="580">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -17675,13 +17675,13 @@
         </is>
       </c>
       <c r="E580">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="F580">
-        <v>-1.28</v>
+        <v>4.52</v>
       </c>
       <c r="G580" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="581">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -17706,13 +17706,13 @@
         </is>
       </c>
       <c r="E581">
-        <v>33.66</v>
+        <v>35.39</v>
       </c>
       <c r="F581">
-        <v>-4.89</v>
+        <v>7.31</v>
       </c>
       <c r="G581" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="582">
@@ -17723,7 +17723,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -17737,13 +17737,13 @@
         </is>
       </c>
       <c r="E582">
-        <v>35.18</v>
+        <v>33.86</v>
       </c>
       <c r="F582">
-        <v>3.9</v>
+        <v>-3.72</v>
       </c>
       <c r="G582" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="583">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -17768,13 +17768,13 @@
         </is>
       </c>
       <c r="E583">
-        <v>21.11</v>
+        <v>20.89</v>
       </c>
       <c r="F583">
-        <v>1.05</v>
+        <v>4.35</v>
       </c>
       <c r="G583" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="584">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -17799,13 +17799,13 @@
         </is>
       </c>
       <c r="E584">
-        <v>80.37</v>
+        <v>71.91</v>
       </c>
       <c r="F584">
-        <v>11.76</v>
+        <v>-7.06</v>
       </c>
       <c r="G584" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="585">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -17830,13 +17830,13 @@
         </is>
       </c>
       <c r="E585">
-        <v>34.11</v>
+        <v>44.91</v>
       </c>
       <c r="F585">
-        <v>-24.05</v>
+        <v>-15.99</v>
       </c>
       <c r="G585" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="586">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -17861,24 +17861,24 @@
         </is>
       </c>
       <c r="E586">
-        <v>6.83</v>
+        <v>6.36</v>
       </c>
       <c r="F586">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
       <c r="G586" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -17892,24 +17892,24 @@
         </is>
       </c>
       <c r="E587">
-        <v>17.9</v>
+        <v>18.57</v>
       </c>
       <c r="F587">
-        <v>-3.61</v>
+        <v>-2.88</v>
       </c>
       <c r="G587" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -17923,24 +17923,24 @@
         </is>
       </c>
       <c r="E588">
-        <v>14.58</v>
+        <v>13.17</v>
       </c>
       <c r="F588">
-        <v>10.71</v>
+        <v>2.33</v>
       </c>
       <c r="G588" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -17954,24 +17954,24 @@
         </is>
       </c>
       <c r="E589">
-        <v>6.39</v>
+        <v>5.99</v>
       </c>
       <c r="F589">
-        <v>6.68</v>
+        <v>-9.1</v>
       </c>
       <c r="G589" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -17985,24 +17985,24 @@
         </is>
       </c>
       <c r="E590">
-        <v>22.94</v>
+        <v>23.61</v>
       </c>
       <c r="F590">
-        <v>-2.84</v>
+        <v>-39.37</v>
       </c>
       <c r="G590" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -18016,24 +18016,24 @@
         </is>
       </c>
       <c r="E591">
-        <v>13.82</v>
+        <v>12.26</v>
       </c>
       <c r="F591">
-        <v>12.72</v>
+        <v>1.32</v>
       </c>
       <c r="G591" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -18047,24 +18047,24 @@
         </is>
       </c>
       <c r="E592">
-        <v>295.28</v>
+        <v>274.33</v>
       </c>
       <c r="F592">
-        <v>7.64</v>
+        <v>-2.86</v>
       </c>
       <c r="G592" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -18078,24 +18078,24 @@
         </is>
       </c>
       <c r="E593">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="F593">
-        <v>-11.51</v>
+        <v>-1.28</v>
       </c>
       <c r="G593" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -18109,24 +18109,24 @@
         </is>
       </c>
       <c r="E594">
-        <v>30.81</v>
+        <v>33.66</v>
       </c>
       <c r="F594">
-        <v>-8.470000000000001</v>
+        <v>-4.89</v>
       </c>
       <c r="G594" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -18140,24 +18140,24 @@
         </is>
       </c>
       <c r="E595">
-        <v>33.42</v>
+        <v>35.18</v>
       </c>
       <c r="F595">
-        <v>-5</v>
+        <v>3.9</v>
       </c>
       <c r="G595" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -18171,24 +18171,24 @@
         </is>
       </c>
       <c r="E596">
-        <v>21.88</v>
+        <v>21.11</v>
       </c>
       <c r="F596">
-        <v>3.65</v>
+        <v>1.05</v>
       </c>
       <c r="G596" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -18202,24 +18202,24 @@
         </is>
       </c>
       <c r="E597">
-        <v>81.76000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F597">
-        <v>1.73</v>
+        <v>11.76</v>
       </c>
       <c r="G597" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -18233,24 +18233,24 @@
         </is>
       </c>
       <c r="E598">
-        <v>33.81</v>
+        <v>34.11</v>
       </c>
       <c r="F598">
-        <v>-0.88</v>
+        <v>-24.05</v>
       </c>
       <c r="G598" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -18264,13 +18264,13 @@
         </is>
       </c>
       <c r="E599">
-        <v>7.19</v>
+        <v>6.83</v>
       </c>
       <c r="F599">
-        <v>5.27</v>
+        <v>7.39</v>
       </c>
       <c r="G599" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="600">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -18295,13 +18295,13 @@
         </is>
       </c>
       <c r="E600">
-        <v>18.09</v>
+        <v>17.9</v>
       </c>
       <c r="F600">
-        <v>1.06</v>
+        <v>-3.61</v>
       </c>
       <c r="G600" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="601">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -18326,13 +18326,13 @@
         </is>
       </c>
       <c r="E601">
-        <v>14.43</v>
+        <v>14.58</v>
       </c>
       <c r="F601">
-        <v>-1.03</v>
+        <v>10.71</v>
       </c>
       <c r="G601" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="602">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -18357,13 +18357,13 @@
         </is>
       </c>
       <c r="E602">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="F602">
-        <v>-0.63</v>
+        <v>6.68</v>
       </c>
       <c r="G602" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="603">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -18391,10 +18391,10 @@
         <v>22.94</v>
       </c>
       <c r="F603">
-        <v>0</v>
+        <v>-2.84</v>
       </c>
       <c r="G603" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="604">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -18419,13 +18419,13 @@
         </is>
       </c>
       <c r="E604">
-        <v>16.25</v>
+        <v>13.82</v>
       </c>
       <c r="F604">
-        <v>17.58</v>
+        <v>12.72</v>
       </c>
       <c r="G604" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="605">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -18450,13 +18450,13 @@
         </is>
       </c>
       <c r="E605">
-        <v>302.48</v>
+        <v>295.28</v>
       </c>
       <c r="F605">
-        <v>2.44</v>
+        <v>7.64</v>
       </c>
       <c r="G605" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="606">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -18481,13 +18481,13 @@
         </is>
       </c>
       <c r="E606">
-        <v>5.76</v>
+        <v>5.46</v>
       </c>
       <c r="F606">
-        <v>5.49</v>
+        <v>-11.51</v>
       </c>
       <c r="G606" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="607">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -18512,13 +18512,13 @@
         </is>
       </c>
       <c r="E607">
-        <v>32.38</v>
+        <v>30.81</v>
       </c>
       <c r="F607">
-        <v>5.1</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="G607" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="608">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -18546,10 +18546,10 @@
         <v>33.42</v>
       </c>
       <c r="F608">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G608" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="609">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -18574,13 +18574,13 @@
         </is>
       </c>
       <c r="E609">
-        <v>22.14</v>
+        <v>21.88</v>
       </c>
       <c r="F609">
-        <v>1.19</v>
+        <v>3.65</v>
       </c>
       <c r="G609" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="610">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="E610">
-        <v>81.14</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="F610">
-        <v>-0.76</v>
+        <v>1.73</v>
       </c>
       <c r="G610" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="611">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -18636,13 +18636,13 @@
         </is>
       </c>
       <c r="E611">
-        <v>47.91</v>
+        <v>33.81</v>
       </c>
       <c r="F611">
-        <v>41.7</v>
+        <v>-0.88</v>
       </c>
       <c r="G611" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="612">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -18667,13 +18667,13 @@
         </is>
       </c>
       <c r="E612">
-        <v>7.03</v>
+        <v>7.19</v>
       </c>
       <c r="F612">
-        <v>-2.23</v>
+        <v>5.27</v>
       </c>
       <c r="G612" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="613">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="E613">
-        <v>16.67</v>
+        <v>18.09</v>
       </c>
       <c r="F613">
-        <v>-7.85</v>
+        <v>1.06</v>
       </c>
       <c r="G613" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="614">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="E614">
-        <v>13.87</v>
+        <v>14.43</v>
       </c>
       <c r="F614">
-        <v>-3.88</v>
+        <v>-1.03</v>
       </c>
       <c r="G614" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="615">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -18760,13 +18760,13 @@
         </is>
       </c>
       <c r="E615">
-        <v>4.47</v>
+        <v>6.35</v>
       </c>
       <c r="F615">
-        <v>-29.61</v>
+        <v>-0.63</v>
       </c>
       <c r="G615" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="616">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -18791,13 +18791,13 @@
         </is>
       </c>
       <c r="E616">
-        <v>17.54</v>
+        <v>22.94</v>
       </c>
       <c r="F616">
-        <v>-23.54</v>
+        <v>0</v>
       </c>
       <c r="G616" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="617">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -18822,13 +18822,13 @@
         </is>
       </c>
       <c r="E617">
-        <v>16.73</v>
+        <v>16.25</v>
       </c>
       <c r="F617">
-        <v>2.95</v>
+        <v>17.58</v>
       </c>
       <c r="G617" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="618">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -18853,13 +18853,13 @@
         </is>
       </c>
       <c r="E618">
-        <v>306.06</v>
+        <v>302.48</v>
       </c>
       <c r="F618">
-        <v>1.18</v>
+        <v>2.44</v>
       </c>
       <c r="G618" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="619">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -18884,13 +18884,13 @@
         </is>
       </c>
       <c r="E619">
-        <v>6.16</v>
+        <v>5.76</v>
       </c>
       <c r="F619">
-        <v>6.94</v>
+        <v>5.49</v>
       </c>
       <c r="G619" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="620">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -18915,13 +18915,13 @@
         </is>
       </c>
       <c r="E620">
-        <v>26.22</v>
+        <v>32.38</v>
       </c>
       <c r="F620">
-        <v>-19.02</v>
+        <v>5.1</v>
       </c>
       <c r="G620" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="621">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -18946,13 +18946,13 @@
         </is>
       </c>
       <c r="E621">
-        <v>35.12</v>
+        <v>33.42</v>
       </c>
       <c r="F621">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="G621" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="622">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -18977,13 +18977,13 @@
         </is>
       </c>
       <c r="E622">
-        <v>22.5</v>
+        <v>22.14</v>
       </c>
       <c r="F622">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="G622" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="623">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="E623">
-        <v>87.14</v>
+        <v>81.14</v>
       </c>
       <c r="F623">
-        <v>7.39</v>
+        <v>-0.76</v>
       </c>
       <c r="G623" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="624">
@@ -19025,7 +19025,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -19039,13 +19039,13 @@
         </is>
       </c>
       <c r="E624">
-        <v>56.91</v>
+        <v>47.91</v>
       </c>
       <c r="F624">
-        <v>18.79</v>
+        <v>41.7</v>
       </c>
       <c r="G624" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="625">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -19070,13 +19070,13 @@
         </is>
       </c>
       <c r="E625">
-        <v>6.58</v>
+        <v>7.03</v>
       </c>
       <c r="F625">
-        <v>-6.4</v>
+        <v>-2.23</v>
       </c>
       <c r="G625" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="626">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -19100,8 +19100,14 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E626">
+        <v>16.67</v>
+      </c>
+      <c r="F626">
+        <v>-7.85</v>
+      </c>
       <c r="G626" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="627">
@@ -19112,7 +19118,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -19125,8 +19131,14 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E627">
+        <v>13.87</v>
+      </c>
+      <c r="F627">
+        <v>-3.88</v>
+      </c>
       <c r="G627" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="628">
@@ -19137,7 +19149,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -19150,8 +19162,14 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E628">
+        <v>4.47</v>
+      </c>
+      <c r="F628">
+        <v>-29.61</v>
+      </c>
       <c r="G628" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="629">
@@ -19162,7 +19180,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -19175,8 +19193,14 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E629">
+        <v>17.54</v>
+      </c>
+      <c r="F629">
+        <v>-23.54</v>
+      </c>
       <c r="G629" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="630">
@@ -19187,7 +19211,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -19200,8 +19224,14 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E630">
+        <v>16.73</v>
+      </c>
+      <c r="F630">
+        <v>2.95</v>
+      </c>
       <c r="G630" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="631">
@@ -19212,7 +19242,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -19225,8 +19255,14 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E631">
+        <v>306.06</v>
+      </c>
+      <c r="F631">
+        <v>1.18</v>
+      </c>
       <c r="G631" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="632">
@@ -19237,7 +19273,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -19250,8 +19286,14 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E632">
+        <v>6.16</v>
+      </c>
+      <c r="F632">
+        <v>6.94</v>
+      </c>
       <c r="G632" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="633">
@@ -19262,7 +19304,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -19275,8 +19317,14 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E633">
+        <v>26.22</v>
+      </c>
+      <c r="F633">
+        <v>-19.02</v>
+      </c>
       <c r="G633" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="634">
@@ -19287,7 +19335,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -19300,8 +19348,14 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E634">
+        <v>35.12</v>
+      </c>
+      <c r="F634">
+        <v>5.09</v>
+      </c>
       <c r="G634" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="635">
@@ -19312,7 +19366,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -19325,8 +19379,14 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E635">
+        <v>22.5</v>
+      </c>
+      <c r="F635">
+        <v>1.63</v>
+      </c>
       <c r="G635" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="636">
@@ -19337,7 +19397,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -19350,8 +19410,14 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E636">
+        <v>87.14</v>
+      </c>
+      <c r="F636">
+        <v>7.39</v>
+      </c>
       <c r="G636" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="637">
@@ -19362,7 +19428,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -19375,8 +19441,14 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E637">
+        <v>56.91</v>
+      </c>
+      <c r="F637">
+        <v>18.79</v>
+      </c>
       <c r="G637" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="638">
@@ -19387,7 +19459,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -19400,8 +19472,14 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E638">
+        <v>6.58</v>
+      </c>
+      <c r="F638">
+        <v>-6.4</v>
+      </c>
       <c r="G638" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="639">
@@ -19412,7 +19490,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -19426,7 +19504,7 @@
         </is>
       </c>
       <c r="G639" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="640">
@@ -19437,7 +19515,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -19451,7 +19529,7 @@
         </is>
       </c>
       <c r="G640" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="641">
@@ -19462,7 +19540,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -19476,7 +19554,7 @@
         </is>
       </c>
       <c r="G641" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="642">
@@ -19487,7 +19565,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -19501,7 +19579,7 @@
         </is>
       </c>
       <c r="G642" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="643">
@@ -19512,7 +19590,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -19526,7 +19604,7 @@
         </is>
       </c>
       <c r="G643" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="644">
@@ -19537,7 +19615,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -19551,7 +19629,7 @@
         </is>
       </c>
       <c r="G644" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="645">
@@ -19562,7 +19640,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -19576,7 +19654,7 @@
         </is>
       </c>
       <c r="G645" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="646">
@@ -19587,7 +19665,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -19601,7 +19679,7 @@
         </is>
       </c>
       <c r="G646" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="647">
@@ -19612,7 +19690,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -19626,7 +19704,7 @@
         </is>
       </c>
       <c r="G647" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="648">
@@ -19637,7 +19715,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -19651,7 +19729,7 @@
         </is>
       </c>
       <c r="G648" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="649">
@@ -19662,7 +19740,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -19676,7 +19754,7 @@
         </is>
       </c>
       <c r="G649" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="650">
@@ -19687,7 +19765,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -19701,7 +19779,7 @@
         </is>
       </c>
       <c r="G650" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="651">
@@ -19712,7 +19790,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -19726,7 +19804,7 @@
         </is>
       </c>
       <c r="G651" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="652">
@@ -19737,7 +19815,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -19751,7 +19829,7 @@
         </is>
       </c>
       <c r="G652" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="653">
@@ -19762,7 +19840,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -19776,7 +19854,7 @@
         </is>
       </c>
       <c r="G653" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="654">
@@ -19787,7 +19865,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -19801,7 +19879,7 @@
         </is>
       </c>
       <c r="G654" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="655">
@@ -19812,7 +19890,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -19826,7 +19904,7 @@
         </is>
       </c>
       <c r="G655" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="656">
@@ -19837,7 +19915,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -19851,7 +19929,7 @@
         </is>
       </c>
       <c r="G656" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="657">
@@ -19862,7 +19940,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -19876,7 +19954,7 @@
         </is>
       </c>
       <c r="G657" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="658">
@@ -19887,7 +19965,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -19901,7 +19979,7 @@
         </is>
       </c>
       <c r="G658" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="659">
@@ -19912,7 +19990,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -19926,7 +20004,7 @@
         </is>
       </c>
       <c r="G659" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="660">
@@ -19937,7 +20015,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -19951,7 +20029,7 @@
         </is>
       </c>
       <c r="G660" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="661">
@@ -19962,7 +20040,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -19976,7 +20054,7 @@
         </is>
       </c>
       <c r="G661" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="662">
@@ -19987,7 +20065,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -20001,7 +20079,7 @@
         </is>
       </c>
       <c r="G662" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="663">
@@ -20012,7 +20090,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -20026,7 +20104,7 @@
         </is>
       </c>
       <c r="G663" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="664">
@@ -20037,7 +20115,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -20051,7 +20129,7 @@
         </is>
       </c>
       <c r="G664" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="665">
@@ -20062,7 +20140,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -20076,7 +20154,7 @@
         </is>
       </c>
       <c r="G665" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="666">
@@ -20087,7 +20165,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -20101,7 +20179,7 @@
         </is>
       </c>
       <c r="G666" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="667">
@@ -20112,7 +20190,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -20126,7 +20204,7 @@
         </is>
       </c>
       <c r="G667" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="668">
@@ -20137,7 +20215,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -20151,7 +20229,7 @@
         </is>
       </c>
       <c r="G668" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="669">
@@ -20162,7 +20240,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20176,7 +20254,7 @@
         </is>
       </c>
       <c r="G669" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="670">
@@ -20187,7 +20265,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20201,7 +20279,7 @@
         </is>
       </c>
       <c r="G670" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="671">
@@ -20212,7 +20290,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -20226,7 +20304,7 @@
         </is>
       </c>
       <c r="G671" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="672">
@@ -20237,7 +20315,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -20251,7 +20329,7 @@
         </is>
       </c>
       <c r="G672" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="673">
@@ -20262,7 +20340,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -20276,7 +20354,7 @@
         </is>
       </c>
       <c r="G673" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="674">
@@ -20287,7 +20365,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -20301,7 +20379,7 @@
         </is>
       </c>
       <c r="G674" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="675">
@@ -20312,7 +20390,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -20326,7 +20404,7 @@
         </is>
       </c>
       <c r="G675" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="676">
@@ -20337,7 +20415,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -20351,7 +20429,7 @@
         </is>
       </c>
       <c r="G676" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="677">
@@ -20362,7 +20440,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -20376,7 +20454,7 @@
         </is>
       </c>
       <c r="G677" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="678">
@@ -20387,7 +20465,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -20401,7 +20479,7 @@
         </is>
       </c>
       <c r="G678" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="679">
@@ -20412,7 +20490,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -20426,7 +20504,7 @@
         </is>
       </c>
       <c r="G679" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="680">
@@ -20437,7 +20515,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -20451,7 +20529,7 @@
         </is>
       </c>
       <c r="G680" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="681">
@@ -20462,7 +20540,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -20476,7 +20554,7 @@
         </is>
       </c>
       <c r="G681" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="682">
@@ -20487,7 +20565,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -20501,7 +20579,7 @@
         </is>
       </c>
       <c r="G682" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="683">
@@ -20512,7 +20590,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -20526,7 +20604,7 @@
         </is>
       </c>
       <c r="G683" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="684">
@@ -20537,7 +20615,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -20551,7 +20629,7 @@
         </is>
       </c>
       <c r="G684" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="685">
@@ -20562,7 +20640,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -20576,7 +20654,7 @@
         </is>
       </c>
       <c r="G685" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="686">
@@ -20587,7 +20665,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -20601,7 +20679,7 @@
         </is>
       </c>
       <c r="G686" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="687">
@@ -20612,7 +20690,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -20626,7 +20704,7 @@
         </is>
       </c>
       <c r="G687" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="688">
@@ -20637,7 +20715,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -20651,7 +20729,7 @@
         </is>
       </c>
       <c r="G688" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="689">
@@ -20662,7 +20740,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -20676,7 +20754,7 @@
         </is>
       </c>
       <c r="G689" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="690">
@@ -20687,7 +20765,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -20701,7 +20779,7 @@
         </is>
       </c>
       <c r="G690" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="691">
@@ -20712,7 +20790,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -20726,7 +20804,7 @@
         </is>
       </c>
       <c r="G691" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="692">
@@ -20737,7 +20815,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -20751,7 +20829,7 @@
         </is>
       </c>
       <c r="G692" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="693">
@@ -20762,7 +20840,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -20776,7 +20854,7 @@
         </is>
       </c>
       <c r="G693" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="694">
@@ -20787,7 +20865,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -20801,7 +20879,7 @@
         </is>
       </c>
       <c r="G694" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="695">
@@ -20812,7 +20890,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -20826,7 +20904,7 @@
         </is>
       </c>
       <c r="G695" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="696">
@@ -20837,7 +20915,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -20851,7 +20929,7 @@
         </is>
       </c>
       <c r="G696" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="697">
@@ -20862,7 +20940,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -20876,7 +20954,7 @@
         </is>
       </c>
       <c r="G697" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="698">
@@ -20887,7 +20965,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -20901,7 +20979,7 @@
         </is>
       </c>
       <c r="G698" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="699">
@@ -20912,7 +20990,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -20926,7 +21004,7 @@
         </is>
       </c>
       <c r="G699" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="700">
@@ -20937,7 +21015,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -20951,7 +21029,7 @@
         </is>
       </c>
       <c r="G700" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="701">
@@ -20962,7 +21040,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -20976,7 +21054,7 @@
         </is>
       </c>
       <c r="G701" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="702">
@@ -20987,7 +21065,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -21001,7 +21079,7 @@
         </is>
       </c>
       <c r="G702" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="703">
@@ -21012,21 +21090,671 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G703" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
-        <is>
-          <t>Gaspar</t>
-        </is>
-      </c>
-      <c r="D703" t="inlineStr">
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G704" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G705" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G706" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G707" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G708" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G709" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G710" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G711" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G712" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G713" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G714" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G715" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="G703" s="2">
+      <c r="G716" s="2">
         <v>45901</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G717" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G718" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G719" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G720" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G721" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G722" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G723" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G724" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G725" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G726" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G727" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G728" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G729" s="2">
+        <v>45931</v>
       </c>
     </row>
   </sheetData>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="E431">
-        <v>13.27</v>
+        <v>11.69</v>
       </c>
       <c r="F431">
-        <v>17.12</v>
+        <v>3.18</v>
       </c>
       <c r="G431" s="2">
         <v>45931</v>
@@ -13204,10 +13204,10 @@
         </is>
       </c>
       <c r="E432">
-        <v>15</v>
+        <v>14.35</v>
       </c>
       <c r="F432">
-        <v>14.07</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G432" s="2">
         <v>45931</v>
@@ -13235,10 +13235,10 @@
         </is>
       </c>
       <c r="E433">
-        <v>5.99</v>
+        <v>6.33</v>
       </c>
       <c r="F433">
-        <v>1.01</v>
+        <v>6.75</v>
       </c>
       <c r="G433" s="2">
         <v>45931</v>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="E434">
-        <v>29.04</v>
+        <v>26.02</v>
       </c>
       <c r="F434">
-        <v>52.2</v>
+        <v>36.37</v>
       </c>
       <c r="G434" s="2">
         <v>45931</v>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="E435">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="F435">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="G435" s="2">
         <v>45931</v>
@@ -13328,10 +13328,10 @@
         </is>
       </c>
       <c r="E436">
-        <v>253.97</v>
+        <v>306.88</v>
       </c>
       <c r="F436">
-        <v>-27.48</v>
+        <v>-12.38</v>
       </c>
       <c r="G436" s="2">
         <v>45931</v>
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="E437">
-        <v>6.15</v>
+        <v>5.79</v>
       </c>
       <c r="F437">
-        <v>11.21</v>
+        <v>4.7</v>
       </c>
       <c r="G437" s="2">
         <v>45931</v>
@@ -13390,10 +13390,10 @@
         </is>
       </c>
       <c r="E438">
-        <v>28.3</v>
+        <v>25.39</v>
       </c>
       <c r="F438">
-        <v>25.39</v>
+        <v>12.49</v>
       </c>
       <c r="G438" s="2">
         <v>45931</v>
@@ -13421,10 +13421,10 @@
         </is>
       </c>
       <c r="E439">
-        <v>39.86</v>
+        <v>36.49</v>
       </c>
       <c r="F439">
-        <v>20.24</v>
+        <v>10.08</v>
       </c>
       <c r="G439" s="2">
         <v>45931</v>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="E440">
-        <v>16.53</v>
+        <v>20.25</v>
       </c>
       <c r="F440">
-        <v>-31.18</v>
+        <v>-15.7</v>
       </c>
       <c r="G440" s="2">
         <v>45931</v>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="E441">
-        <v>98.67</v>
+        <v>97.94</v>
       </c>
       <c r="F441">
-        <v>4.75</v>
+        <v>3.97</v>
       </c>
       <c r="G441" s="2">
         <v>45931</v>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="E442">
-        <v>76.41</v>
+        <v>63.79</v>
       </c>
       <c r="F442">
-        <v>17.34</v>
+        <v>-2.04</v>
       </c>
       <c r="G442" s="2">
         <v>45931</v>
@@ -13545,10 +13545,10 @@
         </is>
       </c>
       <c r="E443">
-        <v>7.87</v>
+        <v>7.57</v>
       </c>
       <c r="F443">
-        <v>20.89</v>
+        <v>16.28</v>
       </c>
       <c r="G443" s="2">
         <v>45931</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -16279,6 +16279,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E535">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F535">
+        <v>-3.19</v>
+      </c>
       <c r="G535" s="2">
         <v>46174</v>
       </c>
@@ -16304,6 +16310,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E536">
+        <v>17.46</v>
+      </c>
+      <c r="F536">
+        <v>70.18000000000001</v>
+      </c>
       <c r="G536" s="2">
         <v>46174</v>
       </c>
@@ -16329,6 +16341,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E537">
+        <v>5.99</v>
+      </c>
+      <c r="F537">
+        <v>78.81</v>
+      </c>
       <c r="G537" s="2">
         <v>46174</v>
       </c>
@@ -16354,6 +16372,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E538">
+        <v>47.64</v>
+      </c>
+      <c r="F538">
+        <v>104.11</v>
+      </c>
       <c r="G538" s="2">
         <v>46174</v>
       </c>
@@ -16379,6 +16403,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E539">
+        <v>14.14</v>
+      </c>
+      <c r="F539">
+        <v>4.82</v>
+      </c>
       <c r="G539" s="2">
         <v>46174</v>
       </c>
@@ -16404,6 +16434,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E540">
+        <v>323.5</v>
+      </c>
+      <c r="F540">
+        <v>1.14</v>
+      </c>
       <c r="G540" s="2">
         <v>46174</v>
       </c>
@@ -16429,6 +16465,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E541">
+        <v>4.76</v>
+      </c>
+      <c r="F541">
+        <v>2.37</v>
+      </c>
       <c r="G541" s="2">
         <v>46174</v>
       </c>
@@ -16454,6 +16496,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E542">
+        <v>24.26</v>
+      </c>
+      <c r="F542">
+        <v>20.88</v>
+      </c>
       <c r="G542" s="2">
         <v>46174</v>
       </c>
@@ -16479,6 +16527,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E543">
+        <v>40.05</v>
+      </c>
+      <c r="F543">
+        <v>-2.2</v>
+      </c>
       <c r="G543" s="2">
         <v>46174</v>
       </c>
@@ -16504,6 +16558,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E544">
+        <v>21.3</v>
+      </c>
+      <c r="F544">
+        <v>3.45</v>
+      </c>
       <c r="G544" s="2">
         <v>46174</v>
       </c>
@@ -16529,6 +16589,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E545">
+        <v>89.37</v>
+      </c>
+      <c r="F545">
+        <v>7.24</v>
+      </c>
       <c r="G545" s="2">
         <v>46174</v>
       </c>
@@ -16554,6 +16620,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E546">
+        <v>101.12</v>
+      </c>
+      <c r="F546">
+        <v>125.16</v>
+      </c>
       <c r="G546" s="2">
         <v>46174</v>
       </c>
@@ -16578,6 +16650,12 @@
         <is>
           <t>Óleo de Soja</t>
         </is>
+      </c>
+      <c r="E547">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="F547">
+        <v>19.79</v>
       </c>
       <c r="G547" s="2">
         <v>46174</v>
